--- a/2025/retro_2025.xlsx
+++ b/2025/retro_2025.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <workbookPr codeName="ThisWorkbook" hidePivotFieldList="1" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UCF_Challenges\NFL-Fantasy\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NFL-Fantasy\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F771D5-4CA9-44CB-82A2-38CC6250C960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F423A871-7854-4308-9AE6-9FD537F37E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" state="hidden" r:id="rId1"/>
@@ -35,8 +35,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="40" r:id="rId10"/>
-    <pivotCache cacheId="35" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="18" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
@@ -2440,317 +2440,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2796,7 +2486,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2824,7 +2518,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2852,7 +2550,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2880,7 +2582,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2908,7 +2614,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2936,7 +2646,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2964,7 +2678,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -2992,7 +2710,11 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -3020,6 +2742,24 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -3034,7 +2774,267 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -12028,10 +12028,10 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mark Meinhardt" refreshedDate="45968.342070254628" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{73AA8BA1-3B09-4917-AD43-51452F8E9686}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mark Meinhardt" refreshedDate="45969.613406712961" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{73AA8BA1-3B09-4917-AD43-51452F8E9686}">
   <cacheSource type="external" connectionId="2"/>
   <cacheFields count="3">
-    <cacheField name="[tretro 1].[Key].[Key]" caption="Key" numFmtId="0" hierarchy="7" level="1">
+    <cacheField name="[tretro 1].[Key].[Key]" caption="Key" numFmtId="0" hierarchy="8" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3" count="3">
         <n v="1"/>
         <n v="2"/>
@@ -12047,7 +12047,7 @@
         </ext>
       </extLst>
     </cacheField>
-    <cacheField name="[tretro 1].[Key 2].[Key 2]" caption="Key 2" numFmtId="0" hierarchy="10" level="1">
+    <cacheField name="[tretro 1].[Key 2].[Key 2]" caption="Key 2" numFmtId="0" hierarchy="11" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="34" count="9">
         <n v="12"/>
         <n v="13"/>
@@ -12075,11 +12075,12 @@
         </ext>
       </extLst>
     </cacheField>
-    <cacheField name="[Measures].[Count of Key 2]" caption="Count of Key 2" numFmtId="0" hierarchy="34" level="32767"/>
+    <cacheField name="[Measures].[Count of Key 2]" caption="Count of Key 2" numFmtId="0" hierarchy="35" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="35">
+  <cacheHierarchies count="36">
     <cacheHierarchy uniqueName="[tretro 1].[Winnings]" caption="Winnings" attribute="1" defaultMemberUniqueName="[tretro 1].[Winnings].[All]" allUniqueName="[tretro 1].[Winnings].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[Winners]" caption="Winners" attribute="1" defaultMemberUniqueName="[tretro 1].[Winners].[All]" allUniqueName="[tretro 1].[Winners].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[tretro 1].[Place]" caption="Place" attribute="1" defaultMemberUniqueName="[tretro 1].[Place].[All]" allUniqueName="[tretro 1].[Place].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[HS Position]" caption="HS Position" attribute="1" defaultMemberUniqueName="[tretro 1].[HS Position].[All]" allUniqueName="[tretro 1].[HS Position].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[HS MVP]" caption="HS MVP" attribute="1" defaultMemberUniqueName="[tretro 1].[HS MVP].[All]" allUniqueName="[tretro 1].[HS MVP].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[HS Wins]" caption="HS Wins" attribute="1" defaultMemberUniqueName="[tretro 1].[HS Wins].[All]" allUniqueName="[tretro 1].[HS Wins].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
@@ -12112,7 +12113,7 @@
     <cacheHierarchy uniqueName="[tretro 1].[total_salary]" caption="total_salary" attribute="1" defaultMemberUniqueName="[tretro 1].[total_salary].[All]" allUniqueName="[tretro 1].[total_salary].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[total_fppg]" caption="total_fppg" attribute="1" defaultMemberUniqueName="[tretro 1].[total_fppg].[All]" allUniqueName="[tretro 1].[total_fppg].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[total_ppts]" caption="total_ppts" attribute="1" defaultMemberUniqueName="[tretro 1].[total_ppts].[All]" allUniqueName="[tretro 1].[total_ppts].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[total_pts]" caption="total_pts" attribute="1" defaultMemberUniqueName="[tretro 1].[total_pts].[All]" allUniqueName="[tretro 1].[total_pts].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[tretro 1].[total_fpts]" caption="total_fpts" attribute="1" defaultMemberUniqueName="[tretro 1].[total_fpts].[All]" allUniqueName="[tretro 1].[total_fpts].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[MVP_name]" caption="MVP_name" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP_name].[All]" allUniqueName="[tretro 1].[MVP_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[p2_name]" caption="p2_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p2_name].[All]" allUniqueName="[tretro 1].[p2_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[tretro 1].[p3_name]" caption="p3_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p3_name].[All]" allUniqueName="[tretro 1].[p3_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
@@ -12124,7 +12125,7 @@
     <cacheHierarchy uniqueName="[Measures].[Sum of Key]" caption="Sum of Key" measure="1" displayFolder="" measureGroup="tretro 1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="10"/>
+          <x15:cacheHierarchy aggregatedColumn="11"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -12134,7 +12135,7 @@
       </fieldsUsage>
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="10"/>
+          <x15:cacheHierarchy aggregatedColumn="11"/>
         </ext>
       </extLst>
     </cacheHierarchy>
@@ -13253,7 +13254,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB527574-7E05-49A2-899E-EFF9B6B3BA1E}" name="PivotTable1" cacheId="35" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB527574-7E05-49A2-899E-EFF9B6B3BA1E}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Key">
   <location ref="Q2:S12" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="3">
     <pivotField name="Key" axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -13334,7 +13335,8 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="35">
+  <pivotHierarchies count="36">
+    <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -13373,8 +13375,8 @@
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="2">
-    <rowHierarchyUsage hierarchyUsage="7"/>
-    <rowHierarchyUsage hierarchyUsage="10"/>
+    <rowHierarchyUsage hierarchyUsage="8"/>
+    <rowHierarchyUsage hierarchyUsage="11"/>
   </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -13393,7 +13395,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
   <location ref="J17:K37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -13572,7 +13574,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
   <location ref="G2:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0"/>
@@ -13695,125 +13697,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
-  <location ref="G19:H24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
-    <pivotField numFmtId="4" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="5">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="11">
-        <item x="9"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="3"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count" fld="5" subtotal="count" baseField="5" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Key">
   <location ref="R2:T19" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -13989,8 +13873,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
   <location ref="G2:H14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -14198,8 +14082,126 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
+  <location ref="G19:H24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="32">
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="11">
+        <item x="9"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count" fld="5" subtotal="count" baseField="5" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
   <location ref="Q2:T9" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" showAll="0"/>
@@ -14350,7 +14352,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
   <location ref="B15:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -14468,7 +14470,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="40" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="O2:R31" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -14829,26 +14831,26 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="46" dataDxfId="45" totalsRowDxfId="44">
   <autoFilter ref="A1:T34" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="42" totalsRowDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="40" totalsRowDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="38" totalsRowDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="36" totalsRowDxfId="16"/>
-    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="15"/>
-    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="34" totalsRowDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="13"/>
-    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="32" totalsRowDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="11"/>
-    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="30" totalsRowDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="9"/>
-    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="28" totalsRowDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="7"/>
-    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="26" totalsRowDxfId="6"/>
-    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="24" totalsRowDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15788,7 +15790,7 @@
     <col min="16" max="16" width="2.59765625" customWidth="1"/>
     <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.59765625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>

--- a/2025/retro_2025.xlsx
+++ b/2025/retro_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NFL-Fantasy\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F423A871-7854-4308-9AE6-9FD537F37E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2FB437-A941-47C5-A795-CFBF303F330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" state="hidden" r:id="rId1"/>
@@ -35,8 +35,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId10"/>
-    <pivotCache cacheId="18" r:id="rId11"/>
+    <pivotCache cacheId="5" r:id="rId10"/>
+    <pivotCache cacheId="17" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="531">
   <si>
     <t>p2_pos</t>
   </si>
@@ -1186,9 +1186,6 @@
   </si>
   <si>
     <t>WR1:SEA</t>
-  </si>
-  <si>
-    <t>WR:MIN</t>
   </si>
   <si>
     <t>WR:NYG</t>
@@ -2379,7 +2376,13 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="50">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6922,68 +6925,110 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'MVP by Key'!$R$3:$S$19</c:f>
+              <c:f>'MVP by Key'!$R$3:$S$25</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="22"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>1</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>2</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>3</c:v>
+                    <c:v>14</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>4</c:v>
+                    <c:v>16</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>5</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>6</c:v>
+                    <c:v>23</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>8</c:v>
+                    <c:v>24</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>10</c:v>
+                    <c:v>27</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>15</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>22</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="10">
-                    <c:v>2</c:v>
+                    <c:v>23</c:v>
                   </c:pt>
                   <c:pt idx="11">
-                    <c:v>3</c:v>
+                    <c:v>13</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>5</c:v>
+                    <c:v>34</c:v>
                   </c:pt>
                   <c:pt idx="13">
-                    <c:v>8</c:v>
+                    <c:v>12</c:v>
                   </c:pt>
                   <c:pt idx="14">
-                    <c:v>9</c:v>
+                    <c:v>23</c:v>
                   </c:pt>
                   <c:pt idx="15">
-                    <c:v>4</c:v>
+                    <c:v>16</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>14</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>23</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>29</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>12</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>12</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>1</c:v>
                   </c:pt>
-                  <c:pt idx="10">
+                  <c:pt idx="4">
                     <c:v>2</c:v>
                   </c:pt>
+                  <c:pt idx="8">
+                    <c:v>3</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>4</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>5</c:v>
+                  </c:pt>
                   <c:pt idx="15">
-                    <c:v>3</c:v>
+                    <c:v>6</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>8</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>9</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>10</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>15</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>22</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -6991,45 +7036,45 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVP by Key'!$T$3:$T$19</c:f>
+              <c:f>'MVP by Key'!$T$3:$T$25</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="22"/>
                 <c:pt idx="0">
-                  <c:v>7</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="8">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="11">
                   <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>1</c:v>
@@ -7041,6 +7086,24 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -7111,10 +7174,13 @@
   <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
     </c:ext>
   </c:extLst>
 </c:chartSpace>
@@ -7734,7 +7800,7 @@
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -7775,6 +7841,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'MVP by Key'!$G$20:$G$24</c:f>
@@ -8148,53 +8271,239 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
-              <c:f>'MVP by Player-Position'!$Q$3:$S$9</c:f>
-              <c:strCache>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>D</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>QB</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>RB</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>TE</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>WR1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>WR3</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:multiLvlStrRef>
+              <c:f>'MVP by Player-Position'!$Q$3:$S$47</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="28"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>D:DEN</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>QB:ARI</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>QB:BAL</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>QB:CHI</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>QB:DAL</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>QB:DEN</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>QB:KC</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>QB:LAC</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>QB:LAR</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>QB:SEA</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>QB:TB</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>RB:DAL</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>RB:NYG</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>RB1:ATL</c:v>
+                  </c:pt>
+                  <c:pt idx="14">
+                    <c:v>RB1:BUF</c:v>
+                  </c:pt>
+                  <c:pt idx="15">
+                    <c:v>RB1:CHI</c:v>
+                  </c:pt>
+                  <c:pt idx="16">
+                    <c:v>RB1:DET</c:v>
+                  </c:pt>
+                  <c:pt idx="17">
+                    <c:v>RB1:SF</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>RB2:DET</c:v>
+                  </c:pt>
+                  <c:pt idx="19">
+                    <c:v>RB2:NYG</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>TE:GB</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>TE1:GB</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>TE2:PIT</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>WR1:ARI</c:v>
+                  </c:pt>
+                  <c:pt idx="24">
+                    <c:v>WR1:LAR</c:v>
+                  </c:pt>
+                  <c:pt idx="25">
+                    <c:v>WR1:NE</c:v>
+                  </c:pt>
+                  <c:pt idx="26">
+                    <c:v>WR1:SEA</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>WR3:BUF</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>D</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>QB</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>RB</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>RB1</c:v>
+                  </c:pt>
+                  <c:pt idx="18">
+                    <c:v>RB2</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>TE</c:v>
+                  </c:pt>
+                  <c:pt idx="21">
+                    <c:v>TE1</c:v>
+                  </c:pt>
+                  <c:pt idx="22">
+                    <c:v>TE2</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>WR1</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>WR3</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>D</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>QB</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>RB</c:v>
+                  </c:pt>
+                  <c:pt idx="20">
+                    <c:v>TE</c:v>
+                  </c:pt>
+                  <c:pt idx="23">
+                    <c:v>WR1</c:v>
+                  </c:pt>
+                  <c:pt idx="27">
+                    <c:v>WR3</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVP by Player-Position'!$T$3:$T$9</c:f>
+              <c:f>'MVP by Player-Position'!$T$3:$T$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>14</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>4</c:v>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -8414,7 +8723,7 @@
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -8455,6 +8764,63 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Team Count'!$B$16:$B$20</c:f>
@@ -11864,7 +12230,17 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="15795"/>
     </cacheField>
     <cacheField name="Key 2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="34"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="34" count="9">
+        <n v="12"/>
+        <n v="13"/>
+        <n v="23"/>
+        <n v="16"/>
+        <n v="29"/>
+        <n v="24"/>
+        <n v="14"/>
+        <n v="34"/>
+        <n v="27"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="MVP Key" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="22" count="11">
@@ -12028,7 +12404,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mark Meinhardt" refreshedDate="45969.613406712961" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{73AA8BA1-3B09-4917-AD43-51452F8E9686}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mark Meinhardt" refreshedDate="45969.642203356481" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{73AA8BA1-3B09-4917-AD43-51452F8E9686}">
   <cacheSource type="external" connectionId="2"/>
   <cacheFields count="3">
     <cacheField name="[tretro 1].[Key].[Key]" caption="Key" numFmtId="0" hierarchy="8" level="1">
@@ -12172,7 +12548,7 @@
     <x v="0"/>
     <n v="108"/>
     <n v="53"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -12205,7 +12581,7 @@
     <x v="0"/>
     <n v="27863"/>
     <n v="5037"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
@@ -12238,7 +12614,7 @@
     <x v="0"/>
     <n v="83"/>
     <n v="48"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="2"/>
     <x v="2"/>
@@ -12271,7 +12647,7 @@
     <x v="1"/>
     <n v="78776"/>
     <n v="14416"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="3"/>
     <x v="3"/>
@@ -12304,7 +12680,7 @@
     <x v="0"/>
     <n v="227"/>
     <n v="71"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="2"/>
     <x v="4"/>
     <x v="4"/>
@@ -12337,7 +12713,7 @@
     <x v="0"/>
     <n v="2707"/>
     <n v="706"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="5"/>
     <x v="5"/>
@@ -12370,7 +12746,7 @@
     <x v="0"/>
     <n v="14668"/>
     <n v="2884"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="4"/>
     <x v="6"/>
     <x v="6"/>
@@ -12403,7 +12779,7 @@
     <x v="0"/>
     <n v="32522"/>
     <n v="5988"/>
-    <n v="16"/>
+    <x v="3"/>
     <x v="4"/>
     <x v="7"/>
     <x v="1"/>
@@ -12436,7 +12812,7 @@
     <x v="0"/>
     <n v="30089"/>
     <n v="5736"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="3"/>
     <x v="7"/>
@@ -12469,7 +12845,7 @@
     <x v="1"/>
     <n v="54196"/>
     <n v="9605"/>
-    <n v="29"/>
+    <x v="4"/>
     <x v="5"/>
     <x v="0"/>
     <x v="8"/>
@@ -12502,7 +12878,7 @@
     <x v="1"/>
     <n v="45325"/>
     <n v="8121"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="6"/>
     <x v="4"/>
     <x v="9"/>
@@ -12535,7 +12911,7 @@
     <x v="1"/>
     <n v="88847"/>
     <n v="15795"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="3"/>
     <x v="8"/>
     <x v="10"/>
@@ -12568,7 +12944,7 @@
     <x v="0"/>
     <n v="36784"/>
     <n v="6925"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="1"/>
     <x v="9"/>
     <x v="11"/>
@@ -12601,7 +12977,7 @@
     <x v="1"/>
     <n v="35310"/>
     <n v="6705"/>
-    <n v="24"/>
+    <x v="5"/>
     <x v="3"/>
     <x v="5"/>
     <x v="12"/>
@@ -12634,7 +13010,7 @@
     <x v="1"/>
     <n v="4973"/>
     <n v="856"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="10"/>
     <x v="13"/>
@@ -12667,7 +13043,7 @@
     <x v="0"/>
     <n v="68287"/>
     <n v="12679"/>
-    <n v="16"/>
+    <x v="3"/>
     <x v="7"/>
     <x v="11"/>
     <x v="14"/>
@@ -12700,7 +13076,7 @@
     <x v="0"/>
     <n v="56121"/>
     <n v="10717"/>
-    <n v="14"/>
+    <x v="6"/>
     <x v="4"/>
     <x v="9"/>
     <x v="15"/>
@@ -12733,7 +13109,7 @@
     <x v="0"/>
     <n v="8942"/>
     <n v="1883"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="8"/>
     <x v="2"/>
     <x v="16"/>
@@ -12766,7 +13142,7 @@
     <x v="0"/>
     <n v="1922"/>
     <n v="467"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="12"/>
     <x v="5"/>
@@ -12799,7 +13175,7 @@
     <x v="2"/>
     <n v="77753"/>
     <n v="14109"/>
-    <n v="34"/>
+    <x v="7"/>
     <x v="8"/>
     <x v="4"/>
     <x v="15"/>
@@ -12832,7 +13208,7 @@
     <x v="0"/>
     <n v="9078"/>
     <n v="1925"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="9"/>
     <x v="13"/>
     <x v="17"/>
@@ -12865,7 +13241,7 @@
     <x v="0"/>
     <n v="992"/>
     <n v="298"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="10"/>
     <x v="14"/>
     <x v="18"/>
@@ -12898,7 +13274,7 @@
     <x v="0"/>
     <n v="6289"/>
     <n v="1349"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="1"/>
     <x v="19"/>
@@ -12931,7 +13307,7 @@
     <x v="0"/>
     <n v="18281"/>
     <n v="3478"/>
-    <n v="13"/>
+    <x v="1"/>
     <x v="4"/>
     <x v="15"/>
     <x v="20"/>
@@ -12964,7 +13340,7 @@
     <x v="0"/>
     <n v="28628"/>
     <n v="5364"/>
-    <n v="14"/>
+    <x v="6"/>
     <x v="4"/>
     <x v="4"/>
     <x v="21"/>
@@ -12997,7 +13373,7 @@
     <x v="1"/>
     <n v="35517"/>
     <n v="6303"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="1"/>
     <x v="16"/>
     <x v="22"/>
@@ -13030,7 +13406,7 @@
     <x v="1"/>
     <n v="64130"/>
     <n v="11503"/>
-    <n v="27"/>
+    <x v="8"/>
     <x v="3"/>
     <x v="4"/>
     <x v="1"/>
@@ -13063,7 +13439,7 @@
     <x v="1"/>
     <n v="29325"/>
     <n v="5723"/>
-    <n v="23"/>
+    <x v="2"/>
     <x v="9"/>
     <x v="10"/>
     <x v="23"/>
@@ -13096,7 +13472,7 @@
     <x v="0"/>
     <n v="14639"/>
     <n v="3064"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="3"/>
     <x v="17"/>
     <x v="15"/>
@@ -13129,7 +13505,7 @@
     <x v="0"/>
     <n v="5640"/>
     <n v="1291"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="4"/>
     <x v="11"/>
     <x v="24"/>
@@ -13162,7 +13538,7 @@
     <x v="0"/>
     <n v="1"/>
     <n v="1"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="1"/>
     <x v="18"/>
     <x v="25"/>
@@ -13195,7 +13571,7 @@
     <x v="0"/>
     <n v="13640"/>
     <n v="2832"/>
-    <n v="14"/>
+    <x v="6"/>
     <x v="6"/>
     <x v="1"/>
     <x v="26"/>
@@ -13228,7 +13604,7 @@
     <x v="0"/>
     <n v="11961"/>
     <n v="2457"/>
-    <n v="12"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="4"/>
     <x v="27"/>
@@ -13254,7 +13630,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB527574-7E05-49A2-899E-EFF9B6B3BA1E}" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB527574-7E05-49A2-899E-EFF9B6B3BA1E}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Key">
   <location ref="Q2:S12" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="3">
     <pivotField name="Key" axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -13395,7 +13771,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
   <location ref="J17:K37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -13574,7 +13950,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
   <location ref="G2:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0"/>
@@ -13697,8 +14073,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Key">
-  <location ref="R2:T19" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Key">
+  <location ref="R2:T25" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -13720,7 +14096,7 @@
         <item x="2"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="12">
         <item m="1" x="3"/>
         <item m="1" x="4"/>
@@ -13738,7 +14114,19 @@
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="7"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="11">
         <item x="4"/>
@@ -13785,12 +14173,12 @@
     </pivotField>
   </pivotFields>
   <rowFields count="2">
-    <field x="7"/>
     <field x="11"/>
+    <field x="10"/>
   </rowFields>
-  <rowItems count="17">
+  <rowItems count="23">
     <i>
-      <x v="9"/>
+      <x/>
       <x/>
     </i>
     <i r="1">
@@ -13802,6 +14190,10 @@
     <i r="1">
       <x v="3"/>
     </i>
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
     <i r="1">
       <x v="4"/>
     </i>
@@ -13811,34 +14203,56 @@
     <i r="1">
       <x v="6"/>
     </i>
+    <i>
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="1"/>
+    </i>
     <i r="1">
       <x v="8"/>
     </i>
-    <i r="1">
-      <x v="9"/>
+    <i>
+      <x v="4"/>
+      <x/>
     </i>
     <i r="1">
-      <x v="10"/>
+      <x v="4"/>
     </i>
     <i>
-      <x v="10"/>
-      <x v="1"/>
+      <x v="5"/>
+      <x v="3"/>
     </i>
-    <i r="1">
+    <i>
+      <x v="6"/>
       <x v="2"/>
     </i>
     <i r="1">
       <x v="4"/>
     </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
+    <i>
+      <x v="7"/>
       <x v="7"/>
     </i>
     <i>
-      <x v="11"/>
-      <x v="3"/>
+      <x v="8"/>
+      <x/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -13874,7 +14288,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
   <location ref="G2:H14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -14083,7 +14497,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
   <location ref="G19:H24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -14201,8 +14615,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
-  <location ref="Q2:T9" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
+  <location ref="Q2:T47" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
@@ -14212,17 +14626,17 @@
     <pivotField compact="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" showAll="0" sortType="ascending">
       <items count="11">
-        <item sd="0" x="9"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="0"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="2"/>
-        <item t="default" sd="0"/>
+        <item x="9"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item t="default"/>
       </items>
     </pivotField>
     <pivotField compact="0" showAll="0"/>
@@ -14284,13 +14698,13 @@
     <pivotField compact="0" showAll="0"/>
     <pivotField axis="axisRow" compact="0" showAll="0">
       <items count="7">
-        <item sd="0" x="3"/>
-        <item sd="0" x="0"/>
-        <item n="RB" sd="0" x="4"/>
-        <item n="TE" sd="0" x="5"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="1"/>
-        <item t="default" sd="0"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item n="RB" x="4"/>
+        <item n="TE" x="5"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
@@ -14299,24 +14713,138 @@
     <field x="6"/>
     <field x="13"/>
   </rowFields>
-  <rowItems count="7">
+  <rowItems count="45">
     <i>
+      <x/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="2">
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="6"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="10"/>
+    </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="12"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="13"/>
+    </i>
+    <i r="2">
+      <x v="14"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
     </i>
     <i>
       <x v="3"/>
     </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="20"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i r="2">
+      <x v="21"/>
+    </i>
+    <i r="1">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
     <i>
       <x v="4"/>
     </i>
+    <i r="1">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="25"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
     <i>
       <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="27"/>
     </i>
     <i t="grand">
       <x/>
@@ -14352,7 +14880,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
   <location ref="B15:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="32">
     <pivotField numFmtId="4" showAll="0"/>
@@ -14470,7 +14998,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
   <location ref="O2:R31" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
   <pivotFields count="32">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -14779,18 +15307,18 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}" name="Table1" displayName="Table1" ref="A1:AF34" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}" name="Table1" displayName="Table1" ref="A1:AF34" totalsRowShown="0" headerRowDxfId="49">
   <autoFilter ref="A1:AF34" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{D2AA0CDD-D609-4F29-A891-5B2A9B97B638}" name="Winnings"/>
     <tableColumn id="2" xr3:uid="{951CDDCB-E748-4FBA-BC57-9BC6CB4ABD61}" name="Winners"/>
     <tableColumn id="32" xr3:uid="{C9B46930-60A5-4A52-A107-30CA389A4430}" name="Place"/>
     <tableColumn id="3" xr3:uid="{96316C00-9998-4DEC-93B0-2A0C771E2793}" name="HS Position"/>
-    <tableColumn id="4" xr3:uid="{EFF99116-80B7-47B5-A377-CCBE51772AED}" name="HS MVP">
-      <calculatedColumnFormula>COUNTIF(Retro!$I2,Retro!$M2)</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{EFF99116-80B7-47B5-A377-CCBE51772AED}" name="HS MVP" dataDxfId="0">
+      <calculatedColumnFormula>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F8284C57-8CD4-4C8E-9CBC-0015B3198933}" name="HS Wins">
-      <calculatedColumnFormula>COUNTIF(Retro!$I2,"&lt;&gt;"&amp;Retro!$M2)</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{F8284C57-8CD4-4C8E-9CBC-0015B3198933}" name="HS Wins" dataDxfId="1">
+      <calculatedColumnFormula>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{082E3E39-C3ED-495A-A992-2A8BE58C2DD0}" name="MVP Pts Rank"/>
     <tableColumn id="7" xr3:uid="{D409B8A2-BC75-49E9-A374-2C6980818423}" name="MVP Position">
@@ -14828,29 +15356,29 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="46" dataDxfId="45" totalsRowDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
   <autoFilter ref="A1:T34" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="5" totalsRowDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -15175,93 +15703,93 @@
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A1" s="52" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B3" t="s">
         <v>434</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>435</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>436</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>437</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>438</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>439</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>440</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>441</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>442</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>443</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>444</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>445</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>446</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>447</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>448</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" t="s">
         <v>449</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>450</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>451</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>452</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>453</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>454</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>455</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>456</v>
       </c>
-      <c r="X3" t="s">
+      <c r="Y3" t="s">
         <v>457</v>
       </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>458</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AA3" t="s">
         <v>459</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>460</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.45">
@@ -15385,16 +15913,16 @@
         <v>97</v>
       </c>
       <c r="M5" t="s">
+        <v>427</v>
+      </c>
+      <c r="N5" t="s">
         <v>428</v>
       </c>
-      <c r="N5" t="s">
+      <c r="O5" t="s">
         <v>429</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>430</v>
-      </c>
-      <c r="P5" t="s">
-        <v>431</v>
       </c>
       <c r="R5">
         <v>3</v>
@@ -15427,7 +15955,7 @@
         <v>157</v>
       </c>
       <c r="AB5" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.45">
@@ -15462,7 +15990,7 @@
         <v>20</v>
       </c>
       <c r="K6" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L6" t="s">
         <v>25</v>
@@ -15474,10 +16002,10 @@
         <v>166</v>
       </c>
       <c r="O6" t="s">
+        <v>385</v>
+      </c>
+      <c r="P6" t="s">
         <v>386</v>
-      </c>
-      <c r="P6" t="s">
-        <v>387</v>
       </c>
       <c r="R6">
         <v>4</v>
@@ -15521,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -15548,7 +16076,7 @@
         <v>57</v>
       </c>
       <c r="L7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="M7" t="s">
         <v>51</v>
@@ -15560,7 +16088,7 @@
         <v>16</v>
       </c>
       <c r="P7" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R7">
         <v>4</v>
@@ -15637,13 +16165,13 @@
         <v>235</v>
       </c>
       <c r="N8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="P8" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="R8">
         <v>2</v>
@@ -15676,7 +16204,7 @@
         <v>240</v>
       </c>
       <c r="AB8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.45">
@@ -15717,16 +16245,16 @@
         <v>37</v>
       </c>
       <c r="M9" t="s">
+        <v>413</v>
+      </c>
+      <c r="N9" t="s">
         <v>414</v>
       </c>
-      <c r="N9" t="s">
+      <c r="O9" t="s">
         <v>415</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>416</v>
-      </c>
-      <c r="P9" t="s">
-        <v>417</v>
       </c>
       <c r="R9">
         <v>4</v>
@@ -15789,8 +16317,8 @@
     <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2.59765625" customWidth="1"/>
     <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.796875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15799,16 +16327,16 @@
         <v>340</v>
       </c>
       <c r="H2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q2" s="56" t="s">
         <v>340</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="S2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="7:26" x14ac:dyDescent="0.45">
@@ -15868,7 +16396,7 @@
     </row>
     <row r="6" spans="7:26" x14ac:dyDescent="0.45">
       <c r="G6" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H6" s="53">
         <v>33</v>
@@ -15952,7 +16480,7 @@
     </row>
     <row r="12" spans="7:26" x14ac:dyDescent="0.45">
       <c r="Q12" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="S12" s="53">
         <v>32</v>
@@ -15991,10 +16519,10 @@
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J17" s="56" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="K17" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="U17" s="16"/>
       <c r="V17" s="12"/>
@@ -16203,7 +16731,7 @@
     </row>
     <row r="37" spans="10:18" x14ac:dyDescent="0.45">
       <c r="J37" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K37" s="53">
         <v>33</v>
@@ -16373,13 +16901,13 @@
         <v>353</v>
       </c>
       <c r="N2" s="58" t="s">
+        <v>482</v>
+      </c>
+      <c r="O2" s="58" t="s">
         <v>483</v>
       </c>
-      <c r="O2" s="58" t="s">
+      <c r="P2" s="58" t="s">
         <v>484</v>
-      </c>
-      <c r="P2" s="58" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="3" spans="13:19" x14ac:dyDescent="0.45">
@@ -16546,7 +17074,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="G2:T24"/>
+  <dimension ref="G2:T25"/>
   <sheetFormatPr defaultColWidth="10.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="5" width="12.59765625" customWidth="1"/>
@@ -16557,7 +17085,8 @@
     <col min="10" max="15" width="12.59765625" customWidth="1"/>
     <col min="16" max="16" width="12.46484375" customWidth="1"/>
     <col min="17" max="17" width="2.59765625" customWidth="1"/>
-    <col min="18" max="19" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.53125" bestFit="1" customWidth="1"/>
     <col min="20" max="21" width="5.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16566,16 +17095,16 @@
         <v>340</v>
       </c>
       <c r="H2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>340</v>
+        <v>492</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="T2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="7:20" x14ac:dyDescent="0.45">
@@ -16589,10 +17118,10 @@
         <v>1</v>
       </c>
       <c r="S3" s="55">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="T3" s="53">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="7:20" x14ac:dyDescent="0.45">
@@ -16603,10 +17132,10 @@
         <v>7</v>
       </c>
       <c r="S4" s="55">
+        <v>13</v>
+      </c>
+      <c r="T4" s="53">
         <v>2</v>
-      </c>
-      <c r="T4" s="53">
-        <v>3</v>
       </c>
     </row>
     <row r="5" spans="7:20" x14ac:dyDescent="0.45">
@@ -16617,10 +17146,10 @@
         <v>6</v>
       </c>
       <c r="S5" s="55">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T5" s="53">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="7:20" x14ac:dyDescent="0.45">
@@ -16631,7 +17160,7 @@
         <v>2</v>
       </c>
       <c r="S6" s="55">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T6" s="53">
         <v>1</v>
@@ -16644,11 +17173,14 @@
       <c r="H7" s="53">
         <v>2</v>
       </c>
+      <c r="R7" s="55">
+        <v>2</v>
+      </c>
       <c r="S7" s="55">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T7" s="53">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="7:20" x14ac:dyDescent="0.45">
@@ -16659,10 +17191,10 @@
         <v>1</v>
       </c>
       <c r="S8" s="55">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="T8" s="53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="7:20" x14ac:dyDescent="0.45">
@@ -16673,7 +17205,7 @@
         <v>2</v>
       </c>
       <c r="S9" s="55">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="T9" s="53">
         <v>1</v>
@@ -16687,10 +17219,10 @@
         <v>1</v>
       </c>
       <c r="S10" s="55">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T10" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="7:20" x14ac:dyDescent="0.45">
@@ -16700,11 +17232,14 @@
       <c r="H11" s="53">
         <v>2</v>
       </c>
+      <c r="R11" s="55">
+        <v>3</v>
+      </c>
       <c r="S11" s="55">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T11" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="7:20" x14ac:dyDescent="0.45">
@@ -16715,10 +17250,10 @@
         <v>2</v>
       </c>
       <c r="S12" s="55">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="T12" s="53">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="7:20" x14ac:dyDescent="0.45">
@@ -16728,41 +17263,44 @@
       <c r="H13" s="53">
         <v>1</v>
       </c>
-      <c r="R13" s="55">
+      <c r="S13" s="55">
+        <v>23</v>
+      </c>
+      <c r="T13" s="53">
         <v>2</v>
-      </c>
-      <c r="S13" s="55">
-        <v>2</v>
-      </c>
-      <c r="T13" s="53">
-        <v>4</v>
       </c>
     </row>
     <row r="14" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G14" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H14" s="53">
         <v>33</v>
       </c>
+      <c r="R14" s="55">
+        <v>4</v>
+      </c>
       <c r="S14" s="55">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T14" s="53">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="7:20" x14ac:dyDescent="0.45">
       <c r="S15" s="55">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="T15" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="7:20" x14ac:dyDescent="0.45">
+      <c r="R16" s="55">
+        <v>5</v>
+      </c>
       <c r="S16" s="55">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T16" s="53">
         <v>1</v>
@@ -16770,7 +17308,7 @@
     </row>
     <row r="17" spans="7:20" x14ac:dyDescent="0.45">
       <c r="S17" s="55">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="T17" s="53">
         <v>1</v>
@@ -16778,10 +17316,10 @@
     </row>
     <row r="18" spans="7:20" x14ac:dyDescent="0.45">
       <c r="R18" s="55">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S18" s="55">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T18" s="53">
         <v>1</v>
@@ -16789,16 +17327,19 @@
     </row>
     <row r="19" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G19" s="56" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H19" t="s">
-        <v>482</v>
-      </c>
-      <c r="R19" s="55" t="s">
-        <v>433</v>
+        <v>481</v>
+      </c>
+      <c r="R19" s="55">
+        <v>8</v>
+      </c>
+      <c r="S19" s="55">
+        <v>14</v>
       </c>
       <c r="T19" s="53">
-        <v>33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="7:20" x14ac:dyDescent="0.45">
@@ -16808,6 +17349,12 @@
       <c r="H20" s="53">
         <v>27</v>
       </c>
+      <c r="S20" s="55">
+        <v>23</v>
+      </c>
+      <c r="T20" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G21" s="57">
@@ -16816,6 +17363,15 @@
       <c r="H21" s="53">
         <v>4</v>
       </c>
+      <c r="R21" s="55">
+        <v>9</v>
+      </c>
+      <c r="S21" s="55">
+        <v>29</v>
+      </c>
+      <c r="T21" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G22" s="57">
@@ -16824,6 +17380,15 @@
       <c r="H22" s="53">
         <v>1</v>
       </c>
+      <c r="R22" s="55">
+        <v>10</v>
+      </c>
+      <c r="S22" s="55">
+        <v>12</v>
+      </c>
+      <c r="T22" s="53">
+        <v>2</v>
+      </c>
     </row>
     <row r="23" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G23" s="57">
@@ -16832,12 +17397,38 @@
       <c r="H23" s="53">
         <v>1</v>
       </c>
+      <c r="R23" s="55">
+        <v>15</v>
+      </c>
+      <c r="S23" s="55">
+        <v>12</v>
+      </c>
+      <c r="T23" s="53">
+        <v>2</v>
+      </c>
     </row>
     <row r="24" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G24" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H24" s="53">
+        <v>33</v>
+      </c>
+      <c r="R24" s="55">
+        <v>22</v>
+      </c>
+      <c r="S24" s="55">
+        <v>12</v>
+      </c>
+      <c r="T24" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="7:20" x14ac:dyDescent="0.45">
+      <c r="R25" s="55" t="s">
+        <v>432</v>
+      </c>
+      <c r="T25" s="53">
         <v>33</v>
       </c>
     </row>
@@ -16865,16 +17456,16 @@
   <sheetData>
     <row r="2" spans="17:22" x14ac:dyDescent="0.45">
       <c r="Q2" s="56" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="S2" s="56" t="s">
         <v>67</v>
       </c>
       <c r="T2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
@@ -16888,230 +17479,456 @@
       </c>
     </row>
     <row r="4" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="Q4" s="55" t="s">
-        <v>28</v>
+      <c r="R4" s="55" t="s">
+        <v>34</v>
       </c>
       <c r="T4" s="53">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="Q5" s="55" t="s">
-        <v>29</v>
+      <c r="S5" s="55" t="s">
+        <v>514</v>
       </c>
       <c r="T5" s="53">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="17:22" x14ac:dyDescent="0.45">
       <c r="Q6" s="55" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="T6" s="53">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="Q7" s="55" t="s">
-        <v>31</v>
+      <c r="R7" s="55" t="s">
+        <v>28</v>
       </c>
       <c r="T7" s="53">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="Q8" s="55" t="s">
-        <v>33</v>
+      <c r="S8" s="55" t="s">
+        <v>187</v>
       </c>
       <c r="T8" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="Q9" s="55" t="s">
-        <v>433</v>
+      <c r="S9" s="55" t="s">
+        <v>12</v>
       </c>
       <c r="T9" s="53">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="10"/>
     </row>
     <row r="10" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S10" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="T10" s="53">
+        <v>1</v>
+      </c>
       <c r="U10" s="3"/>
       <c r="V10" s="13"/>
     </row>
     <row r="11" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S11" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="T11" s="53">
+        <v>1</v>
+      </c>
       <c r="U11" s="3"/>
       <c r="V11" s="13"/>
     </row>
     <row r="12" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S12" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="T12" s="53">
+        <v>1</v>
+      </c>
       <c r="U12" s="3"/>
       <c r="V12" s="13"/>
     </row>
     <row r="13" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S13" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="T13" s="53">
+        <v>3</v>
+      </c>
       <c r="U13" s="3"/>
       <c r="V13" s="13"/>
     </row>
     <row r="14" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S14" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="T14" s="53">
+        <v>3</v>
+      </c>
       <c r="U14" s="3"/>
       <c r="V14" s="13"/>
     </row>
     <row r="15" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S15" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="T15" s="53">
+        <v>1</v>
+      </c>
       <c r="U15" s="3"/>
       <c r="V15" s="13"/>
     </row>
     <row r="16" spans="17:22" x14ac:dyDescent="0.45">
+      <c r="S16" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="T16" s="53">
+        <v>1</v>
+      </c>
       <c r="U16" s="9"/>
       <c r="V16" s="13"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S17" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="53">
+        <v>1</v>
+      </c>
       <c r="U17" s="13"/>
       <c r="V17" s="13"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="Q18" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T18" s="53">
+        <v>10</v>
+      </c>
       <c r="U18" s="3"/>
       <c r="V18" s="13"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="R19" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="T19" s="53">
+        <v>2</v>
+      </c>
       <c r="U19" s="3"/>
       <c r="V19" s="13"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S20" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="T20" s="53">
+        <v>1</v>
+      </c>
       <c r="U20" s="3"/>
       <c r="V20" s="13"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S21" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="T21" s="53">
+        <v>1</v>
+      </c>
       <c r="U21" s="3"/>
       <c r="V21" s="13"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="R22" s="55" t="s">
+        <v>466</v>
+      </c>
+      <c r="T22" s="53">
+        <v>6</v>
+      </c>
       <c r="U22" s="3"/>
       <c r="V22" s="13"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S23" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="T23" s="53">
+        <v>2</v>
+      </c>
       <c r="U23" s="3"/>
       <c r="V23" s="13"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S24" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="T24" s="53">
+        <v>1</v>
+      </c>
       <c r="U24" s="3"/>
       <c r="V24" s="13"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S25" s="55" t="s">
+        <v>404</v>
+      </c>
+      <c r="T25" s="53">
+        <v>1</v>
+      </c>
       <c r="U25" s="3"/>
       <c r="V25" s="13"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S26" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="T26" s="53">
+        <v>1</v>
+      </c>
       <c r="U26" s="3"/>
       <c r="V26" s="13"/>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S27" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="T27" s="53">
+        <v>1</v>
+      </c>
       <c r="U27" s="3"/>
       <c r="V27" s="13"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="R28" s="55" t="s">
+        <v>467</v>
+      </c>
+      <c r="T28" s="53">
+        <v>2</v>
+      </c>
       <c r="U28" s="10"/>
       <c r="V28" s="13"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="S29" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="T29" s="53">
+        <v>1</v>
+      </c>
       <c r="U29" s="3"/>
       <c r="V29" s="13"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A30" s="3"/>
       <c r="G30" s="3"/>
+      <c r="S30" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="T30" s="53">
+        <v>1</v>
+      </c>
       <c r="U30" s="3"/>
       <c r="V30" s="13"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A31" s="3"/>
       <c r="G31" s="3"/>
+      <c r="Q31" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="T31" s="53">
+        <v>3</v>
+      </c>
       <c r="U31" s="3"/>
       <c r="V31" s="13"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A32" s="3"/>
       <c r="G32" s="3"/>
+      <c r="R32" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="T32" s="53">
+        <v>1</v>
+      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="13"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" s="3"/>
       <c r="G33" s="3"/>
+      <c r="S33" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="T33" s="53">
+        <v>1</v>
+      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="13"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A34" s="3"/>
       <c r="G34" s="3"/>
+      <c r="R34" s="55" t="s">
+        <v>485</v>
+      </c>
+      <c r="T34" s="53">
+        <v>1</v>
+      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="13"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A35" s="3"/>
       <c r="G35" s="3"/>
+      <c r="S35" s="55" t="s">
+        <v>417</v>
+      </c>
+      <c r="T35" s="53">
+        <v>1</v>
+      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="13"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A36" s="3"/>
       <c r="G36" s="3"/>
+      <c r="R36" s="55" t="s">
+        <v>468</v>
+      </c>
+      <c r="T36" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A37" s="3"/>
       <c r="G37" s="14"/>
+      <c r="S37" s="55" t="s">
+        <v>411</v>
+      </c>
+      <c r="T37" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="3"/>
       <c r="F38"/>
       <c r="G38" s="14"/>
-      <c r="Q38"/>
+      <c r="Q38" s="55" t="s">
+        <v>31</v>
+      </c>
       <c r="R38"/>
       <c r="S38"/>
-      <c r="T38"/>
+      <c r="T38" s="53">
+        <v>4</v>
+      </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A39" s="3"/>
       <c r="G39" s="3"/>
+      <c r="R39" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="T39" s="53">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A40" s="3"/>
       <c r="G40" s="3"/>
+      <c r="S40" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="T40" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A41" s="3"/>
       <c r="F41" s="14"/>
       <c r="G41" s="3"/>
+      <c r="S41" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="T41" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A42" s="3"/>
       <c r="F42" s="14"/>
       <c r="G42" s="3"/>
+      <c r="S42" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="T42" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A43" s="3"/>
       <c r="F43" s="14"/>
       <c r="G43" s="3"/>
+      <c r="S43" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="T43" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A44" s="3"/>
       <c r="F44" s="14"/>
       <c r="G44" s="3"/>
+      <c r="Q44" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="T44" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A45" s="3"/>
       <c r="F45" s="14"/>
       <c r="G45" s="3"/>
+      <c r="R45" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="T45" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A46" s="3"/>
       <c r="F46" s="14"/>
       <c r="G46" s="3"/>
+      <c r="S46" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="T46" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A47" s="3"/>
       <c r="F47" s="14"/>
       <c r="G47" s="3"/>
+      <c r="Q47" s="55" t="s">
+        <v>432</v>
+      </c>
+      <c r="T47" s="53">
+        <v>33</v>
+      </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A48" s="3"/>
@@ -17249,10 +18066,10 @@
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B15" s="56" t="s">
+        <v>480</v>
+      </c>
+      <c r="C15" t="s">
         <v>481</v>
-      </c>
-      <c r="C15" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.45">
@@ -17289,7 +18106,7 @@
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B20" s="57" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C20" s="53">
         <v>33</v>
@@ -17347,22 +18164,22 @@
         <v>215</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D1" s="46" t="s">
+        <v>490</v>
+      </c>
+      <c r="E1" s="46" t="s">
+        <v>489</v>
+      </c>
+      <c r="F1" s="52" t="s">
+        <v>488</v>
+      </c>
+      <c r="G1" s="46" t="s">
         <v>491</v>
       </c>
-      <c r="E1" s="46" t="s">
-        <v>490</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>489</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>492</v>
-      </c>
       <c r="H1" s="46" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I1" s="52" t="s">
         <v>340</v>
@@ -17374,13 +18191,13 @@
         <v>117</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>67</v>
@@ -17416,7 +18233,7 @@
         <v>26</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>115</v>
@@ -17451,11 +18268,11 @@
         <v>15</v>
       </c>
       <c r="E2" s="3">
-        <f>COUNTIF(Retro!$I2,Retro!$M2)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F2" s="55">
-        <f>COUNTIF(Retro!$I2,"&lt;&gt;"&amp;Retro!$M2)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G2" s="55">
@@ -17553,11 +18370,11 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <f>COUNTIF(Retro!$I3,Retro!$M3)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F3">
-        <f>COUNTIF(Retro!$I3,"&lt;&gt;"&amp;Retro!$M3)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G3" s="55">
@@ -17655,11 +18472,11 @@
         <v>25</v>
       </c>
       <c r="E4" s="3">
-        <f>COUNTIF(Retro!$I4,Retro!$M4)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F4" s="55">
-        <f>COUNTIF(Retro!$I4,"&lt;&gt;"&amp;Retro!$M4)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G4" s="55">
@@ -17698,13 +18515,13 @@
         <v>12</v>
       </c>
       <c r="R4" s="55" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="S4" s="55" t="s">
         <v>96</v>
       </c>
       <c r="T4" s="55" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U4" s="55"/>
       <c r="V4" s="55">
@@ -17754,14 +18571,14 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>356</v>
+        <v>72</v>
       </c>
       <c r="E5">
-        <f>COUNTIF(Retro!$I5,Retro!$M5)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
+        <v>0</v>
       </c>
       <c r="F5">
-        <f>COUNTIF(Retro!$I5,"&lt;&gt;"&amp;Retro!$M5)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G5">
@@ -17797,7 +18614,7 @@
         <v>74</v>
       </c>
       <c r="Q5" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="R5" t="s">
         <v>94</v>
@@ -17806,7 +18623,7 @@
         <v>99</v>
       </c>
       <c r="T5" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="U5"/>
       <c r="V5">
@@ -17859,11 +18676,11 @@
         <v>49</v>
       </c>
       <c r="E6">
-        <f>COUNTIF(Retro!$I6,Retro!$M6)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F6">
-        <f>COUNTIF(Retro!$I6,"&lt;&gt;"&amp;Retro!$M6)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G6">
@@ -17961,11 +18778,11 @@
         <v>354</v>
       </c>
       <c r="E7">
-        <f>COUNTIF(Retro!$I7,Retro!$M7)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F7">
-        <f>COUNTIF(Retro!$I7,"&lt;&gt;"&amp;Retro!$M7)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G7" s="55">
@@ -18010,7 +18827,7 @@
         <v>91</v>
       </c>
       <c r="T7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U7"/>
       <c r="V7">
@@ -18063,11 +18880,11 @@
         <v>36</v>
       </c>
       <c r="E8">
-        <f>COUNTIF(Retro!$I8,Retro!$M8)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F8">
-        <f>COUNTIF(Retro!$I8,"&lt;&gt;"&amp;Retro!$M8)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G8" s="55">
@@ -18103,16 +18920,16 @@
         <v>97</v>
       </c>
       <c r="Q8" t="s">
+        <v>427</v>
+      </c>
+      <c r="R8" t="s">
         <v>428</v>
       </c>
-      <c r="R8" t="s">
+      <c r="S8" t="s">
         <v>429</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>430</v>
-      </c>
-      <c r="T8" t="s">
-        <v>431</v>
       </c>
       <c r="U8"/>
       <c r="V8">
@@ -18146,7 +18963,7 @@
         <v>157</v>
       </c>
       <c r="AF8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -18165,11 +18982,11 @@
         <v>78</v>
       </c>
       <c r="E9">
-        <f>COUNTIF(Retro!$I9,Retro!$M9)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F9">
-        <f>COUNTIF(Retro!$I9,"&lt;&gt;"&amp;Retro!$M9)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G9">
@@ -18267,11 +19084,11 @@
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <f>COUNTIF(Retro!$I10,Retro!$M10)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F10" s="55">
-        <f>COUNTIF(Retro!$I10,"&lt;&gt;"&amp;Retro!$M10)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G10" s="55">
@@ -18301,7 +19118,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="P10" s="55" t="s">
         <v>25</v>
@@ -18313,10 +19130,10 @@
         <v>166</v>
       </c>
       <c r="S10" s="55" t="s">
+        <v>385</v>
+      </c>
+      <c r="T10" s="55" t="s">
         <v>386</v>
-      </c>
-      <c r="T10" s="55" t="s">
-        <v>387</v>
       </c>
       <c r="U10" s="55"/>
       <c r="V10" s="55">
@@ -18366,15 +19183,15 @@
         <v>11</v>
       </c>
       <c r="D11" t="s">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="E11">
-        <f>COUNTIF(Retro!$I11,Retro!$M11)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F11">
-        <f>COUNTIF(Retro!$I11,"&lt;&gt;"&amp;Retro!$M11)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G11" s="55">
         <v>1</v>
@@ -18468,15 +19285,15 @@
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>472</v>
       </c>
       <c r="E12">
-        <f>COUNTIF(Retro!$I12,Retro!$M12)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F12">
-        <f>COUNTIF(Retro!$I12,"&lt;&gt;"&amp;Retro!$M12)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G12" s="55">
         <v>1</v>
@@ -18573,11 +19390,11 @@
         <v>355</v>
       </c>
       <c r="E13">
-        <f>COUNTIF(Retro!$I13,Retro!$M13)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
+        <v>0</v>
       </c>
       <c r="F13">
-        <f>COUNTIF(Retro!$I13,"&lt;&gt;"&amp;Retro!$M13)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G13">
@@ -18619,10 +19436,10 @@
         <v>189</v>
       </c>
       <c r="S13" t="s">
+        <v>392</v>
+      </c>
+      <c r="T13" t="s">
         <v>393</v>
-      </c>
-      <c r="T13" t="s">
-        <v>394</v>
       </c>
       <c r="U13"/>
       <c r="V13">
@@ -18672,14 +19489,14 @@
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E14">
-        <f>COUNTIF(Retro!$I14,Retro!$M14)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F14">
-        <f>COUNTIF(Retro!$I14,"&lt;&gt;"&amp;Retro!$M14)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G14">
@@ -18712,7 +19529,7 @@
         <v>57</v>
       </c>
       <c r="P14" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="Q14" t="s">
         <v>51</v>
@@ -18724,7 +19541,7 @@
         <v>16</v>
       </c>
       <c r="T14" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="U14"/>
       <c r="V14">
@@ -18777,11 +19594,11 @@
         <v>47</v>
       </c>
       <c r="E15">
-        <f>COUNTIF(Retro!$I15,Retro!$M15)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
+        <v>0</v>
       </c>
       <c r="F15">
-        <f>COUNTIF(Retro!$I15,"&lt;&gt;"&amp;Retro!$M15)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G15">
@@ -18820,13 +19637,13 @@
         <v>203</v>
       </c>
       <c r="R15" t="s">
+        <v>387</v>
+      </c>
+      <c r="S15" t="s">
         <v>388</v>
       </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
         <v>389</v>
-      </c>
-      <c r="T15" t="s">
-        <v>390</v>
       </c>
       <c r="U15"/>
       <c r="V15">
@@ -18879,12 +19696,12 @@
         <v>66</v>
       </c>
       <c r="E16">
-        <f>COUNTIF(Retro!$I16,Retro!$M16)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F16">
-        <f>COUNTIF(Retro!$I16,"&lt;&gt;"&amp;Retro!$M16)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -18919,16 +19736,16 @@
         <v>19</v>
       </c>
       <c r="Q16" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="R16" t="s">
         <v>89</v>
       </c>
       <c r="S16" t="s">
+        <v>400</v>
+      </c>
+      <c r="T16" t="s">
         <v>401</v>
-      </c>
-      <c r="T16" t="s">
-        <v>402</v>
       </c>
       <c r="U16"/>
       <c r="V16">
@@ -18953,16 +19770,16 @@
         <v>212</v>
       </c>
       <c r="AC16" t="s">
+        <v>397</v>
+      </c>
+      <c r="AD16" t="s">
         <v>398</v>
-      </c>
-      <c r="AD16" t="s">
-        <v>399</v>
       </c>
       <c r="AE16" t="s">
         <v>213</v>
       </c>
       <c r="AF16" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
@@ -18981,11 +19798,11 @@
         <v>25</v>
       </c>
       <c r="E17">
-        <f>COUNTIF(Retro!$I17,Retro!$M17)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F17">
-        <f>COUNTIF(Retro!$I17,"&lt;&gt;"&amp;Retro!$M17)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G17">
@@ -19021,7 +19838,7 @@
         <v>25</v>
       </c>
       <c r="Q17" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="R17" t="s">
         <v>217</v>
@@ -19030,7 +19847,7 @@
         <v>218</v>
       </c>
       <c r="T17" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="U17"/>
       <c r="V17">
@@ -19083,11 +19900,11 @@
         <v>45</v>
       </c>
       <c r="E18">
-        <f>COUNTIF(Retro!$I18,Retro!$M18)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F18">
-        <f>COUNTIF(Retro!$I18,"&lt;&gt;"&amp;Retro!$M18)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G18">
@@ -19132,7 +19949,7 @@
         <v>174</v>
       </c>
       <c r="T18" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="U18"/>
       <c r="V18">
@@ -19185,11 +20002,11 @@
         <v>43</v>
       </c>
       <c r="E19">
-        <f>COUNTIF(Retro!$I19,Retro!$M19)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F19">
-        <f>COUNTIF(Retro!$I19,"&lt;&gt;"&amp;Retro!$M19)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G19">
@@ -19228,13 +20045,13 @@
         <v>235</v>
       </c>
       <c r="R19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="S19" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="T19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="U19"/>
       <c r="V19">
@@ -19268,7 +20085,7 @@
         <v>240</v>
       </c>
       <c r="AF19" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
@@ -19287,12 +20104,12 @@
         <v>37</v>
       </c>
       <c r="E20">
-        <f>COUNTIF(Retro!$I20,Retro!$M20)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F20">
-        <f>COUNTIF(Retro!$I20,"&lt;&gt;"&amp;Retro!$M20)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -19389,11 +20206,11 @@
         <v>25</v>
       </c>
       <c r="E21" s="55">
-        <f>COUNTIF(Retro!$I21,Retro!$M21)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F21" s="55">
-        <f>COUNTIF(Retro!$I21,"&lt;&gt;"&amp;Retro!$M21)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G21" s="55">
@@ -19435,10 +20252,10 @@
         <v>41</v>
       </c>
       <c r="S21" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="T21" s="55" t="s">
         <v>403</v>
-      </c>
-      <c r="T21" s="55" t="s">
-        <v>404</v>
       </c>
       <c r="U21" s="55"/>
       <c r="V21" s="55">
@@ -19491,11 +20308,11 @@
         <v>49</v>
       </c>
       <c r="E22">
-        <f>COUNTIF(Retro!$I22,Retro!$M22)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F22">
-        <f>COUNTIF(Retro!$I22,"&lt;&gt;"&amp;Retro!$M22)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G22">
@@ -19525,7 +20342,7 @@
         <v>35</v>
       </c>
       <c r="O22" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P22" t="s">
         <v>49</v>
@@ -19540,7 +20357,7 @@
         <v>77</v>
       </c>
       <c r="T22" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="U22"/>
       <c r="V22">
@@ -19593,11 +20410,11 @@
         <v>47</v>
       </c>
       <c r="E23" s="3">
-        <f>COUNTIF(Retro!$I23,Retro!$M23)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F23" s="55">
-        <f>COUNTIF(Retro!$I23,"&lt;&gt;"&amp;Retro!$M23)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G23" s="61">
@@ -19627,7 +20444,7 @@
         <v>22</v>
       </c>
       <c r="O23" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="P23" s="55" t="s">
         <v>47</v>
@@ -19639,7 +20456,7 @@
         <v>48</v>
       </c>
       <c r="S23" s="55" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="T23" s="55" t="s">
         <v>101</v>
@@ -19695,12 +20512,12 @@
         <v>71</v>
       </c>
       <c r="E24" s="3">
-        <f>COUNTIF(Retro!$I24,Retro!$M24)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F24" s="55">
-        <f>COUNTIF(Retro!$I24,"&lt;&gt;"&amp;Retro!$M24)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G24" s="61">
         <v>2</v>
@@ -19738,7 +20555,7 @@
         <v>225</v>
       </c>
       <c r="R24" s="55" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="S24" s="55" t="s">
         <v>90</v>
@@ -19797,11 +20614,11 @@
         <v>354</v>
       </c>
       <c r="E25">
-        <f>COUNTIF(Retro!$I25,Retro!$M25)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F25">
-        <f>COUNTIF(Retro!$I25,"&lt;&gt;"&amp;Retro!$M25)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G25">
@@ -19831,7 +20648,7 @@
         <v>14</v>
       </c>
       <c r="O25" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="P25" t="s">
         <v>354</v>
@@ -19843,10 +20660,10 @@
         <v>22</v>
       </c>
       <c r="S25" t="s">
+        <v>408</v>
+      </c>
+      <c r="T25" t="s">
         <v>409</v>
-      </c>
-      <c r="T25" t="s">
-        <v>410</v>
       </c>
       <c r="U25"/>
       <c r="V25">
@@ -19899,11 +20716,11 @@
         <v>18</v>
       </c>
       <c r="E26">
-        <f>COUNTIF(Retro!$I26,Retro!$M26)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F26">
-        <f>COUNTIF(Retro!$I26,"&lt;&gt;"&amp;Retro!$M26)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G26">
@@ -19939,16 +20756,16 @@
         <v>37</v>
       </c>
       <c r="Q26" t="s">
+        <v>413</v>
+      </c>
+      <c r="R26" t="s">
         <v>414</v>
       </c>
-      <c r="R26" t="s">
+      <c r="S26" t="s">
         <v>415</v>
       </c>
-      <c r="S26" t="s">
+      <c r="T26" t="s">
         <v>416</v>
-      </c>
-      <c r="T26" t="s">
-        <v>417</v>
       </c>
       <c r="U26"/>
       <c r="V26">
@@ -20001,11 +20818,11 @@
         <v>355</v>
       </c>
       <c r="E27">
-        <f>COUNTIF(Retro!$I27,Retro!$M27)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F27">
-        <f>COUNTIF(Retro!$I27,"&lt;&gt;"&amp;Retro!$M27)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G27">
@@ -20041,7 +20858,7 @@
         <v>38</v>
       </c>
       <c r="Q27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="R27" t="s">
         <v>189</v>
@@ -20050,7 +20867,7 @@
         <v>40</v>
       </c>
       <c r="T27" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="U27"/>
       <c r="V27">
@@ -20103,11 +20920,11 @@
         <v>72</v>
       </c>
       <c r="E28">
-        <f>COUNTIF(Retro!$I28,Retro!$M28)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
+        <v>0</v>
       </c>
       <c r="F28">
-        <f>COUNTIF(Retro!$I28,"&lt;&gt;"&amp;Retro!$M28)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G28">
@@ -20140,7 +20957,7 @@
         <v>78</v>
       </c>
       <c r="P28" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q28" t="s">
         <v>75</v>
@@ -20205,12 +21022,12 @@
         <v>84</v>
       </c>
       <c r="E29">
-        <f>COUNTIF(Retro!$I29,Retro!$M29)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F29">
-        <f>COUNTIF(Retro!$I29,"&lt;&gt;"&amp;Retro!$M29)</f>
-        <v>1</v>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -20239,7 +21056,7 @@
         <v>24</v>
       </c>
       <c r="O29" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P29" t="s">
         <v>85</v>
@@ -20248,10 +21065,10 @@
         <v>58</v>
       </c>
       <c r="R29" t="s">
+        <v>418</v>
+      </c>
+      <c r="S29" t="s">
         <v>419</v>
-      </c>
-      <c r="S29" t="s">
-        <v>420</v>
       </c>
       <c r="T29" t="s">
         <v>64</v>
@@ -20273,22 +21090,22 @@
         <v>142.86000000000001</v>
       </c>
       <c r="AA29" t="s">
+        <v>371</v>
+      </c>
+      <c r="AB29" t="s">
         <v>372</v>
       </c>
-      <c r="AB29" t="s">
+      <c r="AC29" t="s">
+        <v>374</v>
+      </c>
+      <c r="AD29" t="s">
         <v>373</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AE29" t="s">
+        <v>377</v>
+      </c>
+      <c r="AF29" t="s">
         <v>375</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>374</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>378</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>376</v>
       </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
@@ -20307,11 +21124,11 @@
         <v>13</v>
       </c>
       <c r="E30">
-        <f>COUNTIF(Retro!$I30,Retro!$M30)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F30">
-        <f>COUNTIF(Retro!$I30,"&lt;&gt;"&amp;Retro!$M30)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G30">
@@ -20350,13 +21167,13 @@
         <v>100</v>
       </c>
       <c r="R30" t="s">
+        <v>421</v>
+      </c>
+      <c r="S30" t="s">
         <v>422</v>
       </c>
-      <c r="S30" t="s">
+      <c r="T30" t="s">
         <v>423</v>
-      </c>
-      <c r="T30" t="s">
-        <v>424</v>
       </c>
       <c r="U30"/>
       <c r="V30">
@@ -20375,22 +21192,22 @@
         <v>116.24</v>
       </c>
       <c r="AA30" t="s">
+        <v>361</v>
+      </c>
+      <c r="AB30" t="s">
         <v>362</v>
       </c>
-      <c r="AB30" t="s">
+      <c r="AC30" t="s">
+        <v>365</v>
+      </c>
+      <c r="AD30" t="s">
         <v>363</v>
       </c>
-      <c r="AC30" t="s">
+      <c r="AE30" t="s">
+        <v>364</v>
+      </c>
+      <c r="AF30" t="s">
         <v>366</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>364</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>365</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>367</v>
       </c>
       <c r="AG30" s="3"/>
       <c r="AH30" s="3"/>
@@ -20409,11 +21226,11 @@
         <v>12</v>
       </c>
       <c r="E31">
-        <f>COUNTIF(Retro!$I31,Retro!$M31)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>1</v>
       </c>
       <c r="F31">
-        <f>COUNTIF(Retro!$I31,"&lt;&gt;"&amp;Retro!$M31)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>0</v>
       </c>
       <c r="G31">
@@ -20446,7 +21263,7 @@
         <v>12</v>
       </c>
       <c r="P31" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Q31" t="s">
         <v>166</v>
@@ -20458,7 +21275,7 @@
         <v>53</v>
       </c>
       <c r="T31" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="U31"/>
       <c r="V31">
@@ -20477,22 +21294,22 @@
         <v>105.04</v>
       </c>
       <c r="AA31" t="s">
+        <v>473</v>
+      </c>
+      <c r="AB31" t="s">
         <v>474</v>
       </c>
-      <c r="AB31" t="s">
+      <c r="AC31" t="s">
         <v>475</v>
       </c>
-      <c r="AC31" t="s">
+      <c r="AD31" t="s">
         <v>476</v>
       </c>
-      <c r="AD31" t="s">
+      <c r="AE31" t="s">
         <v>477</v>
       </c>
-      <c r="AE31" t="s">
+      <c r="AF31" t="s">
         <v>478</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>479</v>
       </c>
       <c r="AG31" s="3"/>
       <c r="AH31" s="3"/>
@@ -20511,11 +21328,11 @@
         <v>355</v>
       </c>
       <c r="E32">
-        <f>COUNTIF(Retro!$I32,Retro!$M32)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F32">
-        <f>COUNTIF(Retro!$I32,"&lt;&gt;"&amp;Retro!$M32)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G32">
@@ -20551,16 +21368,16 @@
         <v>355</v>
       </c>
       <c r="Q32" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R32" t="s">
         <v>49</v>
       </c>
       <c r="S32" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="T32" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="U32"/>
       <c r="V32">
@@ -20579,22 +21396,22 @@
         <v>127.82</v>
       </c>
       <c r="AA32" t="s">
+        <v>497</v>
+      </c>
+      <c r="AB32" t="s">
         <v>498</v>
       </c>
-      <c r="AB32" t="s">
+      <c r="AC32" t="s">
         <v>499</v>
       </c>
-      <c r="AC32" t="s">
+      <c r="AD32" t="s">
         <v>500</v>
       </c>
-      <c r="AD32" t="s">
+      <c r="AE32" t="s">
         <v>501</v>
       </c>
-      <c r="AE32" t="s">
+      <c r="AF32" t="s">
         <v>502</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.45">
@@ -20611,11 +21428,11 @@
         <v>57</v>
       </c>
       <c r="E33">
-        <f>COUNTIF(Retro!$I33,Retro!$M33)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F33">
-        <f>COUNTIF(Retro!$I33,"&lt;&gt;"&amp;Retro!$M33)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G33">
@@ -20654,13 +21471,13 @@
         <v>187</v>
       </c>
       <c r="R33" s="55" t="s">
+        <v>506</v>
+      </c>
+      <c r="S33" s="55" t="s">
         <v>507</v>
       </c>
-      <c r="S33" s="55" t="s">
-        <v>508</v>
-      </c>
       <c r="T33" s="55" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="U33" s="55"/>
       <c r="V33" s="55">
@@ -20679,22 +21496,22 @@
         <v>111.89</v>
       </c>
       <c r="AA33" s="55" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AB33" s="55" t="s">
+        <v>509</v>
+      </c>
+      <c r="AC33" s="55" t="s">
+        <v>508</v>
+      </c>
+      <c r="AD33" s="55" t="s">
+        <v>511</v>
+      </c>
+      <c r="AE33" s="55" t="s">
+        <v>512</v>
+      </c>
+      <c r="AF33" s="55" t="s">
         <v>510</v>
-      </c>
-      <c r="AC33" s="55" t="s">
-        <v>509</v>
-      </c>
-      <c r="AD33" s="55" t="s">
-        <v>512</v>
-      </c>
-      <c r="AE33" s="55" t="s">
-        <v>513</v>
-      </c>
-      <c r="AF33" s="55" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.45">
@@ -20711,11 +21528,11 @@
         <v>63</v>
       </c>
       <c r="E34" s="3">
-        <f>COUNTIF(Retro!$I34,Retro!$M34)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</f>
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <f>COUNTIF(Retro!$I34,"&lt;&gt;"&amp;Retro!$M34)</f>
+        <f>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</f>
         <v>1</v>
       </c>
       <c r="G34" s="55">
@@ -20745,22 +21562,22 @@
         <v>15</v>
       </c>
       <c r="O34" s="55" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P34" s="55" t="s">
         <v>63</v>
       </c>
       <c r="Q34" s="55" t="s">
+        <v>515</v>
+      </c>
+      <c r="R34" s="55" t="s">
         <v>516</v>
       </c>
-      <c r="R34" s="55" t="s">
+      <c r="S34" s="55" t="s">
         <v>517</v>
       </c>
-      <c r="S34" s="55" t="s">
+      <c r="T34" s="55" t="s">
         <v>518</v>
-      </c>
-      <c r="T34" s="55" t="s">
-        <v>519</v>
       </c>
       <c r="U34" s="55"/>
       <c r="V34" s="55">
@@ -20779,22 +21596,22 @@
         <v>72</v>
       </c>
       <c r="AA34" s="55" t="s">
+        <v>519</v>
+      </c>
+      <c r="AB34" s="55" t="s">
         <v>520</v>
       </c>
-      <c r="AB34" s="55" t="s">
+      <c r="AC34" s="55" t="s">
         <v>521</v>
       </c>
-      <c r="AC34" s="55" t="s">
+      <c r="AD34" s="55" t="s">
         <v>522</v>
       </c>
-      <c r="AD34" s="55" t="s">
+      <c r="AE34" s="55" t="s">
         <v>523</v>
       </c>
-      <c r="AE34" s="55" t="s">
+      <c r="AF34" s="55" t="s">
         <v>524</v>
-      </c>
-      <c r="AF34" s="55" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="35" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.45">
@@ -21497,55 +22314,55 @@
         <v>34</v>
       </c>
       <c r="C1" s="64" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D1" s="63" t="s">
         <v>35</v>
       </c>
       <c r="E1" s="64" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F1" s="63" t="s">
         <v>28</v>
       </c>
       <c r="G1" s="64" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1" s="64" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I1" s="63" t="s">
         <v>29</v>
       </c>
       <c r="J1" s="64" t="s">
+        <v>466</v>
+      </c>
+      <c r="K1" s="64" t="s">
         <v>467</v>
-      </c>
-      <c r="K1" s="64" t="s">
-        <v>468</v>
       </c>
       <c r="L1" s="63" t="s">
         <v>30</v>
       </c>
       <c r="M1" s="64" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="N1" s="63" t="s">
         <v>31</v>
       </c>
       <c r="O1" s="64" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P1" s="63" t="s">
         <v>32</v>
       </c>
       <c r="Q1" s="64" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="R1" s="63" t="s">
         <v>33</v>
       </c>
       <c r="S1" s="64" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="T1" s="65" t="s">
         <v>81</v>
@@ -21701,19 +22518,19 @@
         <v>36</v>
       </c>
       <c r="G8" s="69" t="s">
+        <v>379</v>
+      </c>
+      <c r="H8" s="69" t="s">
+        <v>382</v>
+      </c>
+      <c r="I8" s="69" t="s">
+        <v>378</v>
+      </c>
+      <c r="J8" s="69" t="s">
         <v>380</v>
       </c>
-      <c r="H8" s="69" t="s">
-        <v>383</v>
-      </c>
-      <c r="I8" s="69" t="s">
-        <v>379</v>
-      </c>
-      <c r="J8" s="69" t="s">
+      <c r="K8" s="69" t="s">
         <v>381</v>
-      </c>
-      <c r="K8" s="69" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.45">
@@ -22169,25 +22986,25 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A29" s="67" t="s">
+        <v>367</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>369</v>
+      </c>
+      <c r="F29" s="69" t="s">
         <v>368</v>
-      </c>
-      <c r="D29" s="69" t="s">
-        <v>370</v>
-      </c>
-      <c r="F29" s="69" t="s">
-        <v>369</v>
       </c>
       <c r="G29" s="69" t="s">
         <v>281</v>
       </c>
       <c r="I29" s="69" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L29" s="69" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="R29" s="69" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.45">
@@ -22198,19 +23015,19 @@
         <v>256</v>
       </c>
       <c r="I30" s="69" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J30" s="69" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="L30" s="69" t="s">
         <v>258</v>
       </c>
       <c r="N30" s="69" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P30" s="69" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.45">
@@ -22224,13 +23041,13 @@
         <v>12</v>
       </c>
       <c r="I31" s="69" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L31" s="69" t="s">
         <v>82</v>
       </c>
       <c r="M31" s="69" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="N31" s="67"/>
       <c r="P31" s="69" t="s">
@@ -22250,18 +23067,18 @@
         <v>49</v>
       </c>
       <c r="I32" s="55" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="N32" s="55" t="s">
         <v>355</v>
       </c>
       <c r="P32" s="55" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="R32" s="70"/>
       <c r="S32" s="70"/>
       <c r="T32" s="55" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.45">
@@ -22269,10 +23086,10 @@
         <v>187</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F33" s="55" t="s">
         <v>57</v>
@@ -22281,33 +23098,33 @@
         <v>187</v>
       </c>
       <c r="L33" s="55" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="R33" s="70"/>
       <c r="S33" s="70"/>
       <c r="T33" s="55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A34" s="52" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F34" s="55" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="55"/>
       <c r="P34" s="69" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="Q34" s="55" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="R34" s="70"/>
       <c r="S34" s="70"/>
@@ -22569,18 +23386,18 @@
     <sortCondition ref="I46:L46"/>
   </sortState>
   <conditionalFormatting sqref="A63">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text=":DEN">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text=":DEN">
       <formula>NOT(ISERROR(SEARCH(":DEN",A63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text=":CIN">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text=":CIN">
       <formula>NOT(ISERROR(SEARCH(":CIN",A63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63 I63 L63 N63 P63">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text=":DEN">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=":DEN">
       <formula>NOT(ISERROR(SEARCH(":DEN",F63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text=":CIN">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=":CIN">
       <formula>NOT(ISERROR(SEARCH(":CIN",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22612,16 +23429,16 @@
       <c r="L2" s="58"/>
       <c r="M2" s="51"/>
       <c r="O2" s="56" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="P2" s="56" t="s">
+        <v>486</v>
+      </c>
+      <c r="Q2" s="56" t="s">
         <v>487</v>
       </c>
-      <c r="Q2" s="56" t="s">
-        <v>488</v>
-      </c>
       <c r="R2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="3" spans="11:18" x14ac:dyDescent="0.45">
@@ -22742,7 +23559,7 @@
     </row>
     <row r="13" spans="11:18" x14ac:dyDescent="0.45">
       <c r="O13" s="55" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="P13" s="55" t="s">
         <v>29</v>
@@ -22764,7 +23581,7 @@
     </row>
     <row r="15" spans="11:18" x14ac:dyDescent="0.45">
       <c r="P15" s="55" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q15" s="55" t="s">
         <v>354</v>
@@ -22778,7 +23595,7 @@
       <c r="L16" s="55"/>
       <c r="M16" s="55"/>
       <c r="Q16" s="55" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="R16" s="53">
         <v>1</v>
@@ -22786,7 +23603,7 @@
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="Q17" s="55" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="R17" s="53">
         <v>1</v>
@@ -22802,7 +23619,7 @@
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.45">
       <c r="Q19" s="55" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="R19" s="53">
         <v>1</v>
@@ -22810,7 +23627,7 @@
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.45">
       <c r="P20" s="55" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q20" s="55" t="s">
         <v>20</v>
@@ -22829,7 +23646,7 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.45">
       <c r="O22" s="55" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="P22" s="55" t="s">
         <v>30</v>
@@ -22843,10 +23660,10 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.45">
       <c r="P23" s="55" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q23" s="55" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R23" s="53">
         <v>1</v>
@@ -22854,10 +23671,10 @@
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.45">
       <c r="P24" s="55" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q24" s="55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="R24" s="53">
         <v>1</v>
@@ -22924,7 +23741,7 @@
         <v>34</v>
       </c>
       <c r="Q30" s="55" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="R30" s="53">
         <v>1</v>
@@ -22933,7 +23750,7 @@
     <row r="31" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A31" s="3"/>
       <c r="O31" s="55" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="R31" s="53">
         <v>33</v>

--- a/2025/retro_2025.xlsx
+++ b/2025/retro_2025.xlsx
@@ -8,44 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NFL-Fantasy\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2FB437-A941-47C5-A795-CFBF303F330E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AF23B9-3431-403F-86E3-67331FBB15AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="651" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" state="hidden" r:id="rId1"/>
     <sheet name="Wins by Key" sheetId="7" r:id="rId2"/>
     <sheet name="Wins by Postion" sheetId="6" r:id="rId3"/>
     <sheet name="MVP by Key" sheetId="11" r:id="rId4"/>
-    <sheet name="MVP by Player-Position" sheetId="4" r:id="rId5"/>
-    <sheet name="Team Count" sheetId="9" r:id="rId6"/>
-    <sheet name="Retro" sheetId="1" r:id="rId7"/>
-    <sheet name="Position Matrix" sheetId="3" r:id="rId8"/>
-    <sheet name="xMVP by Position" sheetId="5" r:id="rId9"/>
+    <sheet name="MVP by Position" sheetId="5" r:id="rId5"/>
+    <sheet name="MVP by Player" sheetId="4" r:id="rId6"/>
+    <sheet name="Team Count" sheetId="9" r:id="rId7"/>
+    <sheet name="Retro" sheetId="1" r:id="rId8"/>
+    <sheet name="Position Matrix" sheetId="3" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'xMVP by Position'!$B$32:$B$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Retro!$L$2:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'MVP by Position'!$B$32:$B$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'MVP by Position'!$K$2:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Retro!$L$2:$L$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wins by Postion'!$M$2:$M$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'xMVP by Position'!$K$2:$K$11</definedName>
-    <definedName name="_xlcn.WorksheetConnection_retro_2025.xlsxtretro11" hidden="1">Retro!$A$1:$AF$33</definedName>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet2!$A$3:$AB$9</definedName>
-    <definedName name="MVPbyPlayer">'MVP by Player-Position'!$U$2:INDEX(!$R:$R,COUNTA('MVP by Player-Position'!$R:$R))</definedName>
+    <definedName name="MVPbyPlayer">'MVP by Player'!$U$2:INDEX(!$R:$R,COUNTA('MVP by Player'!$R:$R))</definedName>
     <definedName name="WinsByPosition">'Position Matrix'!$A$82:$C$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId10"/>
-    <pivotCache cacheId="17" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId10"/>
+    <pivotCache cacheId="37" r:id="rId11"/>
   </pivotCaches>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
-      <x15:dataModel>
-        <x15:modelTables>
-          <x15:modelTable id="tretro 1" name="tretro 1" connection="WorksheetConnection_retro_2025.xlsx!tretro1"/>
-        </x15:modelTables>
-      </x15:dataModel>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -71,24 +63,6 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="2" xr16:uid="{D16B3E7E-08A8-4B99-9DE6-C18493E0A954}" keepAlive="1" name="ThisWorkbookDataModel" description="Data Model" type="5" refreshedVersion="8" minRefreshableVersion="5" background="1">
-    <dbPr connection="Data Model Connection" command="Model" commandType="1"/>
-    <olapPr sendLocale="1" rowDrillCount="1000"/>
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="" model="1"/>
-      </ext>
-    </extLst>
-  </connection>
-  <connection id="3" xr16:uid="{B4F9CF86-5F96-4E18-82C3-43B1882A65E9}" name="WorksheetConnection_retro_2025.xlsx!tretro1" type="102" refreshedVersion="8" minRefreshableVersion="5">
-    <extLst>
-      <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
-        <x15:connection id="tretro 1" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_retro_2025.xlsxtretro11"/>
-        </x15:connection>
       </ext>
     </extLst>
   </connection>
@@ -118,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="533">
   <si>
     <t>p2_pos</t>
   </si>
@@ -1575,142 +1549,148 @@
     <t>Count 3</t>
   </si>
   <si>
+    <t>MVP Position</t>
+  </si>
+  <si>
+    <t>MVP Pts Rank</t>
+  </si>
+  <si>
+    <t>MVP Key</t>
+  </si>
+  <si>
+    <t>LS Key</t>
+  </si>
+  <si>
+    <t>TE3:BUF</t>
+  </si>
+  <si>
+    <t>WR2:SEA</t>
+  </si>
+  <si>
+    <t>WR4:SEA</t>
+  </si>
+  <si>
+    <t>122368-63589:Sam Darnold</t>
+  </si>
+  <si>
+    <t>122368-129458:Jaxon Smith-Njigba</t>
+  </si>
+  <si>
+    <t>122368-134837:Tory Horton</t>
+  </si>
+  <si>
+    <t>122368-102785:Jayden Daniels</t>
+  </si>
+  <si>
+    <t>122368-87127:Chris Rodriguez Jr.</t>
+  </si>
+  <si>
+    <t>122368-92890:Cody White</t>
+  </si>
+  <si>
+    <t>Points Rank</t>
+  </si>
+  <si>
+    <t>WR:ARI</t>
+  </si>
+  <si>
+    <t>D:ARI</t>
+  </si>
+  <si>
+    <t>TE:ARI</t>
+  </si>
+  <si>
+    <t>D:DAL</t>
+  </si>
+  <si>
+    <t>122371-30231:Jacoby Brissett</t>
+  </si>
+  <si>
+    <t>122371-31716:Dak Prescott</t>
+  </si>
+  <si>
+    <t>122371-12546:Arizona Cardinals</t>
+  </si>
+  <si>
+    <t>122371-91750:Trey McBride</t>
+  </si>
+  <si>
+    <t>122371-12530:Dallas Cowboys</t>
+  </si>
+  <si>
+    <t>122371-152651:Marvin Harrison Jr.</t>
+  </si>
+  <si>
+    <t>D:DEN</t>
+  </si>
+  <si>
+    <t>RB1:LV</t>
+  </si>
+  <si>
+    <t>WR2:DEN</t>
+  </si>
+  <si>
+    <t>D:LV</t>
+  </si>
+  <si>
+    <t>WR2:LV</t>
+  </si>
+  <si>
+    <t>122490-12531:Denver Broncos</t>
+  </si>
+  <si>
+    <t>122490-102965:Bo Nix</t>
+  </si>
+  <si>
+    <t>122490-167031:Ashton Jeanty</t>
+  </si>
+  <si>
+    <t>122490-151903:Troy Franklin</t>
+  </si>
+  <si>
+    <t>122490-12537:Las Vegas Raiders</t>
+  </si>
+  <si>
+    <t>122490-27050:Tyler Lockett</t>
+  </si>
+  <si>
+    <t>Key 2</t>
+  </si>
+  <si>
+    <t>total_fpts</t>
+  </si>
+  <si>
+    <t>Place</t>
+  </si>
+  <si>
+    <t>HSal Player</t>
+  </si>
+  <si>
+    <t>HSal MVP</t>
+  </si>
+  <si>
+    <t>HSal Wins</t>
+  </si>
+  <si>
+    <t>LSal Key</t>
+  </si>
+  <si>
+    <t>Count of MVP_pos</t>
+  </si>
+  <si>
+    <t>Count of MVP Position</t>
+  </si>
+  <si>
     <t>TE1</t>
   </si>
   <si>
-    <t>MVP Position</t>
-  </si>
-  <si>
-    <t>Pos + Team</t>
-  </si>
-  <si>
-    <t>HS Wins</t>
-  </si>
-  <si>
-    <t>HS MVP</t>
-  </si>
-  <si>
-    <t>HS Position</t>
-  </si>
-  <si>
-    <t>MVP Pts Rank</t>
-  </si>
-  <si>
-    <t>MVP Key</t>
-  </si>
-  <si>
-    <t>LS Key</t>
-  </si>
-  <si>
-    <t>TE3:BUF</t>
-  </si>
-  <si>
-    <t>WR2:SEA</t>
-  </si>
-  <si>
-    <t>WR4:SEA</t>
-  </si>
-  <si>
-    <t>122368-63589:Sam Darnold</t>
-  </si>
-  <si>
-    <t>122368-129458:Jaxon Smith-Njigba</t>
-  </si>
-  <si>
-    <t>122368-134837:Tory Horton</t>
-  </si>
-  <si>
-    <t>122368-102785:Jayden Daniels</t>
-  </si>
-  <si>
-    <t>122368-87127:Chris Rodriguez Jr.</t>
-  </si>
-  <si>
-    <t>122368-92890:Cody White</t>
-  </si>
-  <si>
-    <t>Points Rank</t>
-  </si>
-  <si>
-    <t>WR:ARI</t>
-  </si>
-  <si>
-    <t>D:ARI</t>
-  </si>
-  <si>
-    <t>TE:ARI</t>
-  </si>
-  <si>
-    <t>D:DAL</t>
-  </si>
-  <si>
-    <t>122371-30231:Jacoby Brissett</t>
-  </si>
-  <si>
-    <t>122371-31716:Dak Prescott</t>
-  </si>
-  <si>
-    <t>122371-12546:Arizona Cardinals</t>
-  </si>
-  <si>
-    <t>122371-91750:Trey McBride</t>
-  </si>
-  <si>
-    <t>122371-12530:Dallas Cowboys</t>
-  </si>
-  <si>
-    <t>122371-152651:Marvin Harrison Jr.</t>
-  </si>
-  <si>
-    <t>D:DEN</t>
-  </si>
-  <si>
-    <t>RB1:LV</t>
-  </si>
-  <si>
-    <t>WR2:DEN</t>
-  </si>
-  <si>
-    <t>D:LV</t>
-  </si>
-  <si>
-    <t>WR2:LV</t>
-  </si>
-  <si>
-    <t>122490-12531:Denver Broncos</t>
-  </si>
-  <si>
-    <t>122490-102965:Bo Nix</t>
-  </si>
-  <si>
-    <t>122490-167031:Ashton Jeanty</t>
-  </si>
-  <si>
-    <t>122490-151903:Troy Franklin</t>
-  </si>
-  <si>
-    <t>122490-12537:Las Vegas Raiders</t>
-  </si>
-  <si>
-    <t>122490-27050:Tyler Lockett</t>
-  </si>
-  <si>
-    <t>Key 2</t>
-  </si>
-  <si>
-    <t>total_fpts</t>
-  </si>
-  <si>
-    <t>Place</t>
-  </si>
-  <si>
-    <t>MVP Position2</t>
-  </si>
-  <si>
-    <t>Group1</t>
-  </si>
-  <si>
-    <t>Group2</t>
+    <t>Count of LSal Key</t>
+  </si>
+  <si>
+    <t>Count of Key 2</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
   </si>
 </sst>
 </file>
@@ -2252,7 +2232,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2330,6 +2310,9 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2376,13 +2359,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="52">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3112,6 +3089,18 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -3601,32 +3590,78 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[retro_2025.xlsx]xMVP by Position!PivotTable1</c:name>
-    <c:fmtId val="0"/>
+    <c:name>[retro_2025.xlsx]Team Count!PivotTable2</c:name>
+    <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>MVP by Position</a:t>
+              <a:rPr lang="en-US" b="1" i="0" baseline="0"/>
+              <a:t>Team Count</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
       <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
@@ -3640,13 +3675,23 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr/>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -3664,17 +3709,7 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="7.583220847394076E-2"/>
-          <c:y val="7.9343967651387209E-2"/>
-          <c:w val="0.90642375976767164"/>
-          <c:h val="0.67375584926943821"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -3684,7 +3719,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'xMVP by Position'!$R$2</c:f>
+              <c:f>'Team Count'!$C$15</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3693,6 +3728,15 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
             <c:spPr>
@@ -3703,13 +3747,23 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -3724,251 +3778,67 @@
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>'xMVP by Position'!$O$3:$Q$31</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="28"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>QB:ARI</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>QB:BAL</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>QB:CHI</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>QB:DAL</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>QB:DEN</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>QB:KC</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>QB:LAC</c:v>
-                  </c:pt>
-                  <c:pt idx="7">
-                    <c:v>QB:LAR</c:v>
-                  </c:pt>
-                  <c:pt idx="8">
-                    <c:v>QB:TB</c:v>
-                  </c:pt>
-                  <c:pt idx="9">
-                    <c:v>QB:SEA</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>RB:DAL</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>RB:NYG</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>RB1:ATL</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>RB1:BUF</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>RB1:CHI</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>RB1:DET</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>RB1:SF</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>RB2:DET</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>RB2:NYG</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>TE:GB</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>TE1:GB</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>TE2:PIT</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>WR1:LAR</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>WR1:NE</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>WR1:SEA</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>WR1:ARI</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>WR3:BUF</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>D:DEN</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>QB</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>RB</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>RB1</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>RB2</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>TE</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>TE1</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>TE2</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>WR1</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>WR3</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>D</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>QB</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>Group1</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>Group2</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>WR1</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>WR3</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>D</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
+            <c:strRef>
+              <c:f>'Team Count'!$B$16:$B$20</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'xMVP by Position'!$R$3:$R$31</c:f>
+              <c:f>'Team Count'!$C$16:$C$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="28"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-5F2C-4875-89DE-9B32371F48F2}"/>
+              <c16:uniqueId val="{00000000-A502-46BA-BEBD-0BF42EC6AFB0}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3980,12 +3850,13 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="240"/>
-        <c:axId val="154408448"/>
-        <c:axId val="154409984"/>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="47916256"/>
+        <c:axId val="47916736"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="154408448"/>
+        <c:axId val="47916256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3996,56 +3867,145 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
-          <a:ln/>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-2700000" vert="horz" anchor="b" anchorCtr="0"/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" i="0" baseline="0"/>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154409984"/>
+        <c:crossAx val="47916736"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="1"/>
+        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="154409984"/>
+        <c:axId val="47916736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" i="0" baseline="0"/>
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154408448"/>
+        <c:crossAx val="47916256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -4058,6 +4018,11 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
       </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
     </c:ext>
   </c:extLst>
 </c:chartSpace>
@@ -5472,6 +5437,342 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="28"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="29"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="30"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="31"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="32"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="33"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -5484,7 +5785,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wins by Key'!$S$2</c:f>
+              <c:f>'Wins by Key'!$R$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5505,7 +5806,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Wins by Key'!$Q$3:$R$12</c:f>
+              <c:f>'Wins by Key'!$Q$3:$Q$15</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="9"/>
                 <c:lvl>
@@ -5553,12 +5854,12 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wins by Key'!$S$3:$S$12</c:f>
+              <c:f>'Wins by Key'!$R$3:$R$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>11</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>6</c:v>
@@ -5589,7 +5890,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-91C6-4DD8-8758-A8AB5B4AD412}"/>
+              <c16:uniqueId val="{00000003-E21C-4C10-AEBB-B6D4045CA1B6}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5908,6 +6209,62 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -5939,63 +6296,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Wins by Key'!$J$18:$J$37</c:f>
@@ -6129,7 +6429,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3A0F-4030-9B4F-F3EFD364BF8A}"/>
+              <c16:uniqueId val="{00000000-5E48-409B-9D15-EA3C4E3C04F5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8144,7 +8444,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[retro_2025.xlsx]MVP by Player-Position!PivotTable5</c:name>
+    <c:name>[retro_2025.xlsx]MVP by Position!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -8159,7 +8459,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>MVP by Player-Position</a:t>
+              <a:t>MVP by Position</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -8205,6 +8505,43 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout>
@@ -8212,10 +8549,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.9579676707651666E-2"/>
-          <c:y val="0.14725317179118783"/>
-          <c:w val="0.93384542653153479"/>
-          <c:h val="0.6811490809369577"/>
+          <c:x val="7.583220847394076E-2"/>
+          <c:y val="7.9343967651387209E-2"/>
+          <c:w val="0.90642375976767164"/>
+          <c:h val="0.67375584926943821"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -8227,7 +8564,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'MVP by Player-Position'!$T$2</c:f>
+              <c:f>'MVP by Position'!$Q$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -8272,145 +8609,59 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'MVP by Player-Position'!$Q$3:$S$47</c:f>
+              <c:f>'MVP by Position'!$O$3:$P$13</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="28"/>
+                <c:ptCount val="10"/>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>D:DEN</c:v>
+                    <c:v>QB</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>QB:ARI</c:v>
+                    <c:v>RB</c:v>
                   </c:pt>
                   <c:pt idx="2">
-                    <c:v>QB:BAL</c:v>
+                    <c:v>RB1</c:v>
                   </c:pt>
                   <c:pt idx="3">
-                    <c:v>QB:CHI</c:v>
+                    <c:v>RB2</c:v>
                   </c:pt>
                   <c:pt idx="4">
-                    <c:v>QB:DAL</c:v>
+                    <c:v>TE</c:v>
                   </c:pt>
                   <c:pt idx="5">
-                    <c:v>QB:DEN</c:v>
+                    <c:v>TE1</c:v>
                   </c:pt>
                   <c:pt idx="6">
-                    <c:v>QB:KC</c:v>
+                    <c:v>TE2</c:v>
                   </c:pt>
                   <c:pt idx="7">
-                    <c:v>QB:LAC</c:v>
+                    <c:v>WR1</c:v>
                   </c:pt>
                   <c:pt idx="8">
-                    <c:v>QB:LAR</c:v>
+                    <c:v>WR3</c:v>
                   </c:pt>
                   <c:pt idx="9">
-                    <c:v>QB:SEA</c:v>
-                  </c:pt>
-                  <c:pt idx="10">
-                    <c:v>QB:TB</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>RB:DAL</c:v>
-                  </c:pt>
-                  <c:pt idx="12">
-                    <c:v>RB:NYG</c:v>
-                  </c:pt>
-                  <c:pt idx="13">
-                    <c:v>RB1:ATL</c:v>
-                  </c:pt>
-                  <c:pt idx="14">
-                    <c:v>RB1:BUF</c:v>
-                  </c:pt>
-                  <c:pt idx="15">
-                    <c:v>RB1:CHI</c:v>
-                  </c:pt>
-                  <c:pt idx="16">
-                    <c:v>RB1:DET</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>RB1:SF</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>RB2:DET</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>RB2:NYG</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>TE:GB</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>TE1:GB</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>TE2:PIT</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>WR1:ARI</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>WR1:LAR</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>WR1:NE</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>WR1:SEA</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>WR3:BUF</c:v>
+                    <c:v>D</c:v>
                   </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>D</c:v>
+                    <c:v>QB</c:v>
                   </c:pt>
                   <c:pt idx="1">
-                    <c:v>QB</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
                     <c:v>RB</c:v>
                   </c:pt>
-                  <c:pt idx="13">
-                    <c:v>RB1</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>RB2</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
+                  <c:pt idx="4">
                     <c:v>TE</c:v>
                   </c:pt>
-                  <c:pt idx="21">
-                    <c:v>TE1</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>TE2</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
+                  <c:pt idx="7">
                     <c:v>WR1</c:v>
                   </c:pt>
-                  <c:pt idx="27">
+                  <c:pt idx="8">
                     <c:v>WR3</c:v>
                   </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
+                  <c:pt idx="9">
                     <c:v>D</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>QB</c:v>
-                  </c:pt>
-                  <c:pt idx="11">
-                    <c:v>RB</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>TE</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>WR1</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>WR3</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -8418,7 +8669,358 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'MVP by Player-Position'!$T$3:$T$47</c:f>
+              <c:f>'MVP by Position'!$Q$3:$Q$13</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4E0E-48C2-A343-9DA45E6E73A8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="240"/>
+        <c:axId val="154408448"/>
+        <c:axId val="154409984"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="154408448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" vert="horz" anchor="b" anchorCtr="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" i="0" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154409984"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="0"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="154409984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" i="0" baseline="0"/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="154408448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[retro_2025.xlsx]MVP by Player!PivotTable5</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>MVP by Player</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:delete val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.9579676707651666E-2"/>
+          <c:y val="0.14725317179118783"/>
+          <c:w val="0.93384542653153479"/>
+          <c:h val="0.6811490809369577"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'MVP by Player'!$R$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'MVP by Player'!$Q$3:$Q$31</c:f>
+              <c:strCache>
+                <c:ptCount val="28"/>
+                <c:pt idx="0">
+                  <c:v>D:DEN</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>QB:ARI</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>QB:BAL</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>QB:CHI</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>QB:DAL</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>QB:DEN</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>QB:KC</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>QB:LAC</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>QB:LAR</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>QB:SEA</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>QB:TB</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>RB:DAL</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>RB:NYG</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>RB1:ATL</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>RB1:BUF</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>RB1:CHI</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>RB1:DET</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>RB1:SF</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>RB2:DET</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>RB2:NYG</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>TE:GB</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>TE1:GB</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>TE2:PIT</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>WR1:ARI</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>WR1:LAR</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>WR1:NE</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>WR1:SEA</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>WR3:BUF</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'MVP by Player'!$R$3:$R$31</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="28"/>
@@ -8511,7 +9113,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C36C-4DE7-BAB0-8DD22DB02A3E}"/>
+              <c16:uniqueId val="{00000000-4E01-4EB4-B0A6-1955E3F4AE2F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8591,458 +9193,6 @@
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
         <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[retro_2025.xlsx]Team Count!PivotTable2</c:name>
-    <c:fmtId val="5"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" b="1" i="0" baseline="0"/>
-              <a:t>Team Count</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Team Count'!$C$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Team Count'!$B$16:$B$20</c:f>
-              <c:strCache>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Team Count'!$C$16:$C$20</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A502-46BA-BEBD-0BF42EC6AFB0}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="47916256"/>
-        <c:axId val="47916736"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="47916256"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="47916736"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="47916736"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="47916256"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -12043,6 +12193,49 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>771525</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>171451</xdr:rowOff>
@@ -12079,7 +12272,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -12120,68 +12313,28 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>14289</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>4763</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>771525</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>4763</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mark Meinhardt" refreshedDate="45968.340239120371" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="33" xr:uid="{8D0FBD3B-1097-4375-9216-AFA26F1AA81E}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mark Meinhardt" refreshedDate="45970.365932175926" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="33" xr:uid="{8D0FBD3B-1097-4375-9216-AFA26F1AA81E}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:AF34" sheet="Retro"/>
   </cacheSource>
-  <cacheFields count="32">
+  <cacheFields count="33">
     <cacheField name="Winnings" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.54" maxValue="800"/>
     </cacheField>
     <cacheField name="Winners" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="452"/>
     </cacheField>
-    <cacheField name="HS Position" numFmtId="0">
+    <cacheField name="Place" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
+    </cacheField>
+    <cacheField name="HSal Player" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="HS MVP" numFmtId="0">
+    <cacheField name="HSal MVP" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
-    <cacheField name="HS Wins" numFmtId="0">
+    <cacheField name="HSal Wins" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
     </cacheField>
     <cacheField name="MVP Pts Rank" numFmtId="0">
@@ -12205,7 +12358,7 @@
         <s v="TE1"/>
         <s v="D"/>
       </sharedItems>
-      <fieldGroup par="31"/>
+      <fieldGroup par="32"/>
     </cacheField>
     <cacheField name="Key" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="34" count="12">
@@ -12257,8 +12410,8 @@
         <n v="22"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="LS Key" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="49" count="20">
+    <cacheField name="LSal Key" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="47" count="19">
         <n v="16"/>
         <n v="14"/>
         <n v="47"/>
@@ -12274,11 +12427,10 @@
         <n v="26"/>
         <n v="35"/>
         <n v="22"/>
+        <n v="21"/>
         <n v="18"/>
-        <n v="21"/>
         <n v="27"/>
         <n v="40"/>
-        <n v="49" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="MVP_pos" numFmtId="0">
@@ -12302,10 +12454,10 @@
         <s v="RB:NYG"/>
         <s v="RB1:CHI"/>
         <s v="TE2:PIT"/>
+        <s v="WR1:LAR"/>
         <s v="RB1:SF"/>
         <s v="RB1:DET"/>
         <s v="WR1:SEA"/>
-        <s v="WR1:LAR"/>
         <s v="TE1:GB"/>
         <s v="QB:BAL"/>
         <s v="QB:SEA"/>
@@ -12349,7 +12501,7 @@
     <cacheField name="total_ppts" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="41.9" maxValue="93.8"/>
     </cacheField>
-    <cacheField name="total_pts" numFmtId="0">
+    <cacheField name="total_fpts" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="72" maxValue="170.12"/>
     </cacheField>
     <cacheField name="MVP_name" numFmtId="0">
@@ -12371,17 +12523,17 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="MVP Position2" numFmtId="0" databaseField="0">
-      <fieldGroup base="6">
+      <fieldGroup base="7">
         <discretePr count="10">
-          <x v="4"/>
+          <x v="5"/>
           <x v="0"/>
           <x v="1"/>
+          <x v="4"/>
           <x v="5"/>
+          <x v="5"/>
+          <x v="2"/>
           <x v="4"/>
           <x v="4"/>
-          <x v="2"/>
-          <x v="5"/>
-          <x v="5"/>
           <x v="3"/>
         </discretePr>
         <groupItems count="6">
@@ -12389,8 +12541,8 @@
           <s v="WR3"/>
           <s v="WR1"/>
           <s v="D"/>
+          <s v="Group2"/>
           <s v="Group1"/>
-          <s v="Group2"/>
         </groupItems>
       </fieldGroup>
     </cacheField>
@@ -12404,132 +12556,125 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshOnLoad="1" refreshedBy="Mark Meinhardt" refreshedDate="45969.642203356481" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{73AA8BA1-3B09-4917-AD43-51452F8E9686}">
-  <cacheSource type="external" connectionId="2"/>
-  <cacheFields count="3">
-    <cacheField name="[tretro 1].[Key].[Key]" caption="Key" numFmtId="0" hierarchy="8" level="1">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mark Meinhardt" refreshedDate="45970.394095949072" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="33" xr:uid="{36375135-0F9B-43C1-844A-D73AE4E499AE}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="32">
+    <cacheField name="Winnings" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.54" maxValue="800"/>
+    </cacheField>
+    <cacheField name="Winners" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="452"/>
+    </cacheField>
+    <cacheField name="Place" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="25"/>
+    </cacheField>
+    <cacheField name="HSal Player" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="HSal MVP" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="HSal Wins" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="MVP Pts Rank" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="5"/>
+    </cacheField>
+    <cacheField name="MVP Position" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Key" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="3" count="3">
         <n v="1"/>
         <n v="2"/>
         <n v="3"/>
       </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[tretro 1].[Key].&amp;[1]"/>
-            <x15:cachedUniqueName index="1" name="[tretro 1].[Key].&amp;[2]"/>
-            <x15:cachedUniqueName index="2" name="[tretro 1].[Key].&amp;[3]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
     </cacheField>
-    <cacheField name="[tretro 1].[Key 2].[Key 2]" caption="Key 2" numFmtId="0" hierarchy="11" level="1">
+    <cacheField name="ID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="88847"/>
+    </cacheField>
+    <cacheField name="GroupID" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="15795"/>
+    </cacheField>
+    <cacheField name="Key 2" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="34" count="9">
         <n v="12"/>
         <n v="13"/>
+        <n v="23"/>
+        <n v="16"/>
+        <n v="29"/>
+        <n v="24"/>
         <n v="14"/>
-        <n v="16"/>
-        <n v="23"/>
-        <n v="24"/>
+        <n v="34"/>
         <n v="27"/>
-        <n v="29"/>
-        <n v="34"/>
       </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[tretro 1].[Key 2].&amp;[12]"/>
-            <x15:cachedUniqueName index="1" name="[tretro 1].[Key 2].&amp;[13]"/>
-            <x15:cachedUniqueName index="2" name="[tretro 1].[Key 2].&amp;[14]"/>
-            <x15:cachedUniqueName index="3" name="[tretro 1].[Key 2].&amp;[16]"/>
-            <x15:cachedUniqueName index="4" name="[tretro 1].[Key 2].&amp;[23]"/>
-            <x15:cachedUniqueName index="5" name="[tretro 1].[Key 2].&amp;[24]"/>
-            <x15:cachedUniqueName index="6" name="[tretro 1].[Key 2].&amp;[27]"/>
-            <x15:cachedUniqueName index="7" name="[tretro 1].[Key 2].&amp;[29]"/>
-            <x15:cachedUniqueName index="8" name="[tretro 1].[Key 2].&amp;[34]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
     </cacheField>
-    <cacheField name="[Measures].[Count of Key 2]" caption="Count of Key 2" numFmtId="0" hierarchy="35" level="32767"/>
+    <cacheField name="MVP Key" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="22"/>
+    </cacheField>
+    <cacheField name="LSal Key" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="47"/>
+    </cacheField>
+    <cacheField name="MVP_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p2_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p3_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p4_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p5_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p6_pos" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="select" numFmtId="0">
+      <sharedItems containsNonDate="0" containsString="0" containsBlank="1"/>
+    </cacheField>
+    <cacheField name="team_cnt" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2" maxValue="5"/>
+    </cacheField>
+    <cacheField name="total_salary" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="46800" maxValue="60000"/>
+    </cacheField>
+    <cacheField name="total_fppg" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="48.19" maxValue="96.32"/>
+    </cacheField>
+    <cacheField name="total_ppts" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="41.9" maxValue="93.8"/>
+    </cacheField>
+    <cacheField name="total_fpts" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="72" maxValue="170.12"/>
+    </cacheField>
+    <cacheField name="MVP_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p2_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p3_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p4_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p5_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="p6_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
   </cacheFields>
-  <cacheHierarchies count="36">
-    <cacheHierarchy uniqueName="[tretro 1].[Winnings]" caption="Winnings" attribute="1" defaultMemberUniqueName="[tretro 1].[Winnings].[All]" allUniqueName="[tretro 1].[Winnings].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[Winners]" caption="Winners" attribute="1" defaultMemberUniqueName="[tretro 1].[Winners].[All]" allUniqueName="[tretro 1].[Winners].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[Place]" caption="Place" attribute="1" defaultMemberUniqueName="[tretro 1].[Place].[All]" allUniqueName="[tretro 1].[Place].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[HS Position]" caption="HS Position" attribute="1" defaultMemberUniqueName="[tretro 1].[HS Position].[All]" allUniqueName="[tretro 1].[HS Position].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[HS MVP]" caption="HS MVP" attribute="1" defaultMemberUniqueName="[tretro 1].[HS MVP].[All]" allUniqueName="[tretro 1].[HS MVP].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[HS Wins]" caption="HS Wins" attribute="1" defaultMemberUniqueName="[tretro 1].[HS Wins].[All]" allUniqueName="[tretro 1].[HS Wins].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[MVP Pts Rank]" caption="MVP Pts Rank" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP Pts Rank].[All]" allUniqueName="[tretro 1].[MVP Pts Rank].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[MVP Position]" caption="MVP Position" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP Position].[All]" allUniqueName="[tretro 1].[MVP Position].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[Key]" caption="Key" attribute="1" defaultMemberUniqueName="[tretro 1].[Key].[All]" allUniqueName="[tretro 1].[Key].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[tretro 1].[ID]" caption="ID" attribute="1" defaultMemberUniqueName="[tretro 1].[ID].[All]" allUniqueName="[tretro 1].[ID].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[GroupID]" caption="GroupID" attribute="1" defaultMemberUniqueName="[tretro 1].[GroupID].[All]" allUniqueName="[tretro 1].[GroupID].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[Key 2]" caption="Key 2" attribute="1" defaultMemberUniqueName="[tretro 1].[Key 2].[All]" allUniqueName="[tretro 1].[Key 2].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[tretro 1].[MVP Key]" caption="MVP Key" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP Key].[All]" allUniqueName="[tretro 1].[MVP Key].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[LS Key]" caption="LS Key" attribute="1" defaultMemberUniqueName="[tretro 1].[LS Key].[All]" allUniqueName="[tretro 1].[LS Key].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[MVP_pos]" caption="MVP_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP_pos].[All]" allUniqueName="[tretro 1].[MVP_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p2_pos]" caption="p2_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[p2_pos].[All]" allUniqueName="[tretro 1].[p2_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p3_pos]" caption="p3_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[p3_pos].[All]" allUniqueName="[tretro 1].[p3_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p4_pos]" caption="p4_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[p4_pos].[All]" allUniqueName="[tretro 1].[p4_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p5_pos]" caption="p5_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[p5_pos].[All]" allUniqueName="[tretro 1].[p5_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p6_pos]" caption="p6_pos" attribute="1" defaultMemberUniqueName="[tretro 1].[p6_pos].[All]" allUniqueName="[tretro 1].[p6_pos].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[select]" caption="select" attribute="1" defaultMemberUniqueName="[tretro 1].[select].[All]" allUniqueName="[tretro 1].[select].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[team_cnt]" caption="team_cnt" attribute="1" defaultMemberUniqueName="[tretro 1].[team_cnt].[All]" allUniqueName="[tretro 1].[team_cnt].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[total_salary]" caption="total_salary" attribute="1" defaultMemberUniqueName="[tretro 1].[total_salary].[All]" allUniqueName="[tretro 1].[total_salary].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[total_fppg]" caption="total_fppg" attribute="1" defaultMemberUniqueName="[tretro 1].[total_fppg].[All]" allUniqueName="[tretro 1].[total_fppg].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[total_ppts]" caption="total_ppts" attribute="1" defaultMemberUniqueName="[tretro 1].[total_ppts].[All]" allUniqueName="[tretro 1].[total_ppts].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[total_fpts]" caption="total_fpts" attribute="1" defaultMemberUniqueName="[tretro 1].[total_fpts].[All]" allUniqueName="[tretro 1].[total_fpts].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[MVP_name]" caption="MVP_name" attribute="1" defaultMemberUniqueName="[tretro 1].[MVP_name].[All]" allUniqueName="[tretro 1].[MVP_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p2_name]" caption="p2_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p2_name].[All]" allUniqueName="[tretro 1].[p2_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p3_name]" caption="p3_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p3_name].[All]" allUniqueName="[tretro 1].[p3_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p4_name]" caption="p4_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p4_name].[All]" allUniqueName="[tretro 1].[p4_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p5_name]" caption="p5_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p5_name].[All]" allUniqueName="[tretro 1].[p5_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[tretro 1].[p6_name]" caption="p6_name" attribute="1" defaultMemberUniqueName="[tretro 1].[p6_name].[All]" allUniqueName="[tretro 1].[p6_name].[All]" dimensionUniqueName="[tretro 1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count tretro 1]" caption="__XL_Count tretro 1" measure="1" displayFolder="" measureGroup="tretro 1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Key]" caption="Sum of Key" measure="1" displayFolder="" measureGroup="tretro 1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="11"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of Key 2]" caption="Count of Key 2" measure="1" displayFolder="" measureGroup="tretro 1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="11"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="tretro 1" uniqueName="[tretro 1]" caption="tretro 1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="tretro 1" caption="tretro 1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
@@ -12540,6 +12685,7 @@
   <r>
     <n v="86.44"/>
     <n v="61"/>
+    <n v="2"/>
     <s v="RB:PHI"/>
     <n v="0"/>
     <n v="1"/>
@@ -12573,6 +12719,7 @@
   <r>
     <n v="125"/>
     <n v="5"/>
+    <n v="1"/>
     <s v="QB:KC"/>
     <n v="0"/>
     <n v="1"/>
@@ -12606,6 +12753,7 @@
   <r>
     <n v="43.83"/>
     <n v="30"/>
+    <n v="2"/>
     <s v="QB:BUF"/>
     <n v="0"/>
     <n v="1"/>
@@ -12639,8 +12787,9 @@
   <r>
     <n v="92.43"/>
     <n v="14"/>
-    <s v="WR:MIN"/>
     <n v="1"/>
+    <s v="WR1:MIN"/>
+    <n v="0"/>
     <n v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -12672,6 +12821,7 @@
   <r>
     <n v="135.69"/>
     <n v="36"/>
+    <n v="1"/>
     <s v="QB:WAS"/>
     <n v="0"/>
     <n v="1"/>
@@ -12704,6 +12854,7 @@
   </r>
   <r>
     <n v="500"/>
+    <n v="1"/>
     <n v="1"/>
     <s v="RB1:ATL"/>
     <n v="1"/>
@@ -12738,6 +12889,7 @@
   <r>
     <n v="200"/>
     <n v="2"/>
+    <n v="6"/>
     <s v="QB:TB"/>
     <n v="1"/>
     <n v="0"/>
@@ -12771,6 +12923,7 @@
   <r>
     <n v="73.44"/>
     <n v="16"/>
+    <n v="1"/>
     <s v="QB:LAC"/>
     <n v="1"/>
     <n v="0"/>
@@ -12803,6 +12956,7 @@
   </r>
   <r>
     <n v="500"/>
+    <n v="1"/>
     <n v="1"/>
     <s v="QB:BUF"/>
     <n v="0"/>
@@ -12837,9 +12991,10 @@
   <r>
     <n v="500"/>
     <n v="1"/>
-    <s v="WR:NYG"/>
+    <n v="11"/>
+    <s v="WR1:NYG"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="0"/>
     <x v="1"/>
     <x v="5"/>
     <x v="1"/>
@@ -12870,9 +13025,10 @@
   <r>
     <n v="500"/>
     <n v="1"/>
-    <s v="RB:BAL"/>
+    <n v="2"/>
+    <s v="RB1:BAL"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="0"/>
     <x v="1"/>
     <x v="5"/>
     <x v="1"/>
@@ -12903,8 +13059,9 @@
   <r>
     <n v="215"/>
     <n v="5"/>
+    <n v="1"/>
     <s v="WR1:SEA"/>
-    <n v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -12935,6 +13092,7 @@
   </r>
   <r>
     <n v="750"/>
+    <n v="1"/>
     <n v="1"/>
     <s v="RB1:GB"/>
     <n v="0"/>
@@ -12969,8 +13127,9 @@
   <r>
     <n v="18.25"/>
     <n v="73"/>
+    <n v="1"/>
     <s v="WR1:CIN"/>
-    <n v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -13002,9 +13161,10 @@
   <r>
     <n v="6.54"/>
     <n v="452"/>
+    <n v="1"/>
     <s v="RB:SF"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="0"/>
     <x v="1"/>
     <x v="1"/>
     <x v="1"/>
@@ -13035,6 +13195,7 @@
   <r>
     <n v="121.36"/>
     <n v="11"/>
+    <n v="8"/>
     <s v="QB:BUF"/>
     <n v="0"/>
     <n v="1"/>
@@ -13068,6 +13229,7 @@
   <r>
     <n v="300"/>
     <n v="3"/>
+    <n v="1"/>
     <s v="QB:KC"/>
     <n v="1"/>
     <n v="0"/>
@@ -13101,6 +13263,7 @@
   <r>
     <n v="500"/>
     <n v="1"/>
+    <n v="2"/>
     <s v="QB:PHI"/>
     <n v="0"/>
     <n v="1"/>
@@ -13132,8 +13295,43 @@
     <s v="121303-114054:Dalen Cambre"/>
   </r>
   <r>
+    <n v="17.600000000000001"/>
+    <n v="102"/>
+    <n v="1"/>
+    <s v="WR1:DET"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="77753"/>
+    <n v="14109"/>
+    <x v="7"/>
+    <x v="8"/>
+    <x v="4"/>
+    <x v="15"/>
+    <s v="QB:DET"/>
+    <s v="TE:KC"/>
+    <s v="WR2:DET"/>
+    <s v="TE:DET"/>
+    <s v="WR2:KC"/>
+    <m/>
+    <x v="0"/>
+    <n v="59600"/>
+    <n v="77.59"/>
+    <n v="89.75"/>
+    <n v="122.94"/>
+    <s v="121465-57439:Patrick Mahomes"/>
+    <s v="121465-38435:Jared Goff"/>
+    <s v="121465-33076:Travis Kelce"/>
+    <s v="121465-111631:Jameson Williams"/>
+    <s v="121465-105646:Sam LaPorta"/>
+    <s v="121465-86687:Hollywood Brown"/>
+  </r>
+  <r>
     <n v="90"/>
     <n v="8"/>
+    <n v="1"/>
     <s v="QB:BUF"/>
     <n v="0"/>
     <n v="1"/>
@@ -13165,41 +13363,9 @@
     <s v="121479-64585:Dawson Knox"/>
   </r>
   <r>
-    <n v="17.600000000000001"/>
-    <n v="102"/>
-    <s v="WR1:DET"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="2"/>
-    <n v="77753"/>
-    <n v="14109"/>
-    <x v="7"/>
-    <x v="8"/>
-    <x v="4"/>
-    <x v="15"/>
-    <s v="QB:DET"/>
-    <s v="TE:KC"/>
-    <s v="WR2:DET"/>
-    <s v="TE:DET"/>
-    <s v="WR2:KC"/>
-    <m/>
-    <x v="0"/>
-    <n v="59600"/>
-    <n v="77.59"/>
-    <n v="89.75"/>
-    <n v="122.94"/>
-    <s v="121465-57439:Patrick Mahomes"/>
-    <s v="121465-38435:Jared Goff"/>
-    <s v="121465-33076:Travis Kelce"/>
-    <s v="121465-111631:Jameson Williams"/>
-    <s v="121465-105646:Sam LaPorta"/>
-    <s v="121465-86687:Hollywood Brown"/>
-  </r>
-  <r>
     <n v="500"/>
     <n v="1"/>
+    <n v="2"/>
     <s v="QB:WAS"/>
     <n v="0"/>
     <n v="1"/>
@@ -13233,6 +13399,7 @@
   <r>
     <n v="500"/>
     <n v="1"/>
+    <n v="1"/>
     <s v="WR1:CIN"/>
     <n v="0"/>
     <n v="1"/>
@@ -13264,8 +13431,43 @@
     <s v="121556-86092:Evan McPherson"/>
   </r>
   <r>
+    <n v="237.86"/>
+    <n v="7"/>
+    <n v="1"/>
+    <s v="RB:LAR"/>
+    <n v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="35517"/>
+    <n v="6303"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="15"/>
+    <x v="19"/>
+    <s v="QB:LAR"/>
+    <s v="QB:JAC"/>
+    <s v="WR2:JAC"/>
+    <s v="D:LAR"/>
+    <s v="WR:JAC"/>
+    <m/>
+    <x v="0"/>
+    <n v="60000"/>
+    <n v="67.290000000000006"/>
+    <n v="73.650000000000006"/>
+    <n v="123.32"/>
+    <s v="121707-45889:Davante Adams"/>
+    <s v="121707-6654:Matthew Stafford"/>
+    <s v="121707-89951:Trevor Lawrence"/>
+    <s v="121707-184184:Travis Hunter"/>
+    <s v="121707-12538:Los Angeles Rams"/>
+    <s v="121707-137516:Parker Washington"/>
+  </r>
+  <r>
     <n v="300"/>
     <n v="3"/>
+    <n v="1"/>
     <s v="RB1:ATL"/>
     <n v="0"/>
     <n v="1"/>
@@ -13277,7 +13479,7 @@
     <x v="0"/>
     <x v="3"/>
     <x v="1"/>
-    <x v="19"/>
+    <x v="20"/>
     <s v="RB1:ATL"/>
     <s v="WR2:ATL Q"/>
     <s v="K:SF"/>
@@ -13299,6 +13501,7 @@
   <r>
     <n v="166.67"/>
     <n v="3"/>
+    <n v="25"/>
     <s v="RB1:DET"/>
     <n v="1"/>
     <n v="0"/>
@@ -13309,8 +13512,8 @@
     <n v="3478"/>
     <x v="1"/>
     <x v="4"/>
-    <x v="15"/>
-    <x v="20"/>
+    <x v="16"/>
+    <x v="21"/>
     <s v="WR1:DET"/>
     <s v="TE1:TB"/>
     <s v="D:DET"/>
@@ -13332,6 +13535,7 @@
   <r>
     <n v="400"/>
     <n v="1"/>
+    <n v="2"/>
     <s v="WR1:SEA"/>
     <n v="1"/>
     <n v="0"/>
@@ -13343,7 +13547,7 @@
     <x v="6"/>
     <x v="4"/>
     <x v="4"/>
-    <x v="21"/>
+    <x v="22"/>
     <s v="QB:HOU"/>
     <s v="RB2:SEA"/>
     <s v="K:SEA"/>
@@ -13363,43 +13567,11 @@
     <s v="121719-55042:Dalton Schultz"/>
   </r>
   <r>
-    <n v="237.86"/>
-    <n v="7"/>
-    <s v="RB:LAC"/>
-    <n v="0"/>
-    <n v="1"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="1"/>
-    <n v="35517"/>
-    <n v="6303"/>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="16"/>
-    <x v="22"/>
-    <s v="QB:LAR"/>
-    <s v="QB:JAC"/>
-    <s v="WR2:JAC"/>
-    <s v="D:LAR"/>
-    <s v="WR:JAC"/>
-    <m/>
-    <x v="0"/>
-    <n v="60000"/>
-    <n v="67.290000000000006"/>
-    <n v="73.650000000000006"/>
-    <n v="123.32"/>
-    <s v="121707-45889:Davante Adams"/>
-    <s v="121707-6654:Matthew Stafford"/>
-    <s v="121707-89951:Trevor Lawrence"/>
-    <s v="121707-184184:Travis Hunter"/>
-    <s v="121707-12538:Los Angeles Rams"/>
-    <s v="121707-137516:Parker Washington"/>
-  </r>
-  <r>
     <n v="23.15"/>
     <n v="84"/>
+    <n v="1"/>
     <s v="WR1:MIN"/>
-    <n v="1"/>
+    <n v="0"/>
     <n v="0"/>
     <x v="1"/>
     <x v="1"/>
@@ -13431,9 +13603,10 @@
   <r>
     <n v="185"/>
     <n v="5"/>
+    <n v="4"/>
     <s v="RB:GB"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="0"/>
     <x v="1"/>
     <x v="8"/>
     <x v="1"/>
@@ -13463,6 +13636,7 @@
   </r>
   <r>
     <n v="500"/>
+    <n v="1"/>
     <n v="1"/>
     <s v="WR1:KC"/>
     <n v="0"/>
@@ -13497,6 +13671,7 @@
   <r>
     <n v="416.67"/>
     <n v="3"/>
+    <n v="1"/>
     <s v="QB:BAL"/>
     <n v="1"/>
     <n v="0"/>
@@ -13530,6 +13705,7 @@
   <r>
     <n v="500"/>
     <n v="1"/>
+    <n v="2"/>
     <s v="WR1:SEA"/>
     <n v="0"/>
     <n v="1"/>
@@ -13563,6 +13739,7 @@
   <r>
     <n v="800"/>
     <n v="1"/>
+    <n v="4"/>
     <s v="QB:DAL"/>
     <n v="0"/>
     <n v="1"/>
@@ -13596,6 +13773,7 @@
   <r>
     <n v="800"/>
     <n v="1"/>
+    <n v="3"/>
     <s v="QB:DEN"/>
     <n v="0"/>
     <n v="1"/>
@@ -13629,39 +13807,1199 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="33">
+  <r>
+    <n v="86.44"/>
+    <n v="61"/>
+    <n v="2"/>
+    <s v="RB:PHI"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="RB"/>
+    <x v="0"/>
+    <n v="108"/>
+    <n v="53"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="16"/>
+    <s v="RB:DAL"/>
+    <s v="RB:PHI"/>
+    <s v="QB:PHI"/>
+    <s v="WR1:DAL"/>
+    <s v="K:DAL"/>
+    <s v="WR3:PHI"/>
+    <m/>
+    <n v="3"/>
+    <n v="57700"/>
+    <n v="82.4"/>
+    <n v="86.22"/>
+    <n v="105.68"/>
+    <s v="119244-93541:Javonte Williams"/>
+    <s v="119244-64401:Saquon Barkley"/>
+    <s v="119244-69531:Jalen Hurts"/>
+    <s v="119244-86631:CeeDee Lamb"/>
+    <s v="119244-189471:Brandon Aubrey"/>
+    <s v="119244-86229:Jahan Dotson"/>
+  </r>
+  <r>
+    <n v="125"/>
+    <n v="5"/>
+    <n v="1"/>
+    <s v="QB:KC"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="27863"/>
+    <n v="5037"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="14"/>
+    <s v="QB:LAC"/>
+    <s v="QB:KC"/>
+    <s v="WR2:LAC"/>
+    <s v="K:KC"/>
+    <s v="WR3:LAC"/>
+    <s v="WR2:KC"/>
+    <m/>
+    <n v="3"/>
+    <n v="57600"/>
+    <n v="67.69"/>
+    <n v="76.14"/>
+    <n v="137"/>
+    <s v="120114-69189:Justin Herbert"/>
+    <s v="120114-57439:Patrick Mahomes"/>
+    <s v="120114-29253:Keenan Allen"/>
+    <s v="120114-41642:Harrison Butker"/>
+    <s v="120114-120639:Quentin Johnston"/>
+    <s v="120114-86687:Hollywood Brown"/>
+  </r>
+  <r>
+    <n v="43.83"/>
+    <n v="30"/>
+    <n v="2"/>
+    <s v="QB:BUF"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="5"/>
+    <s v="WR3"/>
+    <x v="0"/>
+    <n v="83"/>
+    <n v="48"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="47"/>
+    <s v="WR3:BUF"/>
+    <s v="QB:BUF"/>
+    <s v="QB:BAL"/>
+    <s v="RB1:BAL"/>
+    <s v="WR1:BAL"/>
+    <s v="TE3:BUF"/>
+    <m/>
+    <n v="3"/>
+    <n v="57800"/>
+    <n v="88.55"/>
+    <n v="91.86"/>
+    <n v="170.12"/>
+    <s v="120169-157467:Keon Coleman"/>
+    <s v="120169-62239:Josh Allen"/>
+    <s v="120169-63115:Lamar Jackson"/>
+    <s v="120169-39280:Derrick Henry"/>
+    <s v="120169-112295:Zay Flowers"/>
+    <s v="120169-200291:Jackson Hawes"/>
+  </r>
+  <r>
+    <n v="92.43"/>
+    <n v="14"/>
+    <n v="1"/>
+    <s v="WR1:MIN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="1"/>
+    <n v="78776"/>
+    <n v="14416"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="20"/>
+    <s v="QB:CHI"/>
+    <s v="QB:MIN"/>
+    <s v="RB1:MIN"/>
+    <s v="WR2:CHI"/>
+    <s v="D:CHI"/>
+    <s v="WR4:CHI"/>
+    <m/>
+    <n v="4"/>
+    <n v="59300"/>
+    <n v="48.19"/>
+    <n v="56.2"/>
+    <n v="103.62"/>
+    <s v="120172-152113:Caleb Williams"/>
+    <s v="120172-152575:J.J. McCarthy"/>
+    <s v="120172-40442:Aaron Jones Sr."/>
+    <s v="120172-120033:Rome Odunze"/>
+    <s v="120172-12527:Chicago Bears"/>
+    <s v="120172-64496:Olamide Zaccheaus"/>
+  </r>
+  <r>
+    <n v="135.69"/>
+    <n v="36"/>
+    <n v="1"/>
+    <s v="QB:WAS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="TE"/>
+    <x v="0"/>
+    <n v="227"/>
+    <n v="71"/>
+    <x v="0"/>
+    <n v="15"/>
+    <n v="15"/>
+    <s v="TE:GB"/>
+    <s v="QB:WAS"/>
+    <s v="RB:GB"/>
+    <s v="QB:GB"/>
+    <s v="K:GB"/>
+    <s v="TE:WAS"/>
+    <m/>
+    <n v="2"/>
+    <n v="57500"/>
+    <n v="77.540000000000006"/>
+    <n v="81.99"/>
+    <n v="117.98"/>
+    <s v="120272-160303:Tucker Kraft"/>
+    <s v="120272-102785:Jayden Daniels"/>
+    <s v="120272-72731:Josh Jacobs"/>
+    <s v="120272-69017:Jordan Love"/>
+    <s v="120272-26247:Brandon McManus"/>
+    <s v="120272-29780:Zach Ertz"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB1:ATL"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="2707"/>
+    <n v="706"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="19"/>
+    <s v="RB1:ATL"/>
+    <s v="WR1:MIN"/>
+    <s v="K:MIN"/>
+    <s v="K:ATL"/>
+    <s v="D:ATL"/>
+    <s v="RB2:ATL"/>
+    <m/>
+    <n v="4"/>
+    <n v="57700"/>
+    <n v="61.1"/>
+    <n v="41.9"/>
+    <n v="103.05"/>
+    <s v="120469-136855:Bijan Robinson"/>
+    <s v="120469-85671:Justin Jefferson"/>
+    <s v="120469-102703:Will Reichard"/>
+    <s v="120469-88035:John Parker Romo"/>
+    <s v="120469-12525:Atlanta Falcons"/>
+    <s v="120469-90428:Tyler Allgeier"/>
+  </r>
+  <r>
+    <n v="200"/>
+    <n v="2"/>
+    <n v="6"/>
+    <s v="QB:TB"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="14668"/>
+    <n v="2884"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="42"/>
+    <s v="QB:TB"/>
+    <s v="RB1:TB"/>
+    <s v="QB1:HOU"/>
+    <s v="RB1:HOU"/>
+    <s v="RB2:TB"/>
+    <s v="QB2:HOU"/>
+    <m/>
+    <n v="3"/>
+    <n v="58600"/>
+    <n v="52.9"/>
+    <n v="64.19"/>
+    <n v="96.23"/>
+    <s v="120474-41535:Baker Mayfield"/>
+    <s v="120474-152664:Bucky Irving"/>
+    <s v="120474-129471:C.J. Stroud"/>
+    <s v="120474-53562:Nick Chubb"/>
+    <s v="120474-137902:Rachaad White"/>
+    <s v="120474-103591:Graham Mertz"/>
+  </r>
+  <r>
+    <n v="73.44"/>
+    <n v="16"/>
+    <n v="1"/>
+    <s v="QB:LAC"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="32522"/>
+    <n v="5988"/>
+    <x v="3"/>
+    <n v="1"/>
+    <n v="12"/>
+    <s v="QB:LAC"/>
+    <s v="WR1:LV"/>
+    <s v="WR2:LAC"/>
+    <s v="WR3:LAC"/>
+    <s v="K:LV"/>
+    <s v="D:LAC"/>
+    <m/>
+    <n v="4"/>
+    <n v="58200"/>
+    <n v="96.32"/>
+    <n v="84.7"/>
+    <n v="91.97"/>
+    <s v="120475-69189:Justin Herbert"/>
+    <s v="120475-63634:Jakobi Meyers"/>
+    <s v="120475-29253:Keenan Allen"/>
+    <s v="120475-120639:Quentin Johnston"/>
+    <s v="120475-40856:Daniel Carlson"/>
+    <s v="120475-12548:Los Angeles Chargers"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="QB:BUF"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="30089"/>
+    <n v="5736"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="20"/>
+    <s v="RB1:BUF"/>
+    <s v="QB:BUF"/>
+    <s v="WR1:BUF"/>
+    <s v="WR2:MIA"/>
+    <s v="TE1:BUF"/>
+    <s v="RB2:MIA"/>
+    <m/>
+    <n v="4"/>
+    <n v="59400"/>
+    <n v="76.89"/>
+    <n v="93.8"/>
+    <n v="106.27"/>
+    <s v="120537-91626:James Cook"/>
+    <s v="120537-62239:Josh Allen"/>
+    <s v="120537-86518:Khalil Shakir"/>
+    <s v="120537-90573:Jaylen Waddle"/>
+    <s v="120537-145558:Dalton Kincaid"/>
+    <s v="120537-166112:Ollie Gordon II"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="11"/>
+    <s v="WR1:NYG"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="RB2"/>
+    <x v="1"/>
+    <n v="54196"/>
+    <n v="9605"/>
+    <x v="4"/>
+    <n v="9"/>
+    <n v="16"/>
+    <s v="RB2:NYG"/>
+    <s v="QB:KC"/>
+    <s v="D:KC"/>
+    <s v="K:KC"/>
+    <s v="RB2:KC"/>
+    <s v="WR3:KC"/>
+    <m/>
+    <n v="5"/>
+    <n v="46800"/>
+    <n v="56.7"/>
+    <n v="60.4"/>
+    <n v="96.31"/>
+    <s v="120720-183240:Cam Skattebo"/>
+    <s v="120720-57439:Patrick Mahomes"/>
+    <s v="120720-12536:Kansas City Chiefs"/>
+    <s v="120720-41642:Harrison Butker"/>
+    <s v="120720-45229:Kareem Hunt"/>
+    <s v="120720-89220:Tyquan Thornton"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="RB1:BAL"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="RB2"/>
+    <x v="1"/>
+    <n v="45325"/>
+    <n v="8121"/>
+    <x v="2"/>
+    <n v="8"/>
+    <n v="15"/>
+    <s v="RB2:DET"/>
+    <s v="QB:BAL"/>
+    <s v="RB1:DET"/>
+    <s v="WR1:DET"/>
+    <s v="TE1:BAL"/>
+    <s v="WR2:BAL"/>
+    <m/>
+    <n v="3"/>
+    <n v="58400"/>
+    <n v="76.53"/>
+    <n v="81.25"/>
+    <n v="155.37"/>
+    <s v="120784-73273:David Montgomery"/>
+    <s v="120784-63115:Lamar Jackson"/>
+    <s v="120784-129368:Jahmyr Gibbs"/>
+    <s v="120784-86997:Amon-Ra St. Brown"/>
+    <s v="120784-52436:Mark Andrews"/>
+    <s v="120784-85845:Rashod Bateman"/>
+  </r>
+  <r>
+    <n v="215"/>
+    <n v="5"/>
+    <n v="1"/>
+    <s v="WR1:SEA"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="1"/>
+    <n v="88847"/>
+    <n v="15795"/>
+    <x v="2"/>
+    <n v="2"/>
+    <n v="17"/>
+    <s v="QB:ARI"/>
+    <s v="QB:SEA"/>
+    <s v="WR1:ARI"/>
+    <s v="K:SEA"/>
+    <s v="RB2:SEA"/>
+    <s v="TE1:SEA"/>
+    <m/>
+    <n v="2"/>
+    <n v="58900"/>
+    <n v="59.12"/>
+    <n v="67.010000000000005"/>
+    <n v="94.93"/>
+    <s v="120794-63484:Kyler Murray"/>
+    <s v="120794-63589:Sam Darnold"/>
+    <s v="120794-152651:Marvin Harrison Jr."/>
+    <s v="120794-60745:Jason Myers"/>
+    <s v="120794-103376:Zach Charbonnet"/>
+    <s v="120794-137953:AJ Barner"/>
+  </r>
+  <r>
+    <n v="750"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB1:GB"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="36784"/>
+    <n v="6925"/>
+    <x v="1"/>
+    <n v="3"/>
+    <n v="23"/>
+    <s v="QB:DAL"/>
+    <s v="RB1:GB"/>
+    <s v="WR1:DAL"/>
+    <s v="WR1:GB"/>
+    <s v="K:GB"/>
+    <s v="RB3:GB"/>
+    <m/>
+    <n v="4"/>
+    <n v="59800"/>
+    <n v="56.47"/>
+    <n v="64.47"/>
+    <n v="161.44"/>
+    <s v="120969-31716:Dak Prescott"/>
+    <s v="120969-72731:Josh Jacobs"/>
+    <s v="120969-110246:George Pickens"/>
+    <s v="120969-94370:Romeo Doubs"/>
+    <s v="120969-26247:Brandon McManus"/>
+    <s v="120969-185861:Emanuel Wilson"/>
+  </r>
+  <r>
+    <n v="18.25"/>
+    <n v="73"/>
+    <n v="1"/>
+    <s v="WR1:CIN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="1"/>
+    <n v="35310"/>
+    <n v="6705"/>
+    <x v="5"/>
+    <n v="2"/>
+    <n v="19"/>
+    <s v="QB:DEN"/>
+    <s v="QB:CIN"/>
+    <s v="WR1:DEN"/>
+    <s v="RB1:DEN"/>
+    <s v="RB2:DEN"/>
+    <s v="WR3:DEN Q"/>
+    <m/>
+    <n v="5"/>
+    <n v="60000"/>
+    <n v="64.819999999999993"/>
+    <n v="72.069999999999993"/>
+    <n v="115.91"/>
+    <s v="120973-102965:Bo Nix"/>
+    <s v="120973-60840:Jake Browning"/>
+    <s v="120973-57403:Courtland Sutton"/>
+    <s v="120973-87787:J.K. Dobbins"/>
+    <s v="120973-110484:RJ Harvey"/>
+    <s v="120973-120093:Marvin Mims Jr."/>
+  </r>
+  <r>
+    <n v="6.54"/>
+    <n v="452"/>
+    <n v="1"/>
+    <s v="RB:SF"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="1"/>
+    <n v="4973"/>
+    <n v="856"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="24"/>
+    <s v="QB:LAR"/>
+    <s v="WR1:LAR"/>
+    <s v="QB:SF Q"/>
+    <s v="RB1:LAR"/>
+    <s v="WR2:SF"/>
+    <s v="RB1:SF"/>
+    <m/>
+    <n v="3"/>
+    <n v="52700"/>
+    <n v="76.44"/>
+    <n v="86.09"/>
+    <n v="160.72"/>
+    <s v="121030-6654:Matthew Stafford"/>
+    <s v="121030-103020:Puka Nacua"/>
+    <s v="121030-85607:Brock Purdy"/>
+    <s v="121030-137967:Blake Corum"/>
+    <s v="121030-80289:Kendrick Bourne"/>
+    <s v="121030-90562:Brian Robinson Jr."/>
+  </r>
+  <r>
+    <n v="121.36"/>
+    <n v="11"/>
+    <n v="8"/>
+    <s v="QB:BUF"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="WR1"/>
+    <x v="0"/>
+    <n v="68287"/>
+    <n v="12679"/>
+    <x v="3"/>
+    <n v="6"/>
+    <n v="31"/>
+    <s v="WR1:NE"/>
+    <s v="QB:BUF"/>
+    <s v="TE1:BUF"/>
+    <s v="RB2:NE"/>
+    <s v="K:NE"/>
+    <s v="WR4:BUF"/>
+    <m/>
+    <n v="3"/>
+    <n v="51400"/>
+    <n v="59.97"/>
+    <n v="64.19"/>
+    <n v="107.42"/>
+    <s v="121217-25079:Stefon Diggs"/>
+    <s v="121217-62239:Josh Allen"/>
+    <s v="121217-145558:Dalton Kincaid"/>
+    <s v="121217-111540:Rhamondre Stevenson"/>
+    <s v="121217-152260:Andy Borregales"/>
+    <s v="121217-52613:Curtis Samuel"/>
+  </r>
+  <r>
+    <n v="300"/>
+    <n v="3"/>
+    <n v="1"/>
+    <s v="QB:KC"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="56121"/>
+    <n v="10717"/>
+    <x v="6"/>
+    <n v="1"/>
+    <n v="23"/>
+    <s v="QB:KC"/>
+    <s v="QB:JAC"/>
+    <s v="TE:KC"/>
+    <s v="WR3:KC"/>
+    <s v="RB2:KC"/>
+    <s v="WR2:JAC"/>
+    <m/>
+    <n v="4"/>
+    <n v="58700"/>
+    <n v="65.11"/>
+    <n v="76.31"/>
+    <n v="126.22"/>
+    <s v="121293-57439:Patrick Mahomes"/>
+    <s v="121293-89951:Trevor Lawrence"/>
+    <s v="121293-33076:Travis Kelce"/>
+    <s v="121293-89220:Tyquan Thornton"/>
+    <s v="121293-45229:Kareem Hunt"/>
+    <s v="121293-137516:Parker Washington"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="QB:PHI"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB"/>
+    <x v="0"/>
+    <n v="8942"/>
+    <n v="1883"/>
+    <x v="1"/>
+    <n v="4"/>
+    <n v="47"/>
+    <s v="RB:NYG"/>
+    <s v="QB:PHI"/>
+    <s v="QB:NYG Q"/>
+    <s v="WR1:NYG"/>
+    <s v="TE:PHI"/>
+    <s v="WR:NYG"/>
+    <m/>
+    <n v="2"/>
+    <n v="59700"/>
+    <n v="62.65"/>
+    <n v="68.75"/>
+    <n v="139.62"/>
+    <s v="121303-183240:Cam Skattebo"/>
+    <s v="121303-69531:Jalen Hurts"/>
+    <s v="121303-151966:Jaxson Dart"/>
+    <s v="121303-103539:Wan'Dale Robinson"/>
+    <s v="121303-83074:Dallas Goedert"/>
+    <s v="121303-114054:Dalen Cambre"/>
+  </r>
+  <r>
+    <n v="17.600000000000001"/>
+    <n v="102"/>
+    <n v="1"/>
+    <s v="WR1:DET"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="2"/>
+    <n v="77753"/>
+    <n v="14109"/>
+    <x v="7"/>
+    <n v="4"/>
+    <n v="15"/>
+    <s v="QB:KC"/>
+    <s v="QB:DET"/>
+    <s v="TE:KC"/>
+    <s v="WR2:DET"/>
+    <s v="TE:DET"/>
+    <s v="WR2:KC"/>
+    <m/>
+    <n v="3"/>
+    <n v="59600"/>
+    <n v="77.59"/>
+    <n v="89.75"/>
+    <n v="122.94"/>
+    <s v="121465-57439:Patrick Mahomes"/>
+    <s v="121465-38435:Jared Goff"/>
+    <s v="121465-33076:Travis Kelce"/>
+    <s v="121465-111631:Jameson Williams"/>
+    <s v="121465-105646:Sam LaPorta"/>
+    <s v="121465-86687:Hollywood Brown"/>
+  </r>
+  <r>
+    <n v="90"/>
+    <n v="8"/>
+    <n v="1"/>
+    <s v="QB:BUF"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="1922"/>
+    <n v="467"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="26"/>
+    <s v="RB1:ATL"/>
+    <s v="QB:BUF"/>
+    <s v="QB:ATL"/>
+    <s v="WR1:ATL"/>
+    <s v="RB2:BUF"/>
+    <s v="TE2:BUF"/>
+    <m/>
+    <n v="3"/>
+    <n v="58600"/>
+    <n v="75.39"/>
+    <n v="86.55"/>
+    <n v="132.80000000000001"/>
+    <s v="121479-136855:Bijan Robinson"/>
+    <s v="121479-62239:Josh Allen"/>
+    <s v="121479-88797:Michael Penix Jr."/>
+    <s v="121479-112745:Drake London"/>
+    <s v="121479-103694:Ray Davis"/>
+    <s v="121479-64585:Dawson Knox"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="QB:WAS"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="9078"/>
+    <n v="1925"/>
+    <x v="0"/>
+    <n v="5"/>
+    <n v="35"/>
+    <s v="RB1:CHI"/>
+    <s v="QB:WAS"/>
+    <s v="QB:CHI"/>
+    <s v="K:CHI"/>
+    <s v="TE:WAS"/>
+    <s v="WR4:WAS"/>
+    <m/>
+    <n v="3"/>
+    <n v="54100"/>
+    <n v="65.19"/>
+    <n v="70.650000000000006"/>
+    <n v="125.17"/>
+    <s v="121480-91598:D'Andre Swift"/>
+    <s v="121480-102785:Jayden Daniels"/>
+    <s v="121480-152113:Caleb Williams"/>
+    <s v="121480-91372:Jake Moody"/>
+    <s v="121480-29780:Zach Ertz"/>
+    <s v="121480-33047:Chris Moore"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="WR1:CIN"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="3"/>
+    <s v="TE2"/>
+    <x v="0"/>
+    <n v="992"/>
+    <n v="298"/>
+    <x v="0"/>
+    <n v="22"/>
+    <n v="22"/>
+    <s v="TE2:PIT"/>
+    <s v="WR1:CIN"/>
+    <s v="QB:PIT"/>
+    <s v="QB:CIN"/>
+    <s v="RB1:PIT"/>
+    <s v="K:CIN"/>
+    <m/>
+    <n v="3"/>
+    <n v="59300"/>
+    <n v="62.36"/>
+    <n v="63.85"/>
+    <n v="167.34"/>
+    <s v="121556-86244:Pat Freiermuth"/>
+    <s v="121556-85701:Ja'Marr Chase"/>
+    <s v="121556-6894:Aaron Rodgers"/>
+    <s v="121556-6714:Joe Flacco"/>
+    <s v="121556-112057:Jaylen Warren"/>
+    <s v="121556-86092:Evan McPherson"/>
+  </r>
+  <r>
+    <n v="237.86"/>
+    <n v="7"/>
+    <n v="1"/>
+    <s v="RB:LAR"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="2"/>
+    <s v="WR1"/>
+    <x v="1"/>
+    <n v="35517"/>
+    <n v="6303"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="21"/>
+    <s v="WR1:LAR"/>
+    <s v="QB:LAR"/>
+    <s v="QB:JAC"/>
+    <s v="WR2:JAC"/>
+    <s v="D:LAR"/>
+    <s v="WR:JAC"/>
+    <m/>
+    <n v="3"/>
+    <n v="60000"/>
+    <n v="67.290000000000006"/>
+    <n v="73.650000000000006"/>
+    <n v="123.32"/>
+    <s v="121707-45889:Davante Adams"/>
+    <s v="121707-6654:Matthew Stafford"/>
+    <s v="121707-89951:Trevor Lawrence"/>
+    <s v="121707-184184:Travis Hunter"/>
+    <s v="121707-12538:Los Angeles Rams"/>
+    <s v="121707-137516:Parker Washington"/>
+  </r>
+  <r>
+    <n v="300"/>
+    <n v="3"/>
+    <n v="1"/>
+    <s v="RB1:ATL"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="6289"/>
+    <n v="1349"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="14"/>
+    <s v="RB1:SF"/>
+    <s v="RB1:ATL"/>
+    <s v="WR2:ATL Q"/>
+    <s v="K:SF"/>
+    <s v="D:SF"/>
+    <s v="TE:ATL"/>
+    <m/>
+    <n v="3"/>
+    <n v="59800"/>
+    <n v="74.73"/>
+    <n v="85.1"/>
+    <n v="113.1"/>
+    <s v="121692-55050:Christian McCaffrey"/>
+    <s v="121692-136855:Bijan Robinson"/>
+    <s v="121692-69777:Darnell Mooney"/>
+    <s v="121692-69307:Eddy Pineiro"/>
+    <s v="121692-12549:San Francisco 49ers"/>
+    <s v="121692-86080:Kyle Pitts Sr."/>
+  </r>
+  <r>
+    <n v="166.67"/>
+    <n v="3"/>
+    <n v="25"/>
+    <s v="RB1:DET"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="RB1"/>
+    <x v="0"/>
+    <n v="18281"/>
+    <n v="3478"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="18"/>
+    <s v="RB1:DET"/>
+    <s v="WR1:DET"/>
+    <s v="TE1:TB"/>
+    <s v="D:DET"/>
+    <s v="K:DET"/>
+    <s v="WR5:TB"/>
+    <m/>
+    <n v="4"/>
+    <n v="56500"/>
+    <n v="58.59"/>
+    <n v="66.150000000000006"/>
+    <n v="118.85"/>
+    <s v="121718-129368:Jahmyr Gibbs"/>
+    <s v="121718-86997:Amon-Ra St. Brown"/>
+    <s v="121718-86811:Cade Otton"/>
+    <s v="121718-12532:Detroit Lions"/>
+    <s v="121718-140176:Jake Bates"/>
+    <s v="121718-128624:Tez Johnson"/>
+  </r>
+  <r>
+    <n v="400"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="WR1:SEA"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="WR1"/>
+    <x v="0"/>
+    <n v="28628"/>
+    <n v="5364"/>
+    <x v="6"/>
+    <n v="1"/>
+    <n v="15"/>
+    <s v="WR1:SEA"/>
+    <s v="QB:HOU"/>
+    <s v="RB2:SEA"/>
+    <s v="K:SEA"/>
+    <s v="D:HOU"/>
+    <s v="TE:HOU"/>
+    <m/>
+    <n v="3"/>
+    <n v="58800"/>
+    <n v="69.44"/>
+    <n v="79.25"/>
+    <n v="113.41"/>
+    <s v="121719-129458:Jaxon Smith-Njigba"/>
+    <s v="121719-129471:C.J. Stroud"/>
+    <s v="121719-103376:Zach Charbonnet"/>
+    <s v="121719-60745:Jason Myers"/>
+    <s v="121719-12556:Houston Texans"/>
+    <s v="121719-55042:Dalton Schultz"/>
+  </r>
+  <r>
+    <n v="23.15"/>
+    <n v="84"/>
+    <n v="1"/>
+    <s v="WR1:MIN"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="1"/>
+    <n v="64130"/>
+    <n v="11503"/>
+    <x v="8"/>
+    <n v="2"/>
+    <n v="15"/>
+    <s v="QB:LAC"/>
+    <s v="RB1:LAC"/>
+    <s v="WR2:MIN"/>
+    <s v="TE:LAC"/>
+    <s v="WR3:LAC"/>
+    <s v="K:LAC"/>
+    <m/>
+    <n v="5"/>
+    <n v="58900"/>
+    <n v="75.05"/>
+    <n v="85.7"/>
+    <n v="120.72"/>
+    <s v="121822-69189:Justin Herbert"/>
+    <s v="121822-128633:Kimani Vidal"/>
+    <s v="121822-129210:Jordan Addison"/>
+    <s v="121822-158438:Oronde Gadsden II"/>
+    <s v="121822-133472:Ladd McConkey"/>
+    <s v="121822-92496:Cameron Dicker"/>
+  </r>
+  <r>
+    <n v="185"/>
+    <n v="5"/>
+    <n v="4"/>
+    <s v="RB:GB"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="TE1"/>
+    <x v="1"/>
+    <n v="29325"/>
+    <n v="5723"/>
+    <x v="2"/>
+    <n v="5"/>
+    <n v="24"/>
+    <s v="TE1:GB"/>
+    <s v="QB:GB"/>
+    <s v="QB:PIT"/>
+    <s v="K:PIT"/>
+    <s v="RB2:GB"/>
+    <s v="WR3:PIT"/>
+    <m/>
+    <n v="3"/>
+    <n v="53800"/>
+    <n v="61.57"/>
+    <n v="67.55"/>
+    <n v="142.86000000000001"/>
+    <s v="121989-160303:Tucker Kraft"/>
+    <s v="121989-69017:Jordan Love"/>
+    <s v="121989-6894:Aaron Rodgers"/>
+    <s v="121989-32058:Chris Boswell"/>
+    <s v="121989-185861:Emanuel Wilson"/>
+    <s v="121989-138037:Roman Wilson"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="WR1:KC"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="14639"/>
+    <n v="3064"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="27"/>
+    <s v="QB:KC"/>
+    <s v="WR1:KC"/>
+    <s v="WR2:WAS"/>
+    <s v="TE1:KC"/>
+    <s v="RB3:KC"/>
+    <s v="RB3:WAS"/>
+    <m/>
+    <n v="4"/>
+    <n v="56500"/>
+    <n v="72.819999999999993"/>
+    <n v="85.5"/>
+    <n v="116.24"/>
+    <s v="121993-57439:Patrick Mahomes"/>
+    <s v="121993-111311:Rashee Rice"/>
+    <s v="121993-56250:Terry McLaurin"/>
+    <s v="121993-33076:Travis Kelce"/>
+    <s v="121993-45229:Kareem Hunt"/>
+    <s v="121993-56648:Jeremy McNichols"/>
+  </r>
+  <r>
+    <n v="416.67"/>
+    <n v="3"/>
+    <n v="1"/>
+    <s v="QB:BAL"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="5640"/>
+    <n v="1291"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="31"/>
+    <s v="QB:BAL"/>
+    <s v="RB1:BAL"/>
+    <s v="WR2:MIA"/>
+    <s v="TE1:BAL"/>
+    <s v="D:BAL"/>
+    <s v="TE3:BAL"/>
+    <m/>
+    <n v="5"/>
+    <n v="59600"/>
+    <n v="60.41"/>
+    <n v="72.2"/>
+    <n v="105.04"/>
+    <s v="122149-63115:Lamar Jackson"/>
+    <s v="122149-39280:Derrick Henry"/>
+    <s v="122149-90573:Jaylen Waddle"/>
+    <s v="122149-52436:Mark Andrews"/>
+    <s v="122149-12555:Baltimore Ravens"/>
+    <s v="122149-85635:Charlie Kolar"/>
+  </r>
+  <r>
+    <n v="500"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="WR1:SEA"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="QB"/>
+    <x v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="3"/>
+    <n v="40"/>
+    <s v="QB:SEA"/>
+    <s v="WR1:SEA"/>
+    <s v="WR2:SEA"/>
+    <s v="QB:WAS"/>
+    <s v="RB3:WAS"/>
+    <s v="WR4:SEA"/>
+    <m/>
+    <n v="4"/>
+    <n v="50800"/>
+    <n v="66.2"/>
+    <n v="74.7"/>
+    <n v="127.82"/>
+    <s v="122368-63589:Sam Darnold"/>
+    <s v="122368-129458:Jaxon Smith-Njigba"/>
+    <s v="122368-134837:Tory Horton"/>
+    <s v="122368-102785:Jayden Daniels"/>
+    <s v="122368-87127:Chris Rodriguez Jr."/>
+    <s v="122368-92890:Cody White"/>
+  </r>
+  <r>
+    <n v="800"/>
+    <n v="1"/>
+    <n v="4"/>
+    <s v="QB:DAL"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="2"/>
+    <s v="WR1"/>
+    <x v="0"/>
+    <n v="13640"/>
+    <n v="2832"/>
+    <x v="6"/>
+    <n v="8"/>
+    <n v="14"/>
+    <s v="WR1:ARI"/>
+    <s v="QB:DAL"/>
+    <s v="QB:ARI"/>
+    <s v="TE:ARI"/>
+    <s v="D:DAL"/>
+    <s v="D:ARI"/>
+    <m/>
+    <n v="2"/>
+    <n v="58900"/>
+    <n v="62.43"/>
+    <n v="67.05"/>
+    <n v="111.89"/>
+    <s v="122371-152651:Marvin Harrison Jr."/>
+    <s v="122371-31716:Dak Prescott"/>
+    <s v="122371-30231:Jacoby Brissett"/>
+    <s v="122371-91750:Trey McBride"/>
+    <s v="122371-12530:Dallas Cowboys"/>
+    <s v="122371-12546:Arizona Cardinals"/>
+  </r>
+  <r>
+    <n v="800"/>
+    <n v="1"/>
+    <n v="3"/>
+    <s v="QB:DEN"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <s v="D"/>
+    <x v="0"/>
+    <n v="11961"/>
+    <n v="2457"/>
+    <x v="0"/>
+    <n v="10"/>
+    <n v="15"/>
+    <s v="D:DEN"/>
+    <s v="QB:DEN"/>
+    <s v="RB1:LV"/>
+    <s v="WR2:DEN"/>
+    <s v="D:LV"/>
+    <s v="WR2:LV"/>
+    <m/>
+    <n v="3"/>
+    <n v="54200"/>
+    <n v="57.18"/>
+    <n v="61.05"/>
+    <n v="72"/>
+    <s v="122490-12531:Denver Broncos"/>
+    <s v="122490-102965:Bo Nix"/>
+    <s v="122490-167031:Ashton Jeanty"/>
+    <s v="122490-151903:Troy Franklin"/>
+    <s v="122490-12537:Las Vegas Raiders"/>
+    <s v="122490-27050:Tyler Lockett"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{EB527574-7E05-49A2-899E-EFF9B6B3BA1E}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="33" rowHeaderCaption="Key">
-  <location ref="Q2:S12" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
-  <pivotFields count="3">
-    <pivotField name="Key" axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05D7BD1D-EF91-4589-AB19-3A3F47210B36}" name="PivotTable1" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="Q2:R15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="32">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Key 2" axis="axisRow" compact="0" allDrilled="1" outline="0" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="9">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="10">
         <item x="0"/>
         <item x="1"/>
+        <item x="6"/>
+        <item x="3"/>
         <item x="2"/>
-        <item x="3"/>
+        <item x="5"/>
+        <item x="8"/>
         <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
         <item x="7"/>
-        <item x="8"/>
+        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="2">
-    <field x="0"/>
-    <field x="1"/>
+    <field x="8"/>
+    <field x="11"/>
   </rowFields>
-  <rowItems count="10">
+  <rowItems count="13">
     <i>
       <x/>
+    </i>
+    <i r="1">
       <x/>
     </i>
     <i r="1">
@@ -13675,6 +15013,8 @@
     </i>
     <i>
       <x v="1"/>
+    </i>
+    <i r="1">
       <x v="4"/>
     </i>
     <i r="1">
@@ -13688,6 +15028,8 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i r="1">
       <x v="8"/>
     </i>
     <i t="grand">
@@ -13698,10 +15040,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+    <dataField name="Count of Key 2" fld="11" subtotal="count" baseField="11" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="27" series="1">
+    <chartFormat chart="0" format="33" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -13711,70 +15053,24 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="36">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1" caption="Count"/>
-  </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="2">
-    <rowHierarchyUsage hierarchyUsage="8"/>
-    <rowHierarchyUsage hierarchyUsage="11"/>
-  </rowHierarchiesUsage>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_retro_2025.xlsx!tretro1">
-        <x15:activeTabTopLevelEntity name="[tretro 1]"/>
-      </x15:pivotTableUISettings>
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+      <xpdl:pivotTableDefinition16/>
     </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
   <location ref="J17:K37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -13801,16 +15097,16 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="21">
+      <items count="20">
         <item x="7"/>
         <item x="1"/>
         <item x="4"/>
         <item x="0"/>
         <item x="8"/>
-        <item x="15"/>
+        <item x="16"/>
         <item x="5"/>
         <item x="3"/>
-        <item x="16"/>
+        <item x="15"/>
         <item x="14"/>
         <item x="9"/>
         <item x="10"/>
@@ -13821,7 +15117,6 @@
         <item x="18"/>
         <item x="6"/>
         <item x="2"/>
-        <item m="1" x="19"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -13847,8 +15142,8 @@
       <items count="7">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
@@ -13856,7 +15151,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="12"/>
+    <field x="13"/>
   </rowFields>
   <rowItems count="20">
     <i>
@@ -13924,10 +15219,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="12" subtotal="count" baseField="12" baseItem="0"/>
+    <dataField name="Count of LSal Key" fld="13" subtotal="count" baseField="13" baseItem="1"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="0" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -13950,10 +15245,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C1699D1F-4550-400A-88A9-C0923278F41A}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Key">
   <location ref="G2:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -14018,8 +15314,8 @@
       <items count="7">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
@@ -14027,7 +15323,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="7"/>
+    <field x="8"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -14047,7 +15343,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="7" subtotal="count" baseField="7" baseItem="0"/>
+    <dataField name="Count" fld="8" subtotal="count" baseField="7" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="10" series="1">
@@ -14073,14 +15369,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Key">
   <location ref="R2:T25" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="10">
@@ -14096,22 +15393,7 @@
         <item x="2"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="12">
-        <item m="1" x="3"/>
-        <item m="1" x="4"/>
-        <item m="1" x="9"/>
-        <item m="1" x="6"/>
-        <item m="1" x="5"/>
-        <item m="1" x="8"/>
-        <item m="1" x="11"/>
-        <item m="1" x="7"/>
-        <item m="1" x="10"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
@@ -14142,6 +15424,7 @@
         <item x="10"/>
       </items>
     </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -14153,8 +15436,7 @@
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
@@ -14165,16 +15447,16 @@
       <items count="6">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
       </items>
     </pivotField>
   </pivotFields>
   <rowFields count="2">
+    <field x="12"/>
     <field x="11"/>
-    <field x="10"/>
   </rowFields>
   <rowItems count="23">
     <i>
@@ -14262,7 +15544,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="11" subtotal="count" baseField="12" baseItem="0"/>
+    <dataField name="Count" fld="12" subtotal="count" baseField="12" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
@@ -14288,10 +15570,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F5C6A80F-C986-4044-9970-54BDEBDCA0EC}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Key">
   <location ref="G2:H14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14355,8 +15638,8 @@
       <items count="7">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
@@ -14364,7 +15647,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="11"/>
+    <field x="12"/>
   </rowFields>
   <rowItems count="12">
     <i>
@@ -14408,7 +15691,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="11" subtotal="count" baseField="12" baseItem="0"/>
+    <dataField name="Count" fld="12" subtotal="count" baseField="12" baseItem="0"/>
   </dataFields>
   <chartFormats count="8">
     <chartFormat chart="0" format="0" series="1">
@@ -14497,10 +15780,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{11D64267-FDBB-4773-A3F2-751ECC0E6067}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" rowHeaderCaption="Points Rank">
   <location ref="G19:H24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14557,8 +15841,8 @@
       <items count="7">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
@@ -14566,7 +15850,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="5"/>
+    <field x="6"/>
   </rowFields>
   <rowItems count="5">
     <i>
@@ -14589,7 +15873,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="5" subtotal="count" baseField="5" baseItem="0"/>
+    <dataField name="Count" fld="6" subtotal="count" baseField="5" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
@@ -14615,16 +15899,151 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
-  <location ref="Q2:T47" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
-  <pivotFields count="32">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="4">
+  <location ref="O2:Q13" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="33">
+    <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="10">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="2"/>
+        <item x="9"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField name="MVP_pos" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField name="MVP" axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
+      <items count="6">
+        <item x="0"/>
+        <item n="RB" x="5"/>
+        <item n="TE" x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="32"/>
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i r="1">
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x v="9"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of MVP Position" fld="7" subtotal="count" baseField="6" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0C48D4A-DA1E-42E4-AC03-2F643C2078D3}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" outline="1" outlineData="1" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Player">
+  <location ref="Q2:R31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="33">
     <pivotField compact="0" numFmtId="4" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0" sortType="ascending">
+    <pivotField compact="0" showAll="0"/>
+    <pivotField compact="0" showAll="0" sortType="ascending">
       <items count="11">
         <item x="9"/>
         <item x="1"/>
@@ -14663,17 +16082,17 @@
         <item x="5"/>
         <item x="7"/>
         <item x="17"/>
+        <item x="21"/>
         <item x="20"/>
-        <item x="19"/>
         <item x="9"/>
         <item x="8"/>
         <item x="4"/>
         <item x="23"/>
         <item x="18"/>
         <item x="26"/>
+        <item x="19"/>
+        <item x="14"/>
         <item x="22"/>
-        <item x="14"/>
-        <item x="21"/>
         <item x="2"/>
         <item m="1" x="28"/>
         <item t="default"/>
@@ -14696,154 +16115,104 @@
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
     <pivotField compact="0" showAll="0"/>
-    <pivotField axis="axisRow" compact="0" showAll="0">
+    <pivotField compact="0" showAll="0">
       <items count="7">
         <item x="3"/>
         <item x="0"/>
-        <item n="RB" x="4"/>
-        <item n="TE" x="5"/>
+        <item x="5"/>
+        <item n="TE" x="4"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="3">
-    <field x="31"/>
-    <field x="6"/>
-    <field x="13"/>
+  <rowFields count="1">
+    <field x="14"/>
   </rowFields>
-  <rowItems count="45">
+  <rowItems count="29">
     <i>
-      <x/>
-    </i>
-    <i r="1">
-      <x/>
-    </i>
-    <i r="2">
       <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
-    <i r="2">
-      <x v="6"/>
-    </i>
-    <i r="2">
-      <x v="7"/>
-    </i>
-    <i r="2">
-      <x v="8"/>
-    </i>
-    <i r="2">
-      <x v="9"/>
-    </i>
-    <i r="2">
-      <x v="10"/>
-    </i>
     <i>
       <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="11"/>
-    </i>
-    <i r="2">
-      <x v="12"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="13"/>
-    </i>
-    <i r="2">
-      <x v="14"/>
-    </i>
-    <i r="2">
-      <x v="15"/>
-    </i>
-    <i r="2">
-      <x v="16"/>
-    </i>
-    <i r="2">
-      <x v="17"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="18"/>
-    </i>
-    <i r="2">
-      <x v="19"/>
     </i>
     <i>
       <x v="3"/>
     </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="2">
-      <x v="20"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="2">
-      <x v="21"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="2">
-      <x v="22"/>
-    </i>
     <i>
       <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="2">
-      <x v="23"/>
-    </i>
-    <i r="2">
-      <x v="24"/>
-    </i>
-    <i r="2">
-      <x v="25"/>
-    </i>
-    <i r="2">
-      <x v="26"/>
     </i>
     <i>
       <x v="5"/>
     </i>
-    <i r="1">
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
       <x v="9"/>
     </i>
-    <i r="2">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+    </i>
+    <i>
+      <x v="26"/>
+    </i>
+    <i>
       <x v="27"/>
     </i>
     <i t="grand">
@@ -14854,10 +16223,10 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="13" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Count of MVP_pos" fld="14" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="0" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -14879,11 +16248,12 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30E4A014-D775-48A6-8108-F00E686C03BA}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7" rowHeaderCaption="Team Count">
   <location ref="B15:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="32">
+  <pivotFields count="33">
     <pivotField numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -14940,8 +16310,8 @@
       <items count="7">
         <item x="3"/>
         <item x="0"/>
+        <item x="5"/>
         <item x="4"/>
-        <item x="5"/>
         <item x="2"/>
         <item x="1"/>
         <item t="default"/>
@@ -14949,7 +16319,7 @@
     </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="20"/>
+    <field x="21"/>
   </rowFields>
   <rowItems count="5">
     <i>
@@ -14972,7 +16342,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count" fld="20" subtotal="count" baseField="18" baseItem="0"/>
+    <dataField name="Count" fld="21" subtotal="count" baseField="18" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="5" format="0" series="1">
@@ -14992,236 +16362,6 @@
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
       <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90766011-1FE9-42B2-BDD4-6F637B637E6E}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="O2:R31" firstHeaderRow="1" firstDataRow="1" firstDataCol="3"/>
-  <pivotFields count="32">
-    <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="10">
-        <item x="1"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="6"/>
-        <item x="2"/>
-        <item x="9"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField name="Pos + Team" axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="29">
-        <item x="10"/>
-        <item x="24"/>
-        <item x="3"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="1"/>
-        <item x="13"/>
-        <item x="6"/>
-        <item x="0"/>
-        <item x="16"/>
-        <item x="5"/>
-        <item x="7"/>
-        <item x="17"/>
-        <item x="20"/>
-        <item x="19"/>
-        <item x="9"/>
-        <item x="8"/>
-        <item x="4"/>
-        <item x="23"/>
-        <item x="18"/>
-        <item x="22"/>
-        <item x="14"/>
-        <item x="21"/>
-        <item x="2"/>
-        <item m="1" x="28"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="3"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="3">
-    <field x="31"/>
-    <field x="6"/>
-    <field x="13"/>
-  </rowFields>
-  <rowItems count="29">
-    <i>
-      <x/>
-      <x/>
-      <x/>
-    </i>
-    <i r="2">
-      <x v="1"/>
-    </i>
-    <i r="2">
-      <x v="2"/>
-    </i>
-    <i r="2">
-      <x v="3"/>
-    </i>
-    <i r="2">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="5"/>
-    </i>
-    <i r="2">
-      <x v="6"/>
-    </i>
-    <i r="2">
-      <x v="7"/>
-    </i>
-    <i r="2">
-      <x v="8"/>
-    </i>
-    <i r="2">
-      <x v="26"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x v="1"/>
-      <x v="9"/>
-    </i>
-    <i r="2">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-      <x v="11"/>
-    </i>
-    <i r="2">
-      <x v="12"/>
-    </i>
-    <i r="2">
-      <x v="13"/>
-    </i>
-    <i r="2">
-      <x v="14"/>
-    </i>
-    <i r="2">
-      <x v="15"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-      <x v="16"/>
-    </i>
-    <i r="2">
-      <x v="17"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x v="4"/>
-      <x v="18"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-      <x v="19"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-      <x v="20"/>
-    </i>
-    <i>
-      <x v="3"/>
-      <x v="7"/>
-      <x v="21"/>
-    </i>
-    <i r="2">
-      <x v="22"/>
-    </i>
-    <i r="2">
-      <x v="23"/>
-    </i>
-    <i r="2">
-      <x v="27"/>
-    </i>
-    <i>
-      <x v="4"/>
-      <x v="8"/>
-      <x v="24"/>
-    </i>
-    <i>
-      <x v="5"/>
-      <x v="9"/>
-      <x v="28"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count" fld="13" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -15307,31 +16447,31 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}" name="Table1" displayName="Table1" ref="A1:AF34" totalsRowShown="0" headerRowDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}" name="Table1" displayName="Table1" ref="A1:AF34" totalsRowShown="0" headerRowDxfId="51">
   <autoFilter ref="A1:AF34" xr:uid="{5EF13D29-8EC9-4A4D-ADB1-D0D84CAF154A}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{D2AA0CDD-D609-4F29-A891-5B2A9B97B638}" name="Winnings"/>
     <tableColumn id="2" xr3:uid="{951CDDCB-E748-4FBA-BC57-9BC6CB4ABD61}" name="Winners"/>
     <tableColumn id="32" xr3:uid="{C9B46930-60A5-4A52-A107-30CA389A4430}" name="Place"/>
-    <tableColumn id="3" xr3:uid="{96316C00-9998-4DEC-93B0-2A0C771E2793}" name="HS Position"/>
-    <tableColumn id="4" xr3:uid="{EFF99116-80B7-47B5-A377-CCBE51772AED}" name="HS MVP" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{96316C00-9998-4DEC-93B0-2A0C771E2793}" name="HSal Player"/>
+    <tableColumn id="4" xr3:uid="{EFF99116-80B7-47B5-A377-CCBE51772AED}" name="HSal MVP" dataDxfId="50">
       <calculatedColumnFormula>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F8284C57-8CD4-4C8E-9CBC-0015B3198933}" name="HS Wins" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{F8284C57-8CD4-4C8E-9CBC-0015B3198933}" name="HSal Wins" dataDxfId="49">
       <calculatedColumnFormula>COUNTIFS(Table1[[#This Row],[Key]],1,Table1[[#This Row],[MVP Key]],"&lt;&gt;1")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{082E3E39-C3ED-495A-A992-2A8BE58C2DD0}" name="MVP Pts Rank"/>
-    <tableColumn id="7" xr3:uid="{D409B8A2-BC75-49E9-A374-2C6980818423}" name="MVP Position">
-      <calculatedColumnFormula>MID(Retro!$O2,1,FIND(":",Retro!$O2)-1)</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{D409B8A2-BC75-49E9-A374-2C6980818423}" name="MVP Position" dataDxfId="48">
+      <calculatedColumnFormula>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D7B7A405-880A-4B7E-B73D-1B3844125CCA}" name="Key">
-      <calculatedColumnFormula>INT(MID(Retro!$L2,1,1))</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{D7B7A405-880A-4B7E-B73D-1B3844125CCA}" name="Key" dataDxfId="47">
+      <calculatedColumnFormula>INT(MID(Table1[[#This Row],[Key 2]],1,1))</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" xr3:uid="{75CDC988-398A-4189-9108-EA5EF84E1335}" name="ID"/>
     <tableColumn id="10" xr3:uid="{9E30B069-EB8A-404D-866E-29C5DAB8729E}" name="GroupID"/>
     <tableColumn id="11" xr3:uid="{CCB4204E-6D74-4BCD-B5B6-C27A56377417}" name="Key 2"/>
     <tableColumn id="12" xr3:uid="{20B644B6-92D2-4DC4-B911-9A84DB47B5B7}" name="MVP Key"/>
-    <tableColumn id="13" xr3:uid="{572817D3-2BEC-4DCE-91F6-3C5FC846653A}" name="LS Key"/>
+    <tableColumn id="13" xr3:uid="{572817D3-2BEC-4DCE-91F6-3C5FC846653A}" name="LSal Key"/>
     <tableColumn id="14" xr3:uid="{9E1D53EF-F725-4431-B8F4-DA7C031DCD79}" name="MVP_pos"/>
     <tableColumn id="15" xr3:uid="{EF3C461F-46F6-4F2D-85AB-2F7C7A60EEA2}" name="p2_pos"/>
     <tableColumn id="16" xr3:uid="{3DEE2904-D5B6-43B4-864C-F09958F74768}" name="p3_pos"/>
@@ -15356,29 +16496,29 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="46" dataDxfId="45" totalsRowDxfId="44">
   <autoFilter ref="A1:T34" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="45" totalsRowDxfId="44"/>
-    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
-    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
-    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="16"/>
-    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="13" totalsRowDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{0869948F-49F8-43F4-984E-EB5EBAB53467}" name="D2" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{D9518A54-A717-439D-88F2-039D1254BA96}" name="K" totalsRowFunction="count" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{3C6C9D69-4926-4F00-834F-22157AAEA17A}" name="K2" totalsRowFunction="count" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{0B5FE4A7-B566-4CB2-B85F-7C41231FD249}" name="QB" totalsRowFunction="count" dataDxfId="33" totalsRowDxfId="32"/>
+    <tableColumn id="7" xr3:uid="{7D72277A-6910-4649-8596-8BFE5D985210}" name="QB1" totalsRowFunction="count" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{37390652-7FB1-44F8-BE50-7005BB8D660C}" name="QB2" totalsRowFunction="count" dataDxfId="29" totalsRowDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{9BC9FDCC-8E9A-4D89-ADDA-BE4401596F26}" name="RB" totalsRowFunction="count" dataDxfId="27" totalsRowDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{1A9FACFF-6B01-4DA1-A536-9ECE1E391D55}" name="RB1" totalsRowFunction="count" dataDxfId="25" totalsRowDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{DB3BFD8A-5848-4D46-A567-EC2EF609EE35}" name="RB2" totalsRowFunction="count" dataDxfId="23" totalsRowDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{D8E77E84-6F05-4351-9B6A-19C0CA9F8D91}" name="TE" totalsRowFunction="count" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{2D64C90C-A395-4453-85F3-132E58ADCE21}" name="TE2" totalsRowFunction="count" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{4622AAC3-650A-4D5B-B3D5-361A6F503318}" name="WR1" totalsRowFunction="count" dataDxfId="17" totalsRowDxfId="16"/>
+    <tableColumn id="15" xr3:uid="{C89312D8-F344-482E-9451-87092AA7A956}" name="WR12" totalsRowFunction="count" dataDxfId="15" totalsRowDxfId="14"/>
+    <tableColumn id="16" xr3:uid="{BF0B4145-9588-426B-AC1C-E0269FFB21C2}" name="WR2" totalsRowFunction="count" dataDxfId="13" totalsRowDxfId="12"/>
+    <tableColumn id="17" xr3:uid="{EF50CD25-8213-4183-8E7F-F018B007206F}" name="WR22" totalsRowFunction="count" dataDxfId="11" totalsRowDxfId="10"/>
+    <tableColumn id="18" xr3:uid="{86E44340-4434-46E5-8B77-4ABB587BA7C4}" name="WR3" totalsRowFunction="count" dataDxfId="9" totalsRowDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{81F29627-0828-46FC-860A-D3C074F32915}" name="WR32" totalsRowFunction="count" dataDxfId="7" totalsRowDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{12BD2881-5612-4A57-9C57-BDF6FC575346}" name="WR4" totalsRowFunction="count" dataDxfId="5" totalsRowDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16311,14 +17451,13 @@
     <col min="8" max="8" width="5.796875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.46484375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.1328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.73046875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2.59765625" customWidth="1"/>
-    <col min="17" max="17" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -16330,13 +17469,10 @@
         <v>481</v>
       </c>
       <c r="Q2" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="R2" s="56" t="s">
-        <v>525</v>
-      </c>
-      <c r="S2" t="s">
-        <v>481</v>
+        <v>532</v>
+      </c>
+      <c r="R2" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="3" spans="7:26" x14ac:dyDescent="0.45">
@@ -16346,14 +17482,11 @@
       <c r="H3" s="53">
         <v>23</v>
       </c>
-      <c r="Q3" s="55">
+      <c r="Q3" s="57">
         <v>1</v>
       </c>
-      <c r="R3" s="55">
-        <v>12</v>
-      </c>
-      <c r="S3" s="53">
-        <v>11</v>
+      <c r="R3" s="53">
+        <v>23</v>
       </c>
       <c r="V3" s="12"/>
       <c r="W3" s="12"/>
@@ -16366,11 +17499,11 @@
       <c r="H4" s="53">
         <v>9</v>
       </c>
-      <c r="R4" s="55">
-        <v>13</v>
-      </c>
-      <c r="S4" s="53">
-        <v>6</v>
+      <c r="Q4" s="73">
+        <v>12</v>
+      </c>
+      <c r="R4" s="53">
+        <v>12</v>
       </c>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
@@ -16383,11 +17516,11 @@
       <c r="H5" s="53">
         <v>1</v>
       </c>
-      <c r="R5" s="55">
-        <v>14</v>
-      </c>
-      <c r="S5" s="53">
-        <v>3</v>
+      <c r="Q5" s="73">
+        <v>13</v>
+      </c>
+      <c r="R5" s="53">
+        <v>6</v>
       </c>
       <c r="U5" s="16"/>
       <c r="V5" s="12"/>
@@ -16401,11 +17534,11 @@
       <c r="H6" s="53">
         <v>33</v>
       </c>
-      <c r="R6" s="55">
-        <v>16</v>
-      </c>
-      <c r="S6" s="53">
-        <v>2</v>
+      <c r="Q6" s="73">
+        <v>14</v>
+      </c>
+      <c r="R6" s="53">
+        <v>3</v>
       </c>
       <c r="U6" s="16"/>
       <c r="V6" s="12"/>
@@ -16413,14 +17546,11 @@
       <c r="X6" s="12"/>
     </row>
     <row r="7" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q7" s="55">
+      <c r="Q7" s="73">
+        <v>16</v>
+      </c>
+      <c r="R7" s="53">
         <v>2</v>
-      </c>
-      <c r="R7" s="55">
-        <v>23</v>
-      </c>
-      <c r="S7" s="53">
-        <v>6</v>
       </c>
       <c r="U7" s="16"/>
       <c r="V7" s="12"/>
@@ -16428,11 +17558,11 @@
       <c r="X7" s="12"/>
     </row>
     <row r="8" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="R8" s="55">
-        <v>24</v>
-      </c>
-      <c r="S8" s="53">
-        <v>1</v>
+      <c r="Q8" s="57">
+        <v>2</v>
+      </c>
+      <c r="R8" s="53">
+        <v>9</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="12"/>
@@ -16440,11 +17570,11 @@
       <c r="X8" s="12"/>
     </row>
     <row r="9" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="R9" s="55">
-        <v>27</v>
-      </c>
-      <c r="S9" s="53">
-        <v>1</v>
+      <c r="Q9" s="73">
+        <v>23</v>
+      </c>
+      <c r="R9" s="53">
+        <v>6</v>
       </c>
       <c r="U9" s="16"/>
       <c r="V9" s="12"/>
@@ -16452,10 +17582,10 @@
       <c r="X9" s="12"/>
     </row>
     <row r="10" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="R10" s="55">
-        <v>29</v>
-      </c>
-      <c r="S10" s="53">
+      <c r="Q10" s="73">
+        <v>24</v>
+      </c>
+      <c r="R10" s="53">
         <v>1</v>
       </c>
       <c r="U10" s="16"/>
@@ -16464,13 +17594,10 @@
       <c r="X10" s="12"/>
     </row>
     <row r="11" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q11" s="55">
-        <v>3</v>
-      </c>
-      <c r="R11" s="55">
-        <v>34</v>
-      </c>
-      <c r="S11" s="53">
+      <c r="Q11" s="73">
+        <v>27</v>
+      </c>
+      <c r="R11" s="53">
         <v>1</v>
       </c>
       <c r="U11" s="16"/>
@@ -16479,11 +17606,11 @@
       <c r="X11" s="12"/>
     </row>
     <row r="12" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q12" s="55" t="s">
-        <v>432</v>
-      </c>
-      <c r="S12" s="53">
-        <v>32</v>
+      <c r="Q12" s="73">
+        <v>29</v>
+      </c>
+      <c r="R12" s="53">
+        <v>1</v>
       </c>
       <c r="U12" s="16"/>
       <c r="V12" s="12"/>
@@ -16491,6 +17618,12 @@
       <c r="X12" s="12"/>
     </row>
     <row r="13" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="Q13" s="57">
+        <v>3</v>
+      </c>
+      <c r="R13" s="53">
+        <v>1</v>
+      </c>
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="12"/>
@@ -16499,6 +17632,12 @@
       <c r="Y13" s="12"/>
     </row>
     <row r="14" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="Q14" s="73">
+        <v>34</v>
+      </c>
+      <c r="R14" s="53">
+        <v>1</v>
+      </c>
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="12"/>
@@ -16507,6 +17646,12 @@
       <c r="Z14" s="16"/>
     </row>
     <row r="15" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="Q15" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="R15" s="53">
+        <v>33</v>
+      </c>
       <c r="T15" s="16"/>
       <c r="U15" s="16"/>
       <c r="V15" s="12"/>
@@ -16519,10 +17664,10 @@
     </row>
     <row r="17" spans="2:26" x14ac:dyDescent="0.45">
       <c r="J17" s="56" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="K17" t="s">
-        <v>481</v>
+        <v>530</v>
       </c>
       <c r="U17" s="16"/>
       <c r="V17" s="12"/>
@@ -17098,10 +18243,10 @@
         <v>481</v>
       </c>
       <c r="R2" s="56" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="S2" s="56" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="T2" t="s">
         <v>481</v>
@@ -17327,7 +18472,7 @@
     </row>
     <row r="19" spans="7:20" x14ac:dyDescent="0.45">
       <c r="G19" s="56" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H19" t="s">
         <v>481</v>
@@ -17440,6 +18585,305 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A2:Q69"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.46484375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="51"/>
+      <c r="O2" s="56" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="56" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="3" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K3" s="7"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="51"/>
+      <c r="O3" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="53">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K4" s="7"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="51"/>
+      <c r="O4" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="P4" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K5" s="7"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="51"/>
+      <c r="P5" s="55" t="s">
+        <v>466</v>
+      </c>
+      <c r="Q5" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K6" s="7"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="51"/>
+      <c r="P6" s="55" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q6" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K7" s="7"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="51"/>
+      <c r="O7" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K8" s="7"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="51"/>
+      <c r="P8" s="55" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q8" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K9" s="7"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="51"/>
+      <c r="P9" s="55" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q9" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K10" s="7"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="51"/>
+      <c r="O10" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" s="55" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q10" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K11" s="7"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="51"/>
+      <c r="O11" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="P11" s="55" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q11" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="11"/>
+      <c r="O12" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="P12" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="O13" s="55" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q13" s="53">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="11:17" x14ac:dyDescent="0.45">
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="3"/>
+      <c r="C32" s="15"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A33" s="3"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A34" s="3"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A35" s="3"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A36" s="3"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A38" s="3"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A39" s="3"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A40" s="3"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A41" s="3"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A42" s="3"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A43" s="3"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A44" s="3"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A45" s="3"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A48" s="3"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A49" s="3"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A52" s="3"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A53" s="3"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A54" s="3"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A55" s="3"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A56" s="3"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A57" s="3"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A59" s="3"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A61" s="3"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A63" s="3"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A64" s="3"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A67" s="3"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A68" s="3"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
+      <c r="A69" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A2:V72"/>
@@ -17449,160 +18893,154 @@
     <col min="3" max="3" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.06640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="5.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="17:22" x14ac:dyDescent="0.45">
       <c r="Q2" s="56" t="s">
-        <v>528</v>
-      </c>
-      <c r="R2" s="56" t="s">
-        <v>486</v>
-      </c>
-      <c r="S2" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="T2" t="s">
-        <v>481</v>
+      <c r="R2" t="s">
+        <v>527</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" s="2"/>
     </row>
     <row r="3" spans="17:22" x14ac:dyDescent="0.45">
       <c r="Q3" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="53">
+        <v>509</v>
+      </c>
+      <c r="R3" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="R4" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4" s="53">
+      <c r="Q4" s="55" t="s">
+        <v>187</v>
+      </c>
+      <c r="R4" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S5" s="55" t="s">
-        <v>514</v>
-      </c>
-      <c r="T5" s="53">
+      <c r="Q5" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="17:22" x14ac:dyDescent="0.45">
       <c r="Q6" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="T6" s="53">
-        <v>14</v>
+        <v>132</v>
+      </c>
+      <c r="R6" s="53">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="R7" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="T7" s="53">
-        <v>14</v>
+      <c r="Q7" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="R7" s="53">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S8" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="T8" s="53">
+      <c r="Q8" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="R8" s="53">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S9" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="T9" s="53">
-        <v>1</v>
+      <c r="Q9" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="R9" s="53">
+        <v>3</v>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="10"/>
     </row>
     <row r="10" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S10" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="T10" s="53">
-        <v>1</v>
+      <c r="Q10" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="R10" s="53">
+        <v>3</v>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="13"/>
     </row>
     <row r="11" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S11" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="T11" s="53">
+      <c r="Q11" s="55" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" s="53">
         <v>1</v>
       </c>
       <c r="U11" s="3"/>
       <c r="V11" s="13"/>
     </row>
     <row r="12" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S12" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="T12" s="53">
+      <c r="Q12" s="55" t="s">
+        <v>56</v>
+      </c>
+      <c r="R12" s="53">
         <v>1</v>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="13"/>
     </row>
     <row r="13" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S13" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="T13" s="53">
-        <v>3</v>
+      <c r="Q13" s="55" t="s">
+        <v>36</v>
+      </c>
+      <c r="R13" s="53">
+        <v>1</v>
       </c>
       <c r="U13" s="3"/>
       <c r="V13" s="13"/>
     </row>
     <row r="14" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S14" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="T14" s="53">
-        <v>3</v>
+      <c r="Q14" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="R14" s="53">
+        <v>1</v>
       </c>
       <c r="U14" s="3"/>
       <c r="V14" s="13"/>
     </row>
     <row r="15" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S15" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="T15" s="53">
+      <c r="Q15" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="R15" s="53">
         <v>1</v>
       </c>
       <c r="U15" s="3"/>
       <c r="V15" s="13"/>
     </row>
     <row r="16" spans="17:22" x14ac:dyDescent="0.45">
-      <c r="S16" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="T16" s="53">
-        <v>1</v>
+      <c r="Q16" s="55" t="s">
+        <v>354</v>
+      </c>
+      <c r="R16" s="53">
+        <v>2</v>
       </c>
       <c r="U16" s="9"/>
       <c r="V16" s="13"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S17" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="T17" s="53">
+      <c r="Q17" s="55" t="s">
+        <v>384</v>
+      </c>
+      <c r="R17" s="53">
         <v>1</v>
       </c>
       <c r="U17" s="13"/>
@@ -17610,119 +19048,119 @@
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.45">
       <c r="Q18" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="T18" s="53">
-        <v>10</v>
+        <v>404</v>
+      </c>
+      <c r="R18" s="53">
+        <v>1</v>
       </c>
       <c r="U18" s="3"/>
       <c r="V18" s="13"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="R19" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="T19" s="53">
-        <v>2</v>
+      <c r="Q19" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="R19" s="53">
+        <v>1</v>
       </c>
       <c r="U19" s="3"/>
       <c r="V19" s="13"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S20" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="T20" s="53">
+      <c r="Q20" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="R20" s="53">
         <v>1</v>
       </c>
       <c r="U20" s="3"/>
       <c r="V20" s="13"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S21" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="T21" s="53">
+      <c r="Q21" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="R21" s="53">
         <v>1</v>
       </c>
       <c r="U21" s="3"/>
       <c r="V21" s="13"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="R22" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="T22" s="53">
-        <v>6</v>
+      <c r="Q22" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="R22" s="53">
+        <v>1</v>
       </c>
       <c r="U22" s="3"/>
       <c r="V22" s="13"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S23" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="T23" s="53">
-        <v>2</v>
+      <c r="Q23" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="R23" s="53">
+        <v>1</v>
       </c>
       <c r="U23" s="3"/>
       <c r="V23" s="13"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S24" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="T24" s="53">
+      <c r="Q24" s="55" t="s">
+        <v>417</v>
+      </c>
+      <c r="R24" s="53">
         <v>1</v>
       </c>
       <c r="U24" s="3"/>
       <c r="V24" s="13"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S25" s="55" t="s">
-        <v>404</v>
-      </c>
-      <c r="T25" s="53">
+      <c r="Q25" s="55" t="s">
+        <v>411</v>
+      </c>
+      <c r="R25" s="53">
         <v>1</v>
       </c>
       <c r="U25" s="3"/>
       <c r="V25" s="13"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S26" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="T26" s="53">
+      <c r="Q26" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="R26" s="53">
         <v>1</v>
       </c>
       <c r="U26" s="3"/>
       <c r="V26" s="13"/>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S27" s="55" t="s">
-        <v>401</v>
-      </c>
-      <c r="T27" s="53">
+      <c r="Q27" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="R27" s="53">
         <v>1</v>
       </c>
       <c r="U27" s="3"/>
       <c r="V27" s="13"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="R28" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="T28" s="53">
-        <v>2</v>
+      <c r="Q28" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="R28" s="53">
+        <v>1</v>
       </c>
       <c r="U28" s="10"/>
       <c r="V28" s="13"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="S29" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="T29" s="53">
+      <c r="Q29" s="55" t="s">
+        <v>355</v>
+      </c>
+      <c r="R29" s="53">
         <v>1</v>
       </c>
       <c r="U29" s="3"/>
@@ -17731,10 +19169,10 @@
     <row r="30" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A30" s="3"/>
       <c r="G30" s="3"/>
-      <c r="S30" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="T30" s="53">
+      <c r="Q30" s="55" t="s">
+        <v>106</v>
+      </c>
+      <c r="R30" s="53">
         <v>1</v>
       </c>
       <c r="U30" s="3"/>
@@ -17744,10 +19182,10 @@
       <c r="A31" s="3"/>
       <c r="G31" s="3"/>
       <c r="Q31" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="T31" s="53">
-        <v>3</v>
+        <v>432</v>
+      </c>
+      <c r="R31" s="53">
+        <v>33</v>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="13"/>
@@ -17755,180 +19193,86 @@
     <row r="32" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A32" s="3"/>
       <c r="G32" s="3"/>
-      <c r="R32" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="T32" s="53">
-        <v>1</v>
-      </c>
       <c r="U32" s="3"/>
       <c r="V32" s="13"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" s="3"/>
       <c r="G33" s="3"/>
-      <c r="S33" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="T33" s="53">
-        <v>1</v>
-      </c>
       <c r="U33" s="3"/>
       <c r="V33" s="13"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="R34" s="55" t="s">
-        <v>485</v>
-      </c>
-      <c r="T34" s="53">
-        <v>1</v>
-      </c>
       <c r="U34" s="3"/>
       <c r="V34" s="13"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A35" s="3"/>
       <c r="G35" s="3"/>
-      <c r="S35" s="55" t="s">
-        <v>417</v>
-      </c>
-      <c r="T35" s="53">
-        <v>1</v>
-      </c>
       <c r="U35" s="3"/>
       <c r="V35" s="13"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="R36" s="55" t="s">
-        <v>468</v>
-      </c>
-      <c r="T36" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A37" s="3"/>
       <c r="G37" s="14"/>
-      <c r="S37" s="55" t="s">
-        <v>411</v>
-      </c>
-      <c r="T37" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="38" spans="1:22" s="13" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="3"/>
       <c r="F38"/>
       <c r="G38" s="14"/>
-      <c r="Q38" s="55" t="s">
-        <v>31</v>
-      </c>
+      <c r="Q38"/>
       <c r="R38"/>
       <c r="S38"/>
-      <c r="T38" s="53">
-        <v>4</v>
-      </c>
+      <c r="T38"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A39" s="3"/>
       <c r="G39" s="3"/>
-      <c r="R39" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="T39" s="53">
-        <v>4</v>
-      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A40" s="3"/>
       <c r="G40" s="3"/>
-      <c r="S40" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="T40" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A41" s="3"/>
       <c r="F41" s="14"/>
       <c r="G41" s="3"/>
-      <c r="S41" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="T41" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A42" s="3"/>
       <c r="F42" s="14"/>
       <c r="G42" s="3"/>
-      <c r="S42" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="T42" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A43" s="3"/>
       <c r="F43" s="14"/>
       <c r="G43" s="3"/>
-      <c r="S43" s="55" t="s">
-        <v>355</v>
-      </c>
-      <c r="T43" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A44" s="3"/>
       <c r="F44" s="14"/>
       <c r="G44" s="3"/>
-      <c r="Q44" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="T44" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A45" s="3"/>
       <c r="F45" s="14"/>
       <c r="G45" s="3"/>
-      <c r="R45" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="T45" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A46" s="3"/>
       <c r="F46" s="14"/>
       <c r="G46" s="3"/>
-      <c r="S46" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="T46" s="53">
-        <v>1</v>
-      </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A47" s="3"/>
       <c r="F47" s="14"/>
       <c r="G47" s="3"/>
-      <c r="Q47" s="55" t="s">
-        <v>432</v>
-      </c>
-      <c r="T47" s="53">
-        <v>33</v>
-      </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A48" s="3"/>
@@ -18030,7 +19374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:J20"/>
@@ -18118,41 +19462,42 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AH69"/>
   <sheetFormatPr defaultColWidth="6.46484375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.53125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.1328125" style="55" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.53125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.59765625" style="55" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.19921875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.73046875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.06640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="10.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.73046875" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="8.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.53125" style="3" customWidth="1"/>
-    <col min="21" max="21" width="10.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.06640625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.9296875" style="3" customWidth="1"/>
-    <col min="26" max="26" width="10.19921875" style="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="28.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="29.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="31.796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="28.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="29.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.53125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="9" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.06640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.53125" style="3" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="29.796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="29.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="32.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="28.73046875" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="30.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="35" max="16384" width="6.46484375" style="3"/>
   </cols>
   <sheetData>
@@ -18164,22 +19509,22 @@
         <v>215</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D1" s="46" t="s">
-        <v>490</v>
+        <v>523</v>
       </c>
       <c r="E1" s="46" t="s">
-        <v>489</v>
+        <v>524</v>
       </c>
       <c r="F1" s="52" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="G1" s="46" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="H1" s="46" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I1" s="52" t="s">
         <v>340</v>
@@ -18191,13 +19536,13 @@
         <v>117</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>493</v>
+        <v>526</v>
       </c>
       <c r="O1" s="2" t="s">
         <v>67</v>
@@ -18233,7 +19578,7 @@
         <v>26</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="AA1" s="2" t="s">
         <v>115</v>
@@ -18279,11 +19624,11 @@
         <v>2</v>
       </c>
       <c r="H2" s="61" t="str">
-        <f>MID(Retro!$O2,1,FIND(":",Retro!$O2)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB</v>
       </c>
       <c r="I2" s="55">
-        <f>INT(MID(Retro!$L2,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J2" s="55">
@@ -18381,11 +19726,11 @@
         <v>1</v>
       </c>
       <c r="H3" t="str">
-        <f>MID(Retro!$O3,1,FIND(":",Retro!$O3)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I3">
-        <f>INT(MID(Retro!$L3,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J3">
@@ -18483,11 +19828,11 @@
         <v>5</v>
       </c>
       <c r="H4" s="61" t="str">
-        <f>MID(Retro!$O4,1,FIND(":",Retro!$O4)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>WR3</v>
       </c>
       <c r="I4" s="55">
-        <f>INT(MID(Retro!$L4,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J4" s="55">
@@ -18521,7 +19866,7 @@
         <v>96</v>
       </c>
       <c r="T4" s="55" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="U4" s="55"/>
       <c r="V4" s="55">
@@ -18585,11 +19930,11 @@
         <v>1</v>
       </c>
       <c r="H5" t="str">
-        <f>MID(Retro!$O5,1,FIND(":",Retro!$O5)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I5">
-        <f>INT(MID(Retro!$L5,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J5" s="55">
@@ -18687,11 +20032,11 @@
         <v>1</v>
       </c>
       <c r="H6" t="str">
-        <f>MID(Retro!$O6,1,FIND(":",Retro!$O6)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>TE</v>
       </c>
       <c r="I6">
-        <f>INT(MID(Retro!$L6,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J6" s="55">
@@ -18789,11 +20134,11 @@
         <v>1</v>
       </c>
       <c r="H7" t="str">
-        <f>MID(Retro!$O7,1,FIND(":",Retro!$O7)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I7">
-        <f>INT(MID(Retro!$L7,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J7" s="55">
@@ -18891,11 +20236,11 @@
         <v>1</v>
       </c>
       <c r="H8" t="str">
-        <f>MID(Retro!$O8,1,FIND(":",Retro!$O8)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I8">
-        <f>INT(MID(Retro!$L8,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J8">
@@ -18993,11 +20338,11 @@
         <v>1</v>
       </c>
       <c r="H9" t="str">
-        <f>MID(Retro!$O9,1,FIND(":",Retro!$O9)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I9">
-        <f>INT(MID(Retro!$L9,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J9" s="55">
@@ -19095,11 +20440,11 @@
         <v>2</v>
       </c>
       <c r="H10" s="61" t="str">
-        <f>MID(Retro!$O10,1,FIND(":",Retro!$O10)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I10" s="55">
-        <f>INT(MID(Retro!$L10,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J10" s="55">
@@ -19197,11 +20542,11 @@
         <v>1</v>
       </c>
       <c r="H11" t="str">
-        <f>MID(Retro!$O11,1,FIND(":",Retro!$O11)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB2</v>
       </c>
       <c r="I11">
-        <f>INT(MID(Retro!$L11,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J11" s="55">
@@ -19299,11 +20644,11 @@
         <v>1</v>
       </c>
       <c r="H12" t="str">
-        <f>MID(Retro!$O12,1,FIND(":",Retro!$O12)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB2</v>
       </c>
       <c r="I12">
-        <f>INT(MID(Retro!$L12,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J12" s="55">
@@ -19401,11 +20746,11 @@
         <v>1</v>
       </c>
       <c r="H13" t="str">
-        <f>MID(Retro!$O13,1,FIND(":",Retro!$O13)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I13">
-        <f>INT(MID(Retro!$L13,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J13" s="55">
@@ -19503,11 +20848,11 @@
         <v>1</v>
       </c>
       <c r="H14" t="str">
-        <f>MID(Retro!$O14,1,FIND(":",Retro!$O14)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I14">
-        <f>INT(MID(Retro!$L14,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J14" s="55">
@@ -19605,11 +20950,11 @@
         <v>1</v>
       </c>
       <c r="H15" t="str">
-        <f>MID(Retro!$O15,1,FIND(":",Retro!$O15)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I15">
-        <f>INT(MID(Retro!$L15,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J15" s="55">
@@ -19707,11 +21052,11 @@
         <v>1</v>
       </c>
       <c r="H16" t="str">
-        <f>MID(Retro!$O16,1,FIND(":",Retro!$O16)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I16">
-        <f>INT(MID(Retro!$L16,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J16" s="55">
@@ -19809,11 +21154,11 @@
         <v>1</v>
       </c>
       <c r="H17" t="str">
-        <f>MID(Retro!$O17,1,FIND(":",Retro!$O17)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>WR1</v>
       </c>
       <c r="I17">
-        <f>INT(MID(Retro!$L17,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J17" s="55">
@@ -19911,11 +21256,11 @@
         <v>1</v>
       </c>
       <c r="H18" t="str">
-        <f>MID(Retro!$O18,1,FIND(":",Retro!$O18)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I18">
-        <f>INT(MID(Retro!$L18,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J18" s="55">
@@ -20013,11 +21358,11 @@
         <v>1</v>
       </c>
       <c r="H19" t="str">
-        <f>MID(Retro!$O19,1,FIND(":",Retro!$O19)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB</v>
       </c>
       <c r="I19">
-        <f>INT(MID(Retro!$L19,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J19" s="55">
@@ -20115,11 +21460,11 @@
         <v>1</v>
       </c>
       <c r="H20" t="str">
-        <f>MID(Retro!$O20,1,FIND(":",Retro!$O20)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I20">
-        <f>INT(MID(Retro!$L20,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>3</v>
       </c>
       <c r="J20" s="55">
@@ -20217,11 +21562,11 @@
         <v>1</v>
       </c>
       <c r="H21" s="55" t="str">
-        <f>MID(Retro!$O21,1,FIND(":",Retro!$O21)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I21" s="55">
-        <f>INT(MID(Retro!$L21,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J21" s="55">
@@ -20319,11 +21664,11 @@
         <v>1</v>
       </c>
       <c r="H22" t="str">
-        <f>MID(Retro!$O22,1,FIND(":",Retro!$O22)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I22">
-        <f>INT(MID(Retro!$L22,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J22" s="55">
@@ -20421,11 +21766,11 @@
         <v>3</v>
       </c>
       <c r="H23" s="61" t="str">
-        <f>MID(Retro!$O23,1,FIND(":",Retro!$O23)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>TE2</v>
       </c>
       <c r="I23" s="55">
-        <f>INT(MID(Retro!$L23,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J23" s="55">
@@ -20523,11 +21868,11 @@
         <v>2</v>
       </c>
       <c r="H24" s="61" t="str">
-        <f>MID(Retro!$O24,1,FIND(":",Retro!$O24)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>WR1</v>
       </c>
       <c r="I24" s="55">
-        <f>INT(MID(Retro!$L24,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J24" s="55">
@@ -20625,11 +21970,11 @@
         <v>1</v>
       </c>
       <c r="H25" t="str">
-        <f>MID(Retro!$O25,1,FIND(":",Retro!$O25)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I25">
-        <f>INT(MID(Retro!$L25,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J25" s="55">
@@ -20727,11 +22072,11 @@
         <v>1</v>
       </c>
       <c r="H26" t="str">
-        <f>MID(Retro!$O26,1,FIND(":",Retro!$O26)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>RB1</v>
       </c>
       <c r="I26">
-        <f>INT(MID(Retro!$L26,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J26" s="55">
@@ -20829,11 +22174,11 @@
         <v>1</v>
       </c>
       <c r="H27" t="str">
-        <f>MID(Retro!$O27,1,FIND(":",Retro!$O27)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>WR1</v>
       </c>
       <c r="I27">
-        <f>INT(MID(Retro!$L27,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J27" s="55">
@@ -20931,11 +22276,11 @@
         <v>1</v>
       </c>
       <c r="H28" t="str">
-        <f>MID(Retro!$O28,1,FIND(":",Retro!$O28)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I28">
-        <f>INT(MID(Retro!$L28,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J28" s="55">
@@ -21033,11 +22378,11 @@
         <v>1</v>
       </c>
       <c r="H29" t="str">
-        <f>MID(Retro!$O29,1,FIND(":",Retro!$O29)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>TE1</v>
       </c>
       <c r="I29">
-        <f>INT(MID(Retro!$L29,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>2</v>
       </c>
       <c r="J29" s="55">
@@ -21135,11 +22480,11 @@
         <v>1</v>
       </c>
       <c r="H30" t="str">
-        <f>MID(Retro!$O30,1,FIND(":",Retro!$O30)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I30">
-        <f>INT(MID(Retro!$L30,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J30" s="55">
@@ -21237,11 +22582,11 @@
         <v>1</v>
       </c>
       <c r="H31" t="str">
-        <f>MID(Retro!$O31,1,FIND(":",Retro!$O31)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I31">
-        <f>INT(MID(Retro!$L31,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J31" s="55">
@@ -21339,11 +22684,11 @@
         <v>1</v>
       </c>
       <c r="H32" t="str">
-        <f>MID(Retro!$O32,1,FIND(":",Retro!$O32)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>QB</v>
       </c>
       <c r="I32">
-        <f>INT(MID(Retro!$L32,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J32" s="55">
@@ -21368,7 +22713,7 @@
         <v>355</v>
       </c>
       <c r="Q32" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="R32" t="s">
         <v>49</v>
@@ -21377,7 +22722,7 @@
         <v>423</v>
       </c>
       <c r="T32" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="U32"/>
       <c r="V32">
@@ -21396,22 +22741,22 @@
         <v>127.82</v>
       </c>
       <c r="AA32" t="s">
+        <v>492</v>
+      </c>
+      <c r="AB32" t="s">
+        <v>493</v>
+      </c>
+      <c r="AC32" t="s">
+        <v>494</v>
+      </c>
+      <c r="AD32" t="s">
+        <v>495</v>
+      </c>
+      <c r="AE32" t="s">
+        <v>496</v>
+      </c>
+      <c r="AF32" t="s">
         <v>497</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>498</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>499</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>500</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>501</v>
-      </c>
-      <c r="AF32" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:32" x14ac:dyDescent="0.45">
@@ -21439,11 +22784,11 @@
         <v>2</v>
       </c>
       <c r="H33" t="str">
-        <f>MID(Retro!$O33,1,FIND(":",Retro!$O33)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>WR1</v>
       </c>
       <c r="I33">
-        <f>INT(MID(Retro!$L33,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J33" s="55">
@@ -21471,13 +22816,13 @@
         <v>187</v>
       </c>
       <c r="R33" s="55" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="S33" s="55" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="T33" s="55" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="U33" s="55"/>
       <c r="V33" s="55">
@@ -21496,22 +22841,22 @@
         <v>111.89</v>
       </c>
       <c r="AA33" s="55" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="AB33" s="55" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="AC33" s="55" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="AD33" s="55" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="AE33" s="55" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="AF33" s="55" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="34" spans="1:32" x14ac:dyDescent="0.45">
@@ -21539,11 +22884,11 @@
         <v>1</v>
       </c>
       <c r="H34" s="18" t="str">
-        <f>MID(Retro!$O34,1,FIND(":",Retro!$O34)-1)</f>
+        <f>MID(Table1[[#This Row],[MVP_pos]],1,FIND(":",Table1[[#This Row],[MVP_pos]])-1)</f>
         <v>D</v>
       </c>
       <c r="I34" s="18">
-        <f>INT(MID(Retro!$L34,1,1))</f>
+        <f>INT(MID(Table1[[#This Row],[Key 2]],1,1))</f>
         <v>1</v>
       </c>
       <c r="J34" s="55">
@@ -21562,22 +22907,22 @@
         <v>15</v>
       </c>
       <c r="O34" s="55" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="P34" s="55" t="s">
         <v>63</v>
       </c>
       <c r="Q34" s="55" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="R34" s="55" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="S34" s="55" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="T34" s="55" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="U34" s="55"/>
       <c r="V34" s="55">
@@ -21596,22 +22941,22 @@
         <v>72</v>
       </c>
       <c r="AA34" s="55" t="s">
+        <v>514</v>
+      </c>
+      <c r="AB34" s="55" t="s">
+        <v>515</v>
+      </c>
+      <c r="AC34" s="55" t="s">
+        <v>516</v>
+      </c>
+      <c r="AD34" s="55" t="s">
+        <v>517</v>
+      </c>
+      <c r="AE34" s="55" t="s">
+        <v>518</v>
+      </c>
+      <c r="AF34" s="55" t="s">
         <v>519</v>
-      </c>
-      <c r="AB34" s="55" t="s">
-        <v>520</v>
-      </c>
-      <c r="AC34" s="55" t="s">
-        <v>521</v>
-      </c>
-      <c r="AD34" s="55" t="s">
-        <v>522</v>
-      </c>
-      <c r="AE34" s="55" t="s">
-        <v>523</v>
-      </c>
-      <c r="AF34" s="55" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="35" spans="1:32" s="10" customFormat="1" x14ac:dyDescent="0.45">
@@ -22273,7 +23618,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:X99"/>
@@ -23073,12 +24418,12 @@
         <v>355</v>
       </c>
       <c r="P32" s="55" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="R32" s="70"/>
       <c r="S32" s="70"/>
       <c r="T32" s="55" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.45">
@@ -23086,10 +24431,10 @@
         <v>187</v>
       </c>
       <c r="B33" s="55" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="C33" s="55" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F33" s="55" t="s">
         <v>57</v>
@@ -23098,33 +24443,33 @@
         <v>187</v>
       </c>
       <c r="L33" s="55" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="R33" s="70"/>
       <c r="S33" s="70"/>
       <c r="T33" s="55" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A34" s="52" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B34" s="55" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C34" s="55" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F34" s="55" t="s">
         <v>63</v>
       </c>
       <c r="I34" s="55"/>
       <c r="P34" s="69" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="Q34" s="55" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="R34" s="70"/>
       <c r="S34" s="70"/>
@@ -23386,18 +24731,18 @@
     <sortCondition ref="I46:L46"/>
   </sortState>
   <conditionalFormatting sqref="A63">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text=":DEN">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text=":DEN">
       <formula>NOT(ISERROR(SEARCH(":DEN",A63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text=":CIN">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text=":CIN">
       <formula>NOT(ISERROR(SEARCH(":CIN",A63)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F63 I63 L63 N63 P63">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text=":DEN">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text=":DEN">
       <formula>NOT(ISERROR(SEARCH(":DEN",F63)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text=":CIN">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text=":CIN">
       <formula>NOT(ISERROR(SEARCH(":CIN",F63)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -23407,472 +24752,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr codeName="Sheet6"/>
-  <dimension ref="A2:R69"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="51"/>
-      <c r="O2" s="56" t="s">
-        <v>528</v>
-      </c>
-      <c r="P2" s="56" t="s">
-        <v>486</v>
-      </c>
-      <c r="Q2" s="56" t="s">
-        <v>487</v>
-      </c>
-      <c r="R2" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="3" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K3" s="7"/>
-      <c r="L3" s="12"/>
-      <c r="M3" s="51"/>
-      <c r="O3" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="P3" s="55" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="55" t="s">
-        <v>187</v>
-      </c>
-      <c r="R3" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K4" s="7"/>
-      <c r="L4" s="12"/>
-      <c r="M4" s="51"/>
-      <c r="Q4" s="55" t="s">
-        <v>12</v>
-      </c>
-      <c r="R4" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K5" s="7"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="51"/>
-      <c r="Q5" s="55" t="s">
-        <v>132</v>
-      </c>
-      <c r="R5" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K6" s="7"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="51"/>
-      <c r="Q6" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="R6" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K7" s="7"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="51"/>
-      <c r="Q7" s="55" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K8" s="7"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="51"/>
-      <c r="Q8" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="R8" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K9" s="7"/>
-      <c r="L9" s="12"/>
-      <c r="M9" s="51"/>
-      <c r="Q9" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="R9" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K10" s="7"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="51"/>
-      <c r="Q10" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="R10" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K11" s="7"/>
-      <c r="L11" s="12"/>
-      <c r="M11" s="51"/>
-      <c r="Q11" s="55" t="s">
-        <v>36</v>
-      </c>
-      <c r="R11" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="11"/>
-      <c r="Q12" s="55" t="s">
-        <v>56</v>
-      </c>
-      <c r="R12" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="O13" s="55" t="s">
-        <v>529</v>
-      </c>
-      <c r="P13" s="55" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q13" s="55" t="s">
-        <v>50</v>
-      </c>
-      <c r="R13" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="Q14" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="R14" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="P15" s="55" t="s">
-        <v>466</v>
-      </c>
-      <c r="Q15" s="55" t="s">
-        <v>354</v>
-      </c>
-      <c r="R15" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="11:18" x14ac:dyDescent="0.45">
-      <c r="K16" s="55"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="55"/>
-      <c r="Q16" s="55" t="s">
-        <v>384</v>
-      </c>
-      <c r="R16" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q17" s="55" t="s">
-        <v>404</v>
-      </c>
-      <c r="R17" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q18" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="R18" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q19" s="55" t="s">
-        <v>401</v>
-      </c>
-      <c r="R19" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="P20" s="55" t="s">
-        <v>467</v>
-      </c>
-      <c r="Q20" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="R20" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q21" s="55" t="s">
-        <v>73</v>
-      </c>
-      <c r="R21" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="O22" s="55" t="s">
-        <v>530</v>
-      </c>
-      <c r="P22" s="55" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q22" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="R22" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="P23" s="55" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q23" s="55" t="s">
-        <v>417</v>
-      </c>
-      <c r="R23" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="P24" s="55" t="s">
-        <v>468</v>
-      </c>
-      <c r="Q24" s="55" t="s">
-        <v>411</v>
-      </c>
-      <c r="R24" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="O25" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="P25" s="55" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q25" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="R25" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q26" s="55" t="s">
-        <v>216</v>
-      </c>
-      <c r="R26" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q27" s="55" t="s">
-        <v>355</v>
-      </c>
-      <c r="R27" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="Q28" s="55" t="s">
-        <v>188</v>
-      </c>
-      <c r="R28" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="O29" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="P29" s="55" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q29" s="55" t="s">
-        <v>106</v>
-      </c>
-      <c r="R29" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A30" s="3"/>
-      <c r="O30" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="P30" s="55" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q30" s="55" t="s">
-        <v>514</v>
-      </c>
-      <c r="R30" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A31" s="3"/>
-      <c r="O31" s="55" t="s">
-        <v>432</v>
-      </c>
-      <c r="R31" s="53">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A32" s="3"/>
-      <c r="C32" s="15"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A33" s="3"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A34" s="3"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A35" s="3"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A36" s="3"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A37" s="3"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A38" s="3"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A39" s="3"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A40" s="3"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A41" s="3"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A42" s="3"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A43" s="3"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A44" s="3"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A45" s="3"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A46" s="3"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A47" s="3"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A48" s="3"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A49" s="3"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A50" s="3"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A51" s="3"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A52" s="3"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A53" s="3"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A54" s="3"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A55" s="3"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A56" s="3"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A57" s="3"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A58" s="3"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A59" s="3"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A60" s="3"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A61" s="3"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A62" s="3"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A63" s="3"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A64" s="3"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A65" s="3"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A66" s="3"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A67" s="3"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A68" s="3"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A69" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/2025/retro_2025.xlsx
+++ b/2025/retro_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NFL-Fantasy\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AF23B9-3431-403F-86E3-67331FBB15AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A9D6F5B-CD0E-48FD-9C68-E5279FA80FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="651" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="651" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" state="hidden" r:id="rId1"/>
@@ -35,7 +35,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId10"/>
-    <pivotCache cacheId="37" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -92,7 +92,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="531">
   <si>
     <t>p2_pos</t>
   </si>
@@ -1684,13 +1684,7 @@
     <t>TE1</t>
   </si>
   <si>
-    <t>Count of LSal Key</t>
-  </si>
-  <si>
     <t>Count of Key 2</t>
-  </si>
-  <si>
-    <t>Row Labels</t>
   </si>
 </sst>
 </file>
@@ -2232,7 +2226,7 @@
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2310,9 +2304,6 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3398,7 +3389,31 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:delete val="1"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr/>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
           <c:extLst>
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
@@ -3426,6 +3441,39 @@
             </c:strRef>
           </c:tx>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Wins by Key'!$G$3:$G$6</c:f>
@@ -5763,7 +5811,7 @@
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -5785,7 +5833,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wins by Key'!$R$2</c:f>
+              <c:f>'Wins by Key'!$S$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5804,9 +5852,66 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'Wins by Key'!$Q$3:$Q$15</c:f>
+              <c:f>'Wins by Key'!$Q$3:$R$12</c:f>
               <c:multiLvlStrCache>
                 <c:ptCount val="9"/>
                 <c:lvl>
@@ -5854,7 +5959,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wins by Key'!$R$3:$R$15</c:f>
+              <c:f>'Wins by Key'!$S$3:$S$12</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
@@ -6255,7 +6360,7 @@
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -6277,7 +6382,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Wins by Key'!$K$17</c:f>
+              <c:f>'Wins by Key'!$AC$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -6296,9 +6401,66 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>'Wins by Key'!$J$18:$J$37</c:f>
+              <c:f>'Wins by Key'!$AB$3:$AB$22</c:f>
               <c:strCache>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
@@ -6363,7 +6525,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Wins by Key'!$K$18:$K$37</c:f>
+              <c:f>'Wins by Key'!$AC$3:$AC$22</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -6728,31 +6890,31 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>26</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>20</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>13</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6834,25 +6996,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>18</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0</c:v>
@@ -6937,7 +7099,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>33</c:v>
+                  <c:v>15</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1</c:v>
@@ -11997,16 +12159,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>542924</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>171449</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>962025</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>19049</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -14935,29 +15097,28 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05D7BD1D-EF91-4589-AB19-3A3F47210B36}" name="PivotTable1" cacheId="37" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="Q2:R15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{05D7BD1D-EF91-4589-AB19-3A3F47210B36}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="Q2:S12" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="32">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="10">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="9">
         <item x="0"/>
         <item x="1"/>
         <item x="6"/>
@@ -14967,39 +15128,36 @@
         <item x="8"/>
         <item x="4"/>
         <item x="7"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="8"/>
     <field x="11"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="10">
     <i>
       <x/>
-    </i>
-    <i r="1">
       <x/>
     </i>
     <i r="1">
@@ -15013,8 +15171,6 @@
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i r="1">
       <x v="4"/>
     </i>
     <i r="1">
@@ -15028,8 +15184,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i r="1">
       <x v="8"/>
     </i>
     <i t="grand">
@@ -15059,7 +15213,7 @@
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
     <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -15067,7 +15221,7 @@
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30460D7E-01F5-4B38-BABC-8DDA21E1A2BD}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="LS Key">
-  <location ref="J17:K37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <location ref="AB2:AC22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="33">
     <pivotField numFmtId="4" showAll="0"/>
     <pivotField showAll="0"/>
@@ -15219,7 +15373,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of LSal Key" fld="13" subtotal="count" baseField="13" baseItem="1"/>
+    <dataField name="Count" fld="13" subtotal="count" baseField="13" baseItem="1"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="0" format="1" series="1">
@@ -15372,14 +15526,14 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{112CBA6A-377D-417E-81DA-DA2EC619D049}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="2" rowHeaderCaption="Key">
   <location ref="R2:T25" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="33">
-    <pivotField compact="0" numFmtId="4" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" numFmtId="4" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="10">
         <item x="9"/>
         <item x="1"/>
@@ -15394,8 +15548,8 @@
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="9">
         <item x="0"/>
@@ -15409,7 +15563,7 @@
         <item x="7"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="11">
         <item x="4"/>
         <item x="3"/>
@@ -15425,24 +15579,24 @@
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="6">
         <item x="3"/>
@@ -16497,7 +16651,22 @@
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}" name="tPositionMatrix" displayName="tPositionMatrix" ref="A1:T35" totalsRowCount="1" headerRowDxfId="46" dataDxfId="45" totalsRowDxfId="44">
-  <autoFilter ref="A1:T34" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}"/>
+  <autoFilter ref="A1:T34" xr:uid="{CB264086-7BC5-42E2-AA25-9A4C16A77374}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="QB:ARI"/>
+        <filter val="QB:BAL"/>
+        <filter val="QB:CHI"/>
+        <filter val="QB:DAL"/>
+        <filter val="QB:DEN"/>
+        <filter val="QB:KC"/>
+        <filter val="QB:LAC"/>
+        <filter val="QB:LAR"/>
+        <filter val="QB:SEA"/>
+        <filter val="QB:TB"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="20">
     <tableColumn id="1" xr3:uid="{DFDD9EE6-32DA-48A0-AD42-31F50B96249F}" name="MVP" totalsRowFunction="count" dataDxfId="43" totalsRowDxfId="42"/>
     <tableColumn id="2" xr3:uid="{B9ABA996-39DD-49BD-9BE5-4A2B156287F7}" name="D" totalsRowFunction="count" dataDxfId="41" totalsRowDxfId="40"/>
@@ -17441,27 +17610,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="B2:Z38"/>
+  <dimension ref="B2:AC38"/>
   <sheetFormatPr defaultColWidth="7.59765625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
     <col min="2" max="2" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.796875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="2.59765625" customWidth="1"/>
     <col min="7" max="7" width="10.46484375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.59765625" customWidth="1"/>
     <col min="10" max="10" width="10.46484375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.1328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="4.73046875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="2.59765625" customWidth="1"/>
-    <col min="17" max="17" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.86328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.59765625" customWidth="1"/>
+    <col min="27" max="27" width="2.59765625" customWidth="1"/>
+    <col min="28" max="28" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="7:26" x14ac:dyDescent="0.45">
+    <row r="2" spans="7:29" x14ac:dyDescent="0.45">
       <c r="G2" s="56" t="s">
         <v>340</v>
       </c>
@@ -17469,422 +17643,408 @@
         <v>481</v>
       </c>
       <c r="Q2" s="56" t="s">
-        <v>532</v>
-      </c>
-      <c r="R2" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="3" spans="7:26" x14ac:dyDescent="0.45">
+        <v>340</v>
+      </c>
+      <c r="R2" s="56" t="s">
+        <v>520</v>
+      </c>
+      <c r="S2" t="s">
+        <v>530</v>
+      </c>
+      <c r="AB2" s="56" t="s">
+        <v>488</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="7:29" x14ac:dyDescent="0.45">
       <c r="G3" s="55">
         <v>1</v>
       </c>
       <c r="H3" s="53">
         <v>23</v>
       </c>
-      <c r="Q3" s="57">
+      <c r="Q3" s="55">
         <v>1</v>
       </c>
-      <c r="R3" s="53">
-        <v>23</v>
+      <c r="R3" s="55">
+        <v>12</v>
+      </c>
+      <c r="S3" s="53">
+        <v>12</v>
       </c>
       <c r="V3" s="12"/>
       <c r="W3" s="12"/>
       <c r="X3" s="12"/>
-    </row>
-    <row r="4" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="AB3" s="57">
+        <v>12</v>
+      </c>
+      <c r="AC3" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="7:29" x14ac:dyDescent="0.45">
       <c r="G4" s="55">
         <v>2</v>
       </c>
       <c r="H4" s="53">
         <v>9</v>
       </c>
-      <c r="Q4" s="73">
-        <v>12</v>
-      </c>
-      <c r="R4" s="53">
-        <v>12</v>
+      <c r="R4" s="55">
+        <v>13</v>
+      </c>
+      <c r="S4" s="53">
+        <v>6</v>
       </c>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12"/>
-    </row>
-    <row r="5" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="AB4" s="57">
+        <v>14</v>
+      </c>
+      <c r="AC4" s="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="7:29" x14ac:dyDescent="0.45">
       <c r="G5" s="55">
         <v>3</v>
       </c>
       <c r="H5" s="53">
         <v>1</v>
       </c>
-      <c r="Q5" s="73">
-        <v>13</v>
-      </c>
-      <c r="R5" s="53">
-        <v>6</v>
+      <c r="R5" s="55">
+        <v>14</v>
+      </c>
+      <c r="S5" s="53">
+        <v>3</v>
       </c>
       <c r="U5" s="16"/>
       <c r="V5" s="12"/>
       <c r="W5" s="12"/>
       <c r="X5" s="12"/>
-    </row>
-    <row r="6" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="AB5" s="57">
+        <v>15</v>
+      </c>
+      <c r="AC5" s="53">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="7:29" x14ac:dyDescent="0.45">
       <c r="G6" s="55" t="s">
         <v>432</v>
       </c>
       <c r="H6" s="53">
         <v>33</v>
       </c>
-      <c r="Q6" s="73">
-        <v>14</v>
-      </c>
-      <c r="R6" s="53">
-        <v>3</v>
+      <c r="R6" s="55">
+        <v>16</v>
+      </c>
+      <c r="S6" s="53">
+        <v>2</v>
       </c>
       <c r="U6" s="16"/>
       <c r="V6" s="12"/>
       <c r="W6" s="12"/>
       <c r="X6" s="12"/>
-    </row>
-    <row r="7" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q7" s="73">
+      <c r="AB6" s="57">
         <v>16</v>
       </c>
-      <c r="R7" s="53">
+      <c r="AC6" s="53">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="Q7" s="55">
+        <v>2</v>
+      </c>
+      <c r="R7" s="55">
+        <v>23</v>
+      </c>
+      <c r="S7" s="53">
+        <v>6</v>
       </c>
       <c r="U7" s="16"/>
       <c r="V7" s="12"/>
       <c r="W7" s="12"/>
       <c r="X7" s="12"/>
-    </row>
-    <row r="8" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q8" s="57">
-        <v>2</v>
-      </c>
-      <c r="R8" s="53">
-        <v>9</v>
+      <c r="AB7" s="57">
+        <v>17</v>
+      </c>
+      <c r="AC7" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="R8" s="55">
+        <v>24</v>
+      </c>
+      <c r="S8" s="53">
+        <v>1</v>
       </c>
       <c r="U8" s="16"/>
       <c r="V8" s="12"/>
       <c r="W8" s="12"/>
       <c r="X8" s="12"/>
-    </row>
-    <row r="9" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q9" s="73">
-        <v>23</v>
-      </c>
-      <c r="R9" s="53">
-        <v>6</v>
+      <c r="AB8" s="57">
+        <v>18</v>
+      </c>
+      <c r="AC8" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="R9" s="55">
+        <v>27</v>
+      </c>
+      <c r="S9" s="53">
+        <v>1</v>
       </c>
       <c r="U9" s="16"/>
       <c r="V9" s="12"/>
       <c r="W9" s="12"/>
       <c r="X9" s="12"/>
-    </row>
-    <row r="10" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q10" s="73">
-        <v>24</v>
-      </c>
-      <c r="R10" s="53">
+      <c r="AB9" s="57">
+        <v>19</v>
+      </c>
+      <c r="AC9" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="R10" s="55">
+        <v>29</v>
+      </c>
+      <c r="S10" s="53">
         <v>1</v>
       </c>
       <c r="U10" s="16"/>
       <c r="V10" s="12"/>
       <c r="W10" s="12"/>
       <c r="X10" s="12"/>
-    </row>
-    <row r="11" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q11" s="73">
-        <v>27</v>
-      </c>
-      <c r="R11" s="53">
+      <c r="AB10" s="57">
+        <v>20</v>
+      </c>
+      <c r="AC10" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="Q11" s="55">
+        <v>3</v>
+      </c>
+      <c r="R11" s="55">
+        <v>34</v>
+      </c>
+      <c r="S11" s="53">
         <v>1</v>
       </c>
       <c r="U11" s="16"/>
       <c r="V11" s="12"/>
       <c r="W11" s="12"/>
       <c r="X11" s="12"/>
-    </row>
-    <row r="12" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q12" s="73">
-        <v>29</v>
-      </c>
-      <c r="R12" s="53">
+      <c r="AB11" s="57">
+        <v>21</v>
+      </c>
+      <c r="AC11" s="53">
         <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="7:29" x14ac:dyDescent="0.45">
+      <c r="Q12" s="55" t="s">
+        <v>432</v>
+      </c>
+      <c r="S12" s="53">
+        <v>33</v>
       </c>
       <c r="U12" s="16"/>
       <c r="V12" s="12"/>
       <c r="W12" s="12"/>
       <c r="X12" s="12"/>
-    </row>
-    <row r="13" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q13" s="57">
-        <v>3</v>
-      </c>
-      <c r="R13" s="53">
+      <c r="AB12" s="57">
+        <v>22</v>
+      </c>
+      <c r="AC12" s="53">
         <v>1</v>
       </c>
+    </row>
+    <row r="13" spans="7:29" x14ac:dyDescent="0.45">
       <c r="T13" s="16"/>
       <c r="U13" s="16"/>
       <c r="V13" s="12"/>
       <c r="W13" s="12"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="12"/>
-    </row>
-    <row r="14" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q14" s="73">
-        <v>34</v>
-      </c>
-      <c r="R14" s="53">
-        <v>1</v>
-      </c>
+      <c r="AB13" s="57">
+        <v>23</v>
+      </c>
+      <c r="AC13" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="7:29" x14ac:dyDescent="0.45">
       <c r="T14" s="16"/>
       <c r="U14" s="16"/>
       <c r="V14" s="12"/>
       <c r="W14" s="12"/>
       <c r="X14" s="12"/>
       <c r="Z14" s="16"/>
-    </row>
-    <row r="15" spans="7:26" x14ac:dyDescent="0.45">
-      <c r="Q15" s="57" t="s">
-        <v>432</v>
-      </c>
-      <c r="R15" s="53">
-        <v>33</v>
-      </c>
+      <c r="AB14" s="57">
+        <v>24</v>
+      </c>
+      <c r="AC14" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="7:29" x14ac:dyDescent="0.45">
       <c r="T15" s="16"/>
       <c r="U15" s="16"/>
       <c r="V15" s="12"/>
-    </row>
-    <row r="16" spans="7:26" x14ac:dyDescent="0.45">
+      <c r="AB15" s="57">
+        <v>26</v>
+      </c>
+      <c r="AC15" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="7:29" x14ac:dyDescent="0.45">
       <c r="U16" s="16"/>
       <c r="V16" s="12"/>
       <c r="X16" s="12"/>
       <c r="Z16" s="16"/>
-    </row>
-    <row r="17" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J17" s="56" t="s">
-        <v>488</v>
-      </c>
-      <c r="K17" t="s">
-        <v>530</v>
-      </c>
+      <c r="AB16" s="57">
+        <v>27</v>
+      </c>
+      <c r="AC16" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U17" s="16"/>
       <c r="V17" s="12"/>
       <c r="Z17" s="16"/>
-    </row>
-    <row r="18" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J18" s="57">
-        <v>12</v>
-      </c>
-      <c r="K18" s="53">
-        <v>1</v>
-      </c>
+      <c r="AB17" s="57">
+        <v>31</v>
+      </c>
+      <c r="AC17" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U18" s="16"/>
       <c r="V18" s="12"/>
-    </row>
-    <row r="19" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J19" s="57">
-        <v>14</v>
-      </c>
-      <c r="K19" s="53">
-        <v>3</v>
-      </c>
+      <c r="AB18" s="57">
+        <v>35</v>
+      </c>
+      <c r="AC18" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U19" s="16"/>
       <c r="V19" s="12"/>
-    </row>
-    <row r="20" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J20" s="57">
-        <v>15</v>
-      </c>
-      <c r="K20" s="53">
-        <v>6</v>
-      </c>
+      <c r="AB19" s="57">
+        <v>40</v>
+      </c>
+      <c r="AC19" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U20" s="16"/>
       <c r="V20" s="12"/>
-    </row>
-    <row r="21" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J21" s="57">
-        <v>16</v>
-      </c>
-      <c r="K21" s="53">
-        <v>2</v>
-      </c>
+      <c r="AB20" s="57">
+        <v>42</v>
+      </c>
+      <c r="AC20" s="53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U21" s="16"/>
       <c r="V21" s="12"/>
-    </row>
-    <row r="22" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J22" s="57">
-        <v>17</v>
-      </c>
-      <c r="K22" s="53">
-        <v>1</v>
-      </c>
+      <c r="AB21" s="57">
+        <v>47</v>
+      </c>
+      <c r="AC21" s="53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U22" s="16"/>
       <c r="V22" s="12"/>
-    </row>
-    <row r="23" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J23" s="57">
-        <v>18</v>
-      </c>
-      <c r="K23" s="53">
-        <v>1</v>
-      </c>
+      <c r="AB22" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="AC22" s="53">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:29" x14ac:dyDescent="0.45">
       <c r="U23" s="16"/>
       <c r="V23" s="12"/>
     </row>
-    <row r="24" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="52"/>
       <c r="E24" s="2"/>
-      <c r="J24" s="57">
-        <v>19</v>
-      </c>
-      <c r="K24" s="53">
-        <v>2</v>
-      </c>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
       <c r="U24" s="16"/>
       <c r="V24" s="12"/>
     </row>
-    <row r="25" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:29" x14ac:dyDescent="0.45">
       <c r="C25" s="51"/>
-      <c r="J25" s="57">
-        <v>20</v>
-      </c>
-      <c r="K25" s="53">
-        <v>2</v>
-      </c>
       <c r="U25" s="16"/>
       <c r="V25" s="12"/>
     </row>
-    <row r="26" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B26" s="54"/>
       <c r="C26" s="51"/>
       <c r="E26" s="51"/>
-      <c r="J26" s="57">
-        <v>21</v>
-      </c>
-      <c r="K26" s="53">
-        <v>1</v>
-      </c>
       <c r="U26" s="16"/>
       <c r="V26" s="12"/>
     </row>
-    <row r="27" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B27" s="54"/>
       <c r="C27" s="51"/>
       <c r="E27" s="51"/>
       <c r="F27" s="51"/>
-      <c r="J27" s="57">
-        <v>22</v>
-      </c>
-      <c r="K27" s="53">
-        <v>1</v>
-      </c>
       <c r="U27" s="16"/>
       <c r="V27" s="12"/>
     </row>
-    <row r="28" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B28" s="54"/>
       <c r="C28" s="51"/>
       <c r="E28" s="51"/>
       <c r="F28" s="51"/>
-      <c r="J28" s="57">
-        <v>23</v>
-      </c>
-      <c r="K28" s="53">
-        <v>2</v>
-      </c>
       <c r="U28" s="16"/>
       <c r="V28" s="12"/>
     </row>
-    <row r="29" spans="2:26" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:29" x14ac:dyDescent="0.45">
       <c r="B29" s="54"/>
       <c r="C29" s="51"/>
       <c r="E29" s="51"/>
       <c r="F29" s="51"/>
-      <c r="J29" s="57">
-        <v>24</v>
-      </c>
-      <c r="K29" s="53">
-        <v>2</v>
-      </c>
       <c r="U29" s="16"/>
       <c r="V29" s="12"/>
     </row>
-    <row r="30" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J30" s="57">
-        <v>26</v>
-      </c>
-      <c r="K30" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J31" s="57">
-        <v>27</v>
-      </c>
-      <c r="K31" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:26" x14ac:dyDescent="0.45">
-      <c r="J32" s="57">
-        <v>31</v>
-      </c>
-      <c r="K32" s="53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="10:18" x14ac:dyDescent="0.45">
-      <c r="J33" s="57">
-        <v>35</v>
-      </c>
-      <c r="K33" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="10:18" x14ac:dyDescent="0.45">
-      <c r="J34" s="57">
-        <v>40</v>
-      </c>
-      <c r="K34" s="53">
-        <v>1</v>
-      </c>
+    <row r="34" spans="14:18" x14ac:dyDescent="0.45">
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="10:18" x14ac:dyDescent="0.45">
-      <c r="J35" s="57">
-        <v>42</v>
-      </c>
-      <c r="K35" s="53">
-        <v>1</v>
-      </c>
+    <row r="35" spans="14:18" x14ac:dyDescent="0.45">
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="10:18" x14ac:dyDescent="0.45">
-      <c r="J36" s="57">
-        <v>47</v>
-      </c>
-      <c r="K36" s="53">
-        <v>2</v>
-      </c>
+    <row r="36" spans="14:18" x14ac:dyDescent="0.45">
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="10:18" x14ac:dyDescent="0.45">
-      <c r="J37" s="57" t="s">
-        <v>432</v>
-      </c>
-      <c r="K37" s="53">
-        <v>33</v>
-      </c>
+    <row r="37" spans="14:18" x14ac:dyDescent="0.45">
       <c r="N37" s="4"/>
       <c r="Q37" s="5"/>
     </row>
-    <row r="38" spans="10:18" x14ac:dyDescent="0.45">
+    <row r="38" spans="14:18" x14ac:dyDescent="0.45">
       <c r="N38" s="8"/>
       <c r="O38" s="4"/>
       <c r="R38" s="5"/>
@@ -18062,7 +18222,7 @@
       <c r="O3" s="50"/>
       <c r="P3" s="50">
         <f>tPositionMatrix[[#Totals],[MVP]]</f>
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="R3" s="14"/>
       <c r="S3" s="14"/>
@@ -18073,10 +18233,10 @@
       </c>
       <c r="N4" s="12" cm="1">
         <f t="array" ref="N4:O4">tPositionMatrix[[#Totals],[D]:[D2]]</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O4" s="50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4" s="50"/>
       <c r="Q4" s="50"/>
@@ -18089,10 +18249,10 @@
       </c>
       <c r="N5" s="12" cm="1">
         <f t="array" ref="N5:O5">tPositionMatrix[[#Totals],[K]:[K2]]</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="O5" s="50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" s="50"/>
       <c r="Q5" s="50"/>
@@ -18105,10 +18265,10 @@
       </c>
       <c r="N6" s="12" cm="1">
         <f t="array" ref="N6:P6">tPositionMatrix[[#Totals],[QB]:[QB2]]</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="O6" s="50">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="P6" s="50">
         <v>1</v>
@@ -18123,10 +18283,10 @@
       </c>
       <c r="N7" s="12" cm="1">
         <f t="array" ref="N7:P7">tPositionMatrix[[#Totals],[RB]:[RB2]]</f>
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O7" s="50">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P7" s="50">
         <v>1</v>
@@ -18141,10 +18301,10 @@
       </c>
       <c r="N8" s="12" cm="1">
         <f t="array" ref="N8:O8">tPositionMatrix[[#Totals],[TE]:[TE2]]</f>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="O8" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P8" s="50"/>
       <c r="Q8" s="50"/>
@@ -18155,7 +18315,7 @@
       </c>
       <c r="N9" s="12" cm="1">
         <f t="array" ref="N9:O9">tPositionMatrix[[#Totals],[WR1]:[WR12]]</f>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O9" s="50">
         <v>2</v>
@@ -18169,10 +18329,10 @@
       </c>
       <c r="N10" s="12" cm="1">
         <f t="array" ref="N10:O10">tPositionMatrix[[#Totals],[WR2]:[WR22]]</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="O10" s="50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" s="50"/>
       <c r="Q10" s="50"/>
@@ -18183,7 +18343,7 @@
       </c>
       <c r="N11" s="12" cm="1">
         <f t="array" ref="N11:O11">tPositionMatrix[[#Totals],[WR3]:[WR32]]</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O11" s="50">
         <v>0</v>
@@ -18197,7 +18357,7 @@
       </c>
       <c r="N12" s="12">
         <f>tPositionMatrix[[#Totals],[WR4]]</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O12" s="50"/>
       <c r="P12" s="50"/>
@@ -23717,7 +23877,7 @@
       <c r="W1" s="65"/>
       <c r="X1" s="65"/>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" s="67" t="s">
         <v>50</v>
       </c>
@@ -23763,7 +23923,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A4" s="67" t="s">
         <v>106</v>
       </c>
@@ -23809,7 +23969,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" s="67" t="s">
         <v>140</v>
       </c>
@@ -23832,7 +23992,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" s="67" t="s">
         <v>92</v>
       </c>
@@ -23901,7 +24061,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A10" s="67" t="s">
         <v>24</v>
       </c>
@@ -23924,7 +24084,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A11" s="67" t="s">
         <v>73</v>
       </c>
@@ -23947,7 +24107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.45">
       <c r="A12" s="67" t="s">
         <v>20</v>
       </c>
@@ -24056,7 +24216,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A17" s="67" t="s">
         <v>216</v>
       </c>
@@ -24102,7 +24262,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A19" s="67" t="s">
         <v>233</v>
       </c>
@@ -24125,7 +24285,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A20" s="67" t="s">
         <v>244</v>
       </c>
@@ -24171,7 +24331,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A22" s="67" t="s">
         <v>268</v>
       </c>
@@ -24191,7 +24351,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A23" s="67" t="s">
         <v>291</v>
       </c>
@@ -24214,7 +24374,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A24" s="67" t="s">
         <v>292</v>
       </c>
@@ -24237,7 +24397,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A25" s="67" t="s">
         <v>304</v>
       </c>
@@ -24260,7 +24420,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A26" s="67" t="s">
         <v>316</v>
       </c>
@@ -24283,7 +24443,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A27" s="67" t="s">
         <v>328</v>
       </c>
@@ -24329,7 +24489,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A29" s="67" t="s">
         <v>367</v>
       </c>
@@ -24451,7 +24611,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.45">
       <c r="A34" s="52" t="s">
         <v>509</v>
       </c>
@@ -24477,31 +24637,31 @@
     <row r="35" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[MVP])</f>
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[D])</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[D2])</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[K])</f>
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[K2])</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[QB])</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="G35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[QB1])</f>
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="H35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[QB2])</f>
@@ -24509,11 +24669,11 @@
       </c>
       <c r="I35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[RB])</f>
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="J35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[RB1])</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[RB2])</f>
@@ -24521,15 +24681,15 @@
       </c>
       <c r="L35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[TE])</f>
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="M35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[TE2])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR1])</f>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR12])</f>
@@ -24537,15 +24697,15 @@
       </c>
       <c r="P35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR2])</f>
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="Q35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR22])</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR3])</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="S35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR32])</f>
@@ -24553,7 +24713,7 @@
       </c>
       <c r="T35" s="67">
         <f>SUBTOTAL(103,tPositionMatrix[WR4])</f>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.45">
